--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/DASHBOARD-METAS-PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="904" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C32C9E3-7EBC-4EBF-8184-DE6579C46365}"/>
+  <xr:revisionPtr revIDLastSave="933" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{305420D5-0247-4563-82A2-525971245A2B}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -12033,7 +12033,9 @@
       <c r="C535" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D535" s="2"/>
+      <c r="D535" s="2">
+        <v>541</v>
+      </c>
       <c r="E535" s="18">
         <v>4252.5</v>
       </c>
@@ -12051,7 +12053,9 @@
       <c r="C536" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D536" s="2"/>
+      <c r="D536" s="2">
+        <v>594.5</v>
+      </c>
       <c r="E536" s="18">
         <v>3780</v>
       </c>
@@ -12069,7 +12073,9 @@
       <c r="C537" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D537" s="2"/>
+      <c r="D537" s="2">
+        <v>421</v>
+      </c>
       <c r="E537" s="18">
         <v>1417.5</v>
       </c>
@@ -12087,7 +12093,9 @@
       <c r="C538" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D538" s="2"/>
+      <c r="D538" s="2">
+        <v>422</v>
+      </c>
       <c r="E538" s="18">
         <v>3900</v>
       </c>
@@ -12105,7 +12113,9 @@
       <c r="C539" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D539" s="2"/>
+      <c r="D539" s="2">
+        <v>312</v>
+      </c>
       <c r="E539" s="18">
         <v>2600</v>
       </c>
@@ -12123,7 +12133,9 @@
       <c r="C540" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D540" s="2"/>
+      <c r="D540" s="2">
+        <v>481</v>
+      </c>
       <c r="E540" s="18">
         <v>1670</v>
       </c>
@@ -12141,7 +12153,9 @@
       <c r="C541" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D541" s="2"/>
+      <c r="D541" s="2">
+        <v>332.5</v>
+      </c>
       <c r="E541" s="18">
         <v>1610</v>
       </c>
@@ -12159,7 +12173,9 @@
       <c r="C542" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D542" s="2"/>
+      <c r="D542" s="2">
+        <v>160</v>
+      </c>
       <c r="E542" s="18">
         <v>1150</v>
       </c>
@@ -12177,7 +12193,9 @@
       <c r="C543" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D543" s="2"/>
+      <c r="D543" s="2">
+        <v>340.5</v>
+      </c>
       <c r="E543" s="18">
         <v>1405</v>
       </c>
@@ -12195,7 +12213,9 @@
       <c r="C544" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D544" s="2"/>
+      <c r="D544" s="2">
+        <v>116</v>
+      </c>
       <c r="E544" s="18">
         <v>1200</v>
       </c>
@@ -12213,7 +12233,9 @@
       <c r="C545" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D545" s="2"/>
+      <c r="D545" s="2">
+        <v>606</v>
+      </c>
       <c r="E545" s="18">
         <v>4252.5</v>
       </c>
@@ -12231,7 +12253,9 @@
       <c r="C546" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D546" s="2"/>
+      <c r="D546" s="2">
+        <v>629.5</v>
+      </c>
       <c r="E546" s="18">
         <v>3780</v>
       </c>
@@ -12249,7 +12273,9 @@
       <c r="C547" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D547" s="2"/>
+      <c r="D547" s="2">
+        <v>441</v>
+      </c>
       <c r="E547" s="18">
         <v>1417.5</v>
       </c>
@@ -12267,7 +12293,9 @@
       <c r="C548" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D548" s="2"/>
+      <c r="D548" s="2">
+        <v>465</v>
+      </c>
       <c r="E548" s="18">
         <v>3900</v>
       </c>
@@ -12285,7 +12313,9 @@
       <c r="C549" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D549" s="2"/>
+      <c r="D549" s="2">
+        <v>323</v>
+      </c>
       <c r="E549" s="18">
         <v>2600</v>
       </c>
@@ -12303,7 +12333,9 @@
       <c r="C550" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D550" s="2"/>
+      <c r="D550" s="2">
+        <v>490</v>
+      </c>
       <c r="E550" s="18">
         <v>1670</v>
       </c>
@@ -12321,7 +12353,9 @@
       <c r="C551" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D551" s="2"/>
+      <c r="D551" s="2">
+        <v>332.5</v>
+      </c>
       <c r="E551" s="18">
         <v>1610</v>
       </c>
@@ -12339,7 +12373,9 @@
       <c r="C552" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D552" s="2"/>
+      <c r="D552" s="2">
+        <v>160</v>
+      </c>
       <c r="E552" s="18">
         <v>1150</v>
       </c>
@@ -12357,7 +12393,9 @@
       <c r="C553" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D553" s="2"/>
+      <c r="D553" s="2">
+        <v>348.5</v>
+      </c>
       <c r="E553" s="18">
         <v>1405</v>
       </c>
@@ -12375,7 +12413,9 @@
       <c r="C554" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D554" s="2"/>
+      <c r="D554" s="2">
+        <v>116</v>
+      </c>
       <c r="E554" s="18">
         <v>1200</v>
       </c>
@@ -19836,7 +19876,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
@@ -20000,7 +20040,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
@@ -20164,7 +20204,7 @@
         <v>2</v>
       </c>
       <c r="F29" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
@@ -20246,7 +20286,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
@@ -20328,7 +20368,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
@@ -20410,7 +20450,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
@@ -20574,7 +20614,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/DASHBOARD-METAS-PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="933" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{305420D5-0247-4563-82A2-525971245A2B}"/>
+  <xr:revisionPtr revIDLastSave="953" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19C13A6B-D556-42D8-BB0D-D9E89697FB1B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Propostas" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dados Diários'!$A$1:$F$764</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dados Diários'!$A$1:$F$754</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Meta de Ritmo'!$B$1:$C$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Metas 100%'!$A$1:$D$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Propostas!$A$1:$A$34</definedName>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2602" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2572" uniqueCount="83">
   <si>
     <t>Cidade</t>
   </si>
@@ -808,7 +808,7 @@
   <sheetPr>
     <tabColor rgb="FF1F4E79"/>
   </sheetPr>
-  <dimension ref="A1:J924"/>
+  <dimension ref="A1:J914"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" style="6" bestFit="1" customWidth="1"/>
@@ -12433,12 +12433,14 @@
       <c r="C555" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D555" s="2"/>
+      <c r="D555" s="2">
+        <v>816</v>
+      </c>
       <c r="E555" s="18">
         <v>4252.5</v>
       </c>
       <c r="F555" s="5">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.25">
@@ -12451,12 +12453,14 @@
       <c r="C556" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D556" s="2"/>
+      <c r="D556" s="2">
+        <v>686.5</v>
+      </c>
       <c r="E556" s="18">
         <v>3780</v>
       </c>
       <c r="F556" s="5">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="557" spans="1:6" x14ac:dyDescent="0.25">
@@ -12469,12 +12473,14 @@
       <c r="C557" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D557" s="2"/>
+      <c r="D557" s="2">
+        <v>480</v>
+      </c>
       <c r="E557" s="18">
         <v>1417.5</v>
       </c>
       <c r="F557" s="5">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="558" spans="1:6" x14ac:dyDescent="0.25">
@@ -12487,12 +12493,14 @@
       <c r="C558" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D558" s="2"/>
+      <c r="D558" s="2">
+        <v>609.5</v>
+      </c>
       <c r="E558" s="18">
         <v>3900</v>
       </c>
       <c r="F558" s="5">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.25">
@@ -12505,12 +12513,14 @@
       <c r="C559" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D559" s="2"/>
+      <c r="D559" s="2">
+        <v>394.5</v>
+      </c>
       <c r="E559" s="18">
         <v>2600</v>
       </c>
       <c r="F559" s="5">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.25">
@@ -12523,12 +12533,14 @@
       <c r="C560" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D560" s="2"/>
+      <c r="D560" s="2">
+        <v>632</v>
+      </c>
       <c r="E560" s="18">
         <v>1670</v>
       </c>
       <c r="F560" s="5">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.25">
@@ -12541,12 +12553,14 @@
       <c r="C561" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D561" s="2"/>
+      <c r="D561" s="2">
+        <v>421.5</v>
+      </c>
       <c r="E561" s="18">
         <v>1610</v>
       </c>
       <c r="F561" s="5">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.25">
@@ -12559,12 +12573,14 @@
       <c r="C562" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D562" s="2"/>
+      <c r="D562" s="2">
+        <v>208</v>
+      </c>
       <c r="E562" s="18">
         <v>1150</v>
       </c>
       <c r="F562" s="5">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.25">
@@ -12577,12 +12593,14 @@
       <c r="C563" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D563" s="2"/>
+      <c r="D563" s="2">
+        <v>477.5</v>
+      </c>
       <c r="E563" s="18">
         <v>1405</v>
       </c>
       <c r="F563" s="5">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.25">
@@ -12595,12 +12613,14 @@
       <c r="C564" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D564" s="2"/>
+      <c r="D564" s="2">
+        <v>116</v>
+      </c>
       <c r="E564" s="18">
         <v>1200</v>
       </c>
       <c r="F564" s="5">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.25">
@@ -12618,7 +12638,7 @@
         <v>4252.5</v>
       </c>
       <c r="F565" s="5">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.25">
@@ -12636,7 +12656,7 @@
         <v>3780</v>
       </c>
       <c r="F566" s="5">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.25">
@@ -12654,7 +12674,7 @@
         <v>1417.5</v>
       </c>
       <c r="F567" s="5">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.25">
@@ -12672,7 +12692,7 @@
         <v>3900</v>
       </c>
       <c r="F568" s="5">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.25">
@@ -12690,7 +12710,7 @@
         <v>2600</v>
       </c>
       <c r="F569" s="5">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.25">
@@ -12708,7 +12728,7 @@
         <v>1670</v>
       </c>
       <c r="F570" s="5">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.25">
@@ -12726,7 +12746,7 @@
         <v>1610</v>
       </c>
       <c r="F571" s="5">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.25">
@@ -12744,7 +12764,7 @@
         <v>1150</v>
       </c>
       <c r="F572" s="5">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.25">
@@ -12762,7 +12782,7 @@
         <v>1405</v>
       </c>
       <c r="F573" s="5">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.25">
@@ -12780,7 +12800,7 @@
         <v>1200</v>
       </c>
       <c r="F574" s="5">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.25">
@@ -12798,7 +12818,7 @@
         <v>4252.5</v>
       </c>
       <c r="F575" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.25">
@@ -12816,7 +12836,7 @@
         <v>3780</v>
       </c>
       <c r="F576" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="577" spans="1:6" x14ac:dyDescent="0.25">
@@ -12834,7 +12854,7 @@
         <v>1417.5</v>
       </c>
       <c r="F577" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="578" spans="1:6" x14ac:dyDescent="0.25">
@@ -12852,7 +12872,7 @@
         <v>3900</v>
       </c>
       <c r="F578" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="579" spans="1:6" x14ac:dyDescent="0.25">
@@ -12870,7 +12890,7 @@
         <v>2600</v>
       </c>
       <c r="F579" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.25">
@@ -12888,7 +12908,7 @@
         <v>1670</v>
       </c>
       <c r="F580" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.25">
@@ -12906,7 +12926,7 @@
         <v>1610</v>
       </c>
       <c r="F581" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="582" spans="1:6" x14ac:dyDescent="0.25">
@@ -12924,7 +12944,7 @@
         <v>1150</v>
       </c>
       <c r="F582" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.25">
@@ -12942,7 +12962,7 @@
         <v>1405</v>
       </c>
       <c r="F583" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="584" spans="1:6" x14ac:dyDescent="0.25">
@@ -12960,7 +12980,7 @@
         <v>1200</v>
       </c>
       <c r="F584" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.25">
@@ -12978,7 +12998,7 @@
         <v>4252.5</v>
       </c>
       <c r="F585" s="5">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="586" spans="1:6" x14ac:dyDescent="0.25">
@@ -12996,7 +13016,7 @@
         <v>3780</v>
       </c>
       <c r="F586" s="5">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="587" spans="1:6" x14ac:dyDescent="0.25">
@@ -13014,7 +13034,7 @@
         <v>1417.5</v>
       </c>
       <c r="F587" s="5">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="588" spans="1:6" x14ac:dyDescent="0.25">
@@ -13032,7 +13052,7 @@
         <v>3900</v>
       </c>
       <c r="F588" s="5">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="589" spans="1:6" x14ac:dyDescent="0.25">
@@ -13050,7 +13070,7 @@
         <v>2600</v>
       </c>
       <c r="F589" s="5">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="590" spans="1:6" x14ac:dyDescent="0.25">
@@ -13068,7 +13088,7 @@
         <v>1670</v>
       </c>
       <c r="F590" s="5">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="591" spans="1:6" x14ac:dyDescent="0.25">
@@ -13086,7 +13106,7 @@
         <v>1610</v>
       </c>
       <c r="F591" s="5">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="592" spans="1:6" x14ac:dyDescent="0.25">
@@ -13104,7 +13124,7 @@
         <v>1150</v>
       </c>
       <c r="F592" s="5">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="593" spans="1:6" x14ac:dyDescent="0.25">
@@ -13122,7 +13142,7 @@
         <v>1405</v>
       </c>
       <c r="F593" s="5">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="594" spans="1:6" x14ac:dyDescent="0.25">
@@ -13140,7 +13160,7 @@
         <v>1200</v>
       </c>
       <c r="F594" s="5">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.25">
@@ -13158,7 +13178,7 @@
         <v>4252.5</v>
       </c>
       <c r="F595" s="5">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="596" spans="1:6" x14ac:dyDescent="0.25">
@@ -13176,7 +13196,7 @@
         <v>3780</v>
       </c>
       <c r="F596" s="5">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.25">
@@ -13194,7 +13214,7 @@
         <v>1417.5</v>
       </c>
       <c r="F597" s="5">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="598" spans="1:6" x14ac:dyDescent="0.25">
@@ -13212,7 +13232,7 @@
         <v>3900</v>
       </c>
       <c r="F598" s="5">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.25">
@@ -13230,7 +13250,7 @@
         <v>2600</v>
       </c>
       <c r="F599" s="5">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.25">
@@ -13248,7 +13268,7 @@
         <v>1670</v>
       </c>
       <c r="F600" s="5">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="601" spans="1:6" x14ac:dyDescent="0.25">
@@ -13266,7 +13286,7 @@
         <v>1610</v>
       </c>
       <c r="F601" s="5">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="602" spans="1:6" x14ac:dyDescent="0.25">
@@ -13284,7 +13304,7 @@
         <v>1150</v>
       </c>
       <c r="F602" s="5">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="603" spans="1:6" x14ac:dyDescent="0.25">
@@ -13302,7 +13322,7 @@
         <v>1405</v>
       </c>
       <c r="F603" s="5">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="604" spans="1:6" x14ac:dyDescent="0.25">
@@ -13320,7 +13340,7 @@
         <v>1200</v>
       </c>
       <c r="F604" s="5">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="605" spans="1:6" x14ac:dyDescent="0.25">
@@ -13338,7 +13358,7 @@
         <v>4252.5</v>
       </c>
       <c r="F605" s="5">
-        <v>46277</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="606" spans="1:6" x14ac:dyDescent="0.25">
@@ -13356,7 +13376,7 @@
         <v>3780</v>
       </c>
       <c r="F606" s="5">
-        <v>46277</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="607" spans="1:6" x14ac:dyDescent="0.25">
@@ -13374,7 +13394,7 @@
         <v>1417.5</v>
       </c>
       <c r="F607" s="5">
-        <v>46277</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="608" spans="1:6" x14ac:dyDescent="0.25">
@@ -13392,7 +13412,7 @@
         <v>3900</v>
       </c>
       <c r="F608" s="5">
-        <v>46277</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="609" spans="1:6" x14ac:dyDescent="0.25">
@@ -13410,7 +13430,7 @@
         <v>2600</v>
       </c>
       <c r="F609" s="5">
-        <v>46277</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="610" spans="1:6" x14ac:dyDescent="0.25">
@@ -13428,7 +13448,7 @@
         <v>1670</v>
       </c>
       <c r="F610" s="5">
-        <v>46277</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="611" spans="1:6" x14ac:dyDescent="0.25">
@@ -13446,7 +13466,7 @@
         <v>1610</v>
       </c>
       <c r="F611" s="5">
-        <v>46277</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="612" spans="1:6" x14ac:dyDescent="0.25">
@@ -13464,7 +13484,7 @@
         <v>1150</v>
       </c>
       <c r="F612" s="5">
-        <v>46277</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="613" spans="1:6" x14ac:dyDescent="0.25">
@@ -13482,7 +13502,7 @@
         <v>1405</v>
       </c>
       <c r="F613" s="5">
-        <v>46277</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="614" spans="1:6" x14ac:dyDescent="0.25">
@@ -13500,7 +13520,7 @@
         <v>1200</v>
       </c>
       <c r="F614" s="5">
-        <v>46277</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="615" spans="1:6" x14ac:dyDescent="0.25">
@@ -13518,7 +13538,7 @@
         <v>4252.5</v>
       </c>
       <c r="F615" s="5">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="616" spans="1:6" x14ac:dyDescent="0.25">
@@ -13536,7 +13556,7 @@
         <v>3780</v>
       </c>
       <c r="F616" s="5">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.25">
@@ -13554,7 +13574,7 @@
         <v>1417.5</v>
       </c>
       <c r="F617" s="5">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.25">
@@ -13572,7 +13592,7 @@
         <v>3900</v>
       </c>
       <c r="F618" s="5">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.25">
@@ -13590,7 +13610,7 @@
         <v>2600</v>
       </c>
       <c r="F619" s="5">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="620" spans="1:6" x14ac:dyDescent="0.25">
@@ -13608,7 +13628,7 @@
         <v>1670</v>
       </c>
       <c r="F620" s="5">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.25">
@@ -13626,7 +13646,7 @@
         <v>1610</v>
       </c>
       <c r="F621" s="5">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="622" spans="1:6" x14ac:dyDescent="0.25">
@@ -13644,7 +13664,7 @@
         <v>1150</v>
       </c>
       <c r="F622" s="5">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="623" spans="1:6" x14ac:dyDescent="0.25">
@@ -13662,7 +13682,7 @@
         <v>1405</v>
       </c>
       <c r="F623" s="5">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="624" spans="1:6" x14ac:dyDescent="0.25">
@@ -13680,7 +13700,7 @@
         <v>1200</v>
       </c>
       <c r="F624" s="5">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="625" spans="1:6" x14ac:dyDescent="0.25">
@@ -13698,7 +13718,7 @@
         <v>4252.5</v>
       </c>
       <c r="F625" s="5">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="626" spans="1:6" x14ac:dyDescent="0.25">
@@ -13716,7 +13736,7 @@
         <v>3780</v>
       </c>
       <c r="F626" s="5">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="627" spans="1:6" x14ac:dyDescent="0.25">
@@ -13734,7 +13754,7 @@
         <v>1417.5</v>
       </c>
       <c r="F627" s="5">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="628" spans="1:6" x14ac:dyDescent="0.25">
@@ -13752,7 +13772,7 @@
         <v>3900</v>
       </c>
       <c r="F628" s="5">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="629" spans="1:6" x14ac:dyDescent="0.25">
@@ -13770,7 +13790,7 @@
         <v>2600</v>
       </c>
       <c r="F629" s="5">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="630" spans="1:6" x14ac:dyDescent="0.25">
@@ -13788,7 +13808,7 @@
         <v>1670</v>
       </c>
       <c r="F630" s="5">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="631" spans="1:6" x14ac:dyDescent="0.25">
@@ -13806,7 +13826,7 @@
         <v>1610</v>
       </c>
       <c r="F631" s="5">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="632" spans="1:6" x14ac:dyDescent="0.25">
@@ -13824,7 +13844,7 @@
         <v>1150</v>
       </c>
       <c r="F632" s="5">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="633" spans="1:6" x14ac:dyDescent="0.25">
@@ -13842,7 +13862,7 @@
         <v>1405</v>
       </c>
       <c r="F633" s="5">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="634" spans="1:6" x14ac:dyDescent="0.25">
@@ -13860,7 +13880,7 @@
         <v>1200</v>
       </c>
       <c r="F634" s="5">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="635" spans="1:6" x14ac:dyDescent="0.25">
@@ -13878,7 +13898,7 @@
         <v>4252.5</v>
       </c>
       <c r="F635" s="5">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="636" spans="1:6" x14ac:dyDescent="0.25">
@@ -13896,7 +13916,7 @@
         <v>3780</v>
       </c>
       <c r="F636" s="5">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="637" spans="1:6" x14ac:dyDescent="0.25">
@@ -13914,7 +13934,7 @@
         <v>1417.5</v>
       </c>
       <c r="F637" s="5">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="638" spans="1:6" x14ac:dyDescent="0.25">
@@ -13932,7 +13952,7 @@
         <v>3900</v>
       </c>
       <c r="F638" s="5">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="639" spans="1:6" x14ac:dyDescent="0.25">
@@ -13950,7 +13970,7 @@
         <v>2600</v>
       </c>
       <c r="F639" s="5">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="640" spans="1:6" x14ac:dyDescent="0.25">
@@ -13968,7 +13988,7 @@
         <v>1670</v>
       </c>
       <c r="F640" s="5">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="641" spans="1:6" x14ac:dyDescent="0.25">
@@ -13986,7 +14006,7 @@
         <v>1610</v>
       </c>
       <c r="F641" s="5">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="642" spans="1:6" x14ac:dyDescent="0.25">
@@ -14004,7 +14024,7 @@
         <v>1150</v>
       </c>
       <c r="F642" s="5">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="643" spans="1:6" x14ac:dyDescent="0.25">
@@ -14022,7 +14042,7 @@
         <v>1405</v>
       </c>
       <c r="F643" s="5">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="644" spans="1:6" x14ac:dyDescent="0.25">
@@ -14040,7 +14060,7 @@
         <v>1200</v>
       </c>
       <c r="F644" s="5">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="645" spans="1:6" x14ac:dyDescent="0.25">
@@ -14058,7 +14078,7 @@
         <v>4252.5</v>
       </c>
       <c r="F645" s="5">
-        <v>46282</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="646" spans="1:6" x14ac:dyDescent="0.25">
@@ -14076,7 +14096,7 @@
         <v>3780</v>
       </c>
       <c r="F646" s="5">
-        <v>46282</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="647" spans="1:6" x14ac:dyDescent="0.25">
@@ -14094,7 +14114,7 @@
         <v>1417.5</v>
       </c>
       <c r="F647" s="5">
-        <v>46282</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="648" spans="1:6" x14ac:dyDescent="0.25">
@@ -14112,7 +14132,7 @@
         <v>3900</v>
       </c>
       <c r="F648" s="5">
-        <v>46282</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.25">
@@ -14130,7 +14150,7 @@
         <v>2600</v>
       </c>
       <c r="F649" s="5">
-        <v>46282</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="650" spans="1:6" x14ac:dyDescent="0.25">
@@ -14148,7 +14168,7 @@
         <v>1670</v>
       </c>
       <c r="F650" s="5">
-        <v>46282</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.25">
@@ -14166,7 +14186,7 @@
         <v>1610</v>
       </c>
       <c r="F651" s="5">
-        <v>46282</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="652" spans="1:6" x14ac:dyDescent="0.25">
@@ -14184,7 +14204,7 @@
         <v>1150</v>
       </c>
       <c r="F652" s="5">
-        <v>46282</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="653" spans="1:6" x14ac:dyDescent="0.25">
@@ -14202,7 +14222,7 @@
         <v>1405</v>
       </c>
       <c r="F653" s="5">
-        <v>46282</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="654" spans="1:6" x14ac:dyDescent="0.25">
@@ -14220,7 +14240,7 @@
         <v>1200</v>
       </c>
       <c r="F654" s="5">
-        <v>46282</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="655" spans="1:6" x14ac:dyDescent="0.25">
@@ -14238,7 +14258,7 @@
         <v>4252.5</v>
       </c>
       <c r="F655" s="5">
-        <v>46283</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="656" spans="1:6" x14ac:dyDescent="0.25">
@@ -14256,7 +14276,7 @@
         <v>3780</v>
       </c>
       <c r="F656" s="5">
-        <v>46283</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="657" spans="1:6" x14ac:dyDescent="0.25">
@@ -14274,7 +14294,7 @@
         <v>1417.5</v>
       </c>
       <c r="F657" s="5">
-        <v>46283</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="658" spans="1:6" x14ac:dyDescent="0.25">
@@ -14292,7 +14312,7 @@
         <v>3900</v>
       </c>
       <c r="F658" s="5">
-        <v>46283</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="659" spans="1:6" x14ac:dyDescent="0.25">
@@ -14310,7 +14330,7 @@
         <v>2600</v>
       </c>
       <c r="F659" s="5">
-        <v>46283</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="660" spans="1:6" x14ac:dyDescent="0.25">
@@ -14328,7 +14348,7 @@
         <v>1670</v>
       </c>
       <c r="F660" s="5">
-        <v>46283</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="661" spans="1:6" x14ac:dyDescent="0.25">
@@ -14346,7 +14366,7 @@
         <v>1610</v>
       </c>
       <c r="F661" s="5">
-        <v>46283</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="662" spans="1:6" x14ac:dyDescent="0.25">
@@ -14364,7 +14384,7 @@
         <v>1150</v>
       </c>
       <c r="F662" s="5">
-        <v>46283</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="663" spans="1:6" x14ac:dyDescent="0.25">
@@ -14382,7 +14402,7 @@
         <v>1405</v>
       </c>
       <c r="F663" s="5">
-        <v>46283</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="664" spans="1:6" x14ac:dyDescent="0.25">
@@ -14400,7 +14420,7 @@
         <v>1200</v>
       </c>
       <c r="F664" s="5">
-        <v>46283</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="665" spans="1:6" x14ac:dyDescent="0.25">
@@ -14418,7 +14438,7 @@
         <v>4252.5</v>
       </c>
       <c r="F665" s="5">
-        <v>46284</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="666" spans="1:6" x14ac:dyDescent="0.25">
@@ -14436,7 +14456,7 @@
         <v>3780</v>
       </c>
       <c r="F666" s="5">
-        <v>46284</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="667" spans="1:6" x14ac:dyDescent="0.25">
@@ -14454,7 +14474,7 @@
         <v>1417.5</v>
       </c>
       <c r="F667" s="5">
-        <v>46284</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="668" spans="1:6" x14ac:dyDescent="0.25">
@@ -14472,7 +14492,7 @@
         <v>3900</v>
       </c>
       <c r="F668" s="5">
-        <v>46284</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.25">
@@ -14490,7 +14510,7 @@
         <v>2600</v>
       </c>
       <c r="F669" s="5">
-        <v>46284</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="670" spans="1:6" x14ac:dyDescent="0.25">
@@ -14508,7 +14528,7 @@
         <v>1670</v>
       </c>
       <c r="F670" s="5">
-        <v>46284</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.25">
@@ -14526,7 +14546,7 @@
         <v>1610</v>
       </c>
       <c r="F671" s="5">
-        <v>46284</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="672" spans="1:6" x14ac:dyDescent="0.25">
@@ -14544,7 +14564,7 @@
         <v>1150</v>
       </c>
       <c r="F672" s="5">
-        <v>46284</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.25">
@@ -14562,7 +14582,7 @@
         <v>1405</v>
       </c>
       <c r="F673" s="5">
-        <v>46284</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="674" spans="1:6" x14ac:dyDescent="0.25">
@@ -14580,7 +14600,7 @@
         <v>1200</v>
       </c>
       <c r="F674" s="5">
-        <v>46284</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.25">
@@ -14598,7 +14618,7 @@
         <v>4252.5</v>
       </c>
       <c r="F675" s="5">
-        <v>46286</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="676" spans="1:6" x14ac:dyDescent="0.25">
@@ -14616,7 +14636,7 @@
         <v>3780</v>
       </c>
       <c r="F676" s="5">
-        <v>46286</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="677" spans="1:6" x14ac:dyDescent="0.25">
@@ -14634,7 +14654,7 @@
         <v>1417.5</v>
       </c>
       <c r="F677" s="5">
-        <v>46286</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="678" spans="1:6" x14ac:dyDescent="0.25">
@@ -14652,7 +14672,7 @@
         <v>3900</v>
       </c>
       <c r="F678" s="5">
-        <v>46286</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="679" spans="1:6" x14ac:dyDescent="0.25">
@@ -14670,7 +14690,7 @@
         <v>2600</v>
       </c>
       <c r="F679" s="5">
-        <v>46286</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="680" spans="1:6" x14ac:dyDescent="0.25">
@@ -14688,7 +14708,7 @@
         <v>1670</v>
       </c>
       <c r="F680" s="5">
-        <v>46286</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="681" spans="1:6" x14ac:dyDescent="0.25">
@@ -14706,7 +14726,7 @@
         <v>1610</v>
       </c>
       <c r="F681" s="5">
-        <v>46286</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="682" spans="1:6" x14ac:dyDescent="0.25">
@@ -14724,7 +14744,7 @@
         <v>1150</v>
       </c>
       <c r="F682" s="5">
-        <v>46286</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="683" spans="1:6" x14ac:dyDescent="0.25">
@@ -14742,7 +14762,7 @@
         <v>1405</v>
       </c>
       <c r="F683" s="5">
-        <v>46286</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="684" spans="1:6" x14ac:dyDescent="0.25">
@@ -14760,7 +14780,7 @@
         <v>1200</v>
       </c>
       <c r="F684" s="5">
-        <v>46286</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="685" spans="1:6" x14ac:dyDescent="0.25">
@@ -14778,7 +14798,7 @@
         <v>4252.5</v>
       </c>
       <c r="F685" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="686" spans="1:6" x14ac:dyDescent="0.25">
@@ -14796,7 +14816,7 @@
         <v>3780</v>
       </c>
       <c r="F686" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="687" spans="1:6" x14ac:dyDescent="0.25">
@@ -14814,7 +14834,7 @@
         <v>1417.5</v>
       </c>
       <c r="F687" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="688" spans="1:6" x14ac:dyDescent="0.25">
@@ -14832,7 +14852,7 @@
         <v>3900</v>
       </c>
       <c r="F688" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="689" spans="1:6" x14ac:dyDescent="0.25">
@@ -14850,7 +14870,7 @@
         <v>2600</v>
       </c>
       <c r="F689" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="690" spans="1:6" x14ac:dyDescent="0.25">
@@ -14868,7 +14888,7 @@
         <v>1670</v>
       </c>
       <c r="F690" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="691" spans="1:6" x14ac:dyDescent="0.25">
@@ -14886,7 +14906,7 @@
         <v>1610</v>
       </c>
       <c r="F691" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="692" spans="1:6" x14ac:dyDescent="0.25">
@@ -14904,7 +14924,7 @@
         <v>1150</v>
       </c>
       <c r="F692" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="693" spans="1:6" x14ac:dyDescent="0.25">
@@ -14922,7 +14942,7 @@
         <v>1405</v>
       </c>
       <c r="F693" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="694" spans="1:6" x14ac:dyDescent="0.25">
@@ -14940,7 +14960,7 @@
         <v>1200</v>
       </c>
       <c r="F694" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="695" spans="1:6" x14ac:dyDescent="0.25">
@@ -14958,7 +14978,7 @@
         <v>4252.5</v>
       </c>
       <c r="F695" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="696" spans="1:6" x14ac:dyDescent="0.25">
@@ -14976,7 +14996,7 @@
         <v>3780</v>
       </c>
       <c r="F696" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="697" spans="1:6" x14ac:dyDescent="0.25">
@@ -14994,7 +15014,7 @@
         <v>1417.5</v>
       </c>
       <c r="F697" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="698" spans="1:6" x14ac:dyDescent="0.25">
@@ -15012,7 +15032,7 @@
         <v>3900</v>
       </c>
       <c r="F698" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="699" spans="1:6" x14ac:dyDescent="0.25">
@@ -15030,7 +15050,7 @@
         <v>2600</v>
       </c>
       <c r="F699" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="700" spans="1:6" x14ac:dyDescent="0.25">
@@ -15048,7 +15068,7 @@
         <v>1670</v>
       </c>
       <c r="F700" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="701" spans="1:6" x14ac:dyDescent="0.25">
@@ -15066,7 +15086,7 @@
         <v>1610</v>
       </c>
       <c r="F701" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="702" spans="1:6" x14ac:dyDescent="0.25">
@@ -15084,7 +15104,7 @@
         <v>1150</v>
       </c>
       <c r="F702" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="703" spans="1:6" x14ac:dyDescent="0.25">
@@ -15102,7 +15122,7 @@
         <v>1405</v>
       </c>
       <c r="F703" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="704" spans="1:6" x14ac:dyDescent="0.25">
@@ -15120,7 +15140,7 @@
         <v>1200</v>
       </c>
       <c r="F704" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="705" spans="1:6" x14ac:dyDescent="0.25">
@@ -15138,7 +15158,7 @@
         <v>4252.5</v>
       </c>
       <c r="F705" s="5">
-        <v>46289</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="706" spans="1:6" x14ac:dyDescent="0.25">
@@ -15156,7 +15176,7 @@
         <v>3780</v>
       </c>
       <c r="F706" s="5">
-        <v>46289</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="707" spans="1:6" x14ac:dyDescent="0.25">
@@ -15174,7 +15194,7 @@
         <v>1417.5</v>
       </c>
       <c r="F707" s="5">
-        <v>46289</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="708" spans="1:6" x14ac:dyDescent="0.25">
@@ -15192,7 +15212,7 @@
         <v>3900</v>
       </c>
       <c r="F708" s="5">
-        <v>46289</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="709" spans="1:6" x14ac:dyDescent="0.25">
@@ -15210,7 +15230,7 @@
         <v>2600</v>
       </c>
       <c r="F709" s="5">
-        <v>46289</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="710" spans="1:6" x14ac:dyDescent="0.25">
@@ -15228,7 +15248,7 @@
         <v>1670</v>
       </c>
       <c r="F710" s="5">
-        <v>46289</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="711" spans="1:6" x14ac:dyDescent="0.25">
@@ -15246,7 +15266,7 @@
         <v>1610</v>
       </c>
       <c r="F711" s="5">
-        <v>46289</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="712" spans="1:6" x14ac:dyDescent="0.25">
@@ -15264,7 +15284,7 @@
         <v>1150</v>
       </c>
       <c r="F712" s="5">
-        <v>46289</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="713" spans="1:6" x14ac:dyDescent="0.25">
@@ -15282,7 +15302,7 @@
         <v>1405</v>
       </c>
       <c r="F713" s="5">
-        <v>46289</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="714" spans="1:6" x14ac:dyDescent="0.25">
@@ -15300,7 +15320,7 @@
         <v>1200</v>
       </c>
       <c r="F714" s="5">
-        <v>46289</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="715" spans="1:6" x14ac:dyDescent="0.25">
@@ -15318,7 +15338,7 @@
         <v>4252.5</v>
       </c>
       <c r="F715" s="5">
-        <v>46290</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="716" spans="1:6" x14ac:dyDescent="0.25">
@@ -15336,7 +15356,7 @@
         <v>3780</v>
       </c>
       <c r="F716" s="5">
-        <v>46290</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="717" spans="1:6" x14ac:dyDescent="0.25">
@@ -15354,7 +15374,7 @@
         <v>1417.5</v>
       </c>
       <c r="F717" s="5">
-        <v>46290</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="718" spans="1:6" x14ac:dyDescent="0.25">
@@ -15372,7 +15392,7 @@
         <v>3900</v>
       </c>
       <c r="F718" s="5">
-        <v>46290</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="719" spans="1:6" x14ac:dyDescent="0.25">
@@ -15390,7 +15410,7 @@
         <v>2600</v>
       </c>
       <c r="F719" s="5">
-        <v>46290</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="720" spans="1:6" x14ac:dyDescent="0.25">
@@ -15408,7 +15428,7 @@
         <v>1670</v>
       </c>
       <c r="F720" s="5">
-        <v>46290</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="721" spans="1:6" x14ac:dyDescent="0.25">
@@ -15426,7 +15446,7 @@
         <v>1610</v>
       </c>
       <c r="F721" s="5">
-        <v>46290</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="722" spans="1:6" x14ac:dyDescent="0.25">
@@ -15444,7 +15464,7 @@
         <v>1150</v>
       </c>
       <c r="F722" s="5">
-        <v>46290</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="723" spans="1:6" x14ac:dyDescent="0.25">
@@ -15462,7 +15482,7 @@
         <v>1405</v>
       </c>
       <c r="F723" s="5">
-        <v>46290</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="724" spans="1:6" x14ac:dyDescent="0.25">
@@ -15480,7 +15500,7 @@
         <v>1200</v>
       </c>
       <c r="F724" s="5">
-        <v>46290</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="725" spans="1:6" x14ac:dyDescent="0.25">
@@ -15498,7 +15518,7 @@
         <v>4252.5</v>
       </c>
       <c r="F725" s="5">
-        <v>46291</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="726" spans="1:6" x14ac:dyDescent="0.25">
@@ -15516,7 +15536,7 @@
         <v>3780</v>
       </c>
       <c r="F726" s="5">
-        <v>46291</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="727" spans="1:6" x14ac:dyDescent="0.25">
@@ -15534,7 +15554,7 @@
         <v>1417.5</v>
       </c>
       <c r="F727" s="5">
-        <v>46291</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="728" spans="1:6" x14ac:dyDescent="0.25">
@@ -15552,7 +15572,7 @@
         <v>3900</v>
       </c>
       <c r="F728" s="5">
-        <v>46291</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="729" spans="1:6" x14ac:dyDescent="0.25">
@@ -15570,7 +15590,7 @@
         <v>2600</v>
       </c>
       <c r="F729" s="5">
-        <v>46291</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="730" spans="1:6" x14ac:dyDescent="0.25">
@@ -15588,7 +15608,7 @@
         <v>1670</v>
       </c>
       <c r="F730" s="5">
-        <v>46291</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="731" spans="1:6" x14ac:dyDescent="0.25">
@@ -15606,7 +15626,7 @@
         <v>1610</v>
       </c>
       <c r="F731" s="5">
-        <v>46291</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="732" spans="1:6" x14ac:dyDescent="0.25">
@@ -15624,7 +15644,7 @@
         <v>1150</v>
       </c>
       <c r="F732" s="5">
-        <v>46291</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="733" spans="1:6" x14ac:dyDescent="0.25">
@@ -15642,7 +15662,7 @@
         <v>1405</v>
       </c>
       <c r="F733" s="5">
-        <v>46291</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="734" spans="1:6" x14ac:dyDescent="0.25">
@@ -15660,7 +15680,7 @@
         <v>1200</v>
       </c>
       <c r="F734" s="5">
-        <v>46291</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="735" spans="1:6" x14ac:dyDescent="0.25">
@@ -15678,7 +15698,7 @@
         <v>4252.5</v>
       </c>
       <c r="F735" s="5">
-        <v>46293</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="736" spans="1:6" x14ac:dyDescent="0.25">
@@ -15696,7 +15716,7 @@
         <v>3780</v>
       </c>
       <c r="F736" s="5">
-        <v>46293</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="737" spans="1:6" x14ac:dyDescent="0.25">
@@ -15714,7 +15734,7 @@
         <v>1417.5</v>
       </c>
       <c r="F737" s="5">
-        <v>46293</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="738" spans="1:6" x14ac:dyDescent="0.25">
@@ -15732,7 +15752,7 @@
         <v>3900</v>
       </c>
       <c r="F738" s="5">
-        <v>46293</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="739" spans="1:6" x14ac:dyDescent="0.25">
@@ -15750,7 +15770,7 @@
         <v>2600</v>
       </c>
       <c r="F739" s="5">
-        <v>46293</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="740" spans="1:6" x14ac:dyDescent="0.25">
@@ -15768,7 +15788,7 @@
         <v>1670</v>
       </c>
       <c r="F740" s="5">
-        <v>46293</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="741" spans="1:6" x14ac:dyDescent="0.25">
@@ -15786,7 +15806,7 @@
         <v>1610</v>
       </c>
       <c r="F741" s="5">
-        <v>46293</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="742" spans="1:6" x14ac:dyDescent="0.25">
@@ -15804,7 +15824,7 @@
         <v>1150</v>
       </c>
       <c r="F742" s="5">
-        <v>46293</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="743" spans="1:6" x14ac:dyDescent="0.25">
@@ -15822,7 +15842,7 @@
         <v>1405</v>
       </c>
       <c r="F743" s="5">
-        <v>46293</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="744" spans="1:6" x14ac:dyDescent="0.25">
@@ -15840,7 +15860,7 @@
         <v>1200</v>
       </c>
       <c r="F744" s="5">
-        <v>46293</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="745" spans="1:6" x14ac:dyDescent="0.25">
@@ -15858,7 +15878,7 @@
         <v>4252.5</v>
       </c>
       <c r="F745" s="5">
-        <v>46294</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="746" spans="1:6" x14ac:dyDescent="0.25">
@@ -15876,7 +15896,7 @@
         <v>3780</v>
       </c>
       <c r="F746" s="5">
-        <v>46294</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="747" spans="1:6" x14ac:dyDescent="0.25">
@@ -15894,7 +15914,7 @@
         <v>1417.5</v>
       </c>
       <c r="F747" s="5">
-        <v>46294</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="748" spans="1:6" x14ac:dyDescent="0.25">
@@ -15912,7 +15932,7 @@
         <v>3900</v>
       </c>
       <c r="F748" s="5">
-        <v>46294</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="749" spans="1:6" x14ac:dyDescent="0.25">
@@ -15930,7 +15950,7 @@
         <v>2600</v>
       </c>
       <c r="F749" s="5">
-        <v>46294</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="750" spans="1:6" x14ac:dyDescent="0.25">
@@ -15948,7 +15968,7 @@
         <v>1670</v>
       </c>
       <c r="F750" s="5">
-        <v>46294</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="751" spans="1:6" x14ac:dyDescent="0.25">
@@ -15966,7 +15986,7 @@
         <v>1610</v>
       </c>
       <c r="F751" s="5">
-        <v>46294</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="752" spans="1:6" x14ac:dyDescent="0.25">
@@ -15984,7 +16004,7 @@
         <v>1150</v>
       </c>
       <c r="F752" s="5">
-        <v>46294</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="753" spans="1:6" x14ac:dyDescent="0.25">
@@ -16002,7 +16022,7 @@
         <v>1405</v>
       </c>
       <c r="F753" s="5">
-        <v>46294</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="754" spans="1:6" x14ac:dyDescent="0.25">
@@ -16020,188 +16040,38 @@
         <v>1200</v>
       </c>
       <c r="F754" s="5">
-        <v>46294</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="755" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A755" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B755" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C755" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D755" s="2"/>
-      <c r="E755" s="18">
-        <v>4252.5</v>
-      </c>
-      <c r="F755" s="5">
-        <v>46295</v>
-      </c>
+      <c r="E755" s="18"/>
     </row>
     <row r="756" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A756" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B756" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C756" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D756" s="2"/>
-      <c r="E756" s="18">
-        <v>3780</v>
-      </c>
-      <c r="F756" s="5">
-        <v>46295</v>
-      </c>
+      <c r="E756" s="18"/>
     </row>
     <row r="757" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A757" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B757" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C757" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D757" s="2"/>
-      <c r="E757" s="18">
-        <v>1417.5</v>
-      </c>
-      <c r="F757" s="5">
-        <v>46295</v>
-      </c>
+      <c r="E757" s="18"/>
     </row>
     <row r="758" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A758" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B758" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C758" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D758" s="2"/>
-      <c r="E758" s="18">
-        <v>3900</v>
-      </c>
-      <c r="F758" s="5">
-        <v>46295</v>
-      </c>
+      <c r="E758" s="18"/>
     </row>
     <row r="759" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A759" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B759" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C759" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D759" s="2"/>
-      <c r="E759" s="18">
-        <v>2600</v>
-      </c>
-      <c r="F759" s="5">
-        <v>46295</v>
-      </c>
+      <c r="E759" s="18"/>
     </row>
     <row r="760" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A760" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B760" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C760" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D760" s="2"/>
-      <c r="E760" s="18">
-        <v>1670</v>
-      </c>
-      <c r="F760" s="5">
-        <v>46295</v>
-      </c>
+      <c r="E760" s="18"/>
     </row>
     <row r="761" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A761" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B761" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C761" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D761" s="2"/>
-      <c r="E761" s="18">
-        <v>1610</v>
-      </c>
-      <c r="F761" s="5">
-        <v>46295</v>
-      </c>
+      <c r="E761" s="18"/>
     </row>
     <row r="762" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A762" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B762" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C762" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D762" s="2"/>
-      <c r="E762" s="18">
-        <v>1150</v>
-      </c>
-      <c r="F762" s="5">
-        <v>46295</v>
-      </c>
+      <c r="E762" s="18"/>
     </row>
     <row r="763" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A763" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B763" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C763" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D763" s="2"/>
-      <c r="E763" s="18">
-        <v>1405</v>
-      </c>
-      <c r="F763" s="5">
-        <v>46295</v>
-      </c>
+      <c r="E763" s="18"/>
     </row>
     <row r="764" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A764" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B764" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C764" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D764" s="2"/>
-      <c r="E764" s="18">
-        <v>1200</v>
-      </c>
-      <c r="F764" s="5">
-        <v>46295</v>
-      </c>
+      <c r="E764" s="18"/>
     </row>
     <row r="765" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E765" s="18"/>
@@ -16653,38 +16523,8 @@
     <row r="914" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E914" s="18"/>
     </row>
-    <row r="915" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E915" s="18"/>
-    </row>
-    <row r="916" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E916" s="18"/>
-    </row>
-    <row r="917" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E917" s="18"/>
-    </row>
-    <row r="918" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E918" s="18"/>
-    </row>
-    <row r="919" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E919" s="18"/>
-    </row>
-    <row r="920" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E920" s="18"/>
-    </row>
-    <row r="921" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E921" s="18"/>
-    </row>
-    <row r="922" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E922" s="18"/>
-    </row>
-    <row r="923" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E923" s="18"/>
-    </row>
-    <row r="924" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E924" s="18"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F764" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F754" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19785,7 +19625,7 @@
       <c r="H24" s="14">
         <v>46271</v>
       </c>
-      <c r="I24" s="13">
+      <c r="I24" s="14">
         <v>46272</v>
       </c>
       <c r="J24" s="13">
@@ -19880,11 +19720,9 @@
       </c>
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
-      <c r="I25" s="8">
-        <v>0</v>
-      </c>
+      <c r="I25" s="8"/>
       <c r="J25" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K25" s="8">
         <v>0</v>
@@ -19962,9 +19800,7 @@
       </c>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
-      <c r="I26" s="8">
-        <v>0</v>
-      </c>
+      <c r="I26" s="8"/>
       <c r="J26" s="8">
         <v>0</v>
       </c>
@@ -20044,9 +19880,7 @@
       </c>
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
-      <c r="I27" s="8">
-        <v>0</v>
-      </c>
+      <c r="I27" s="8"/>
       <c r="J27" s="8">
         <v>0</v>
       </c>
@@ -20126,11 +19960,9 @@
       </c>
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
-      <c r="I28" s="8">
-        <v>0</v>
-      </c>
+      <c r="I28" s="8"/>
       <c r="J28" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" s="8">
         <v>0</v>
@@ -20208,9 +20040,7 @@
       </c>
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
-      <c r="I29" s="8">
-        <v>0</v>
-      </c>
+      <c r="I29" s="8"/>
       <c r="J29" s="8">
         <v>0</v>
       </c>
@@ -20290,11 +20120,9 @@
       </c>
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
-      <c r="I30" s="8">
-        <v>0</v>
-      </c>
+      <c r="I30" s="8"/>
       <c r="J30" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" s="8">
         <v>0</v>
@@ -20372,9 +20200,7 @@
       </c>
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
-      <c r="I31" s="8">
-        <v>0</v>
-      </c>
+      <c r="I31" s="8"/>
       <c r="J31" s="8">
         <v>0</v>
       </c>
@@ -20454,9 +20280,7 @@
       </c>
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
-      <c r="I32" s="8">
-        <v>0</v>
-      </c>
+      <c r="I32" s="8"/>
       <c r="J32" s="8">
         <v>0</v>
       </c>
@@ -20536,11 +20360,9 @@
       </c>
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
-      <c r="I33" s="8">
-        <v>0</v>
-      </c>
+      <c r="I33" s="8"/>
       <c r="J33" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" s="8">
         <v>0</v>
@@ -20618,11 +20440,9 @@
       </c>
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
-      <c r="I34" s="8">
-        <v>0</v>
-      </c>
+      <c r="I34" s="8"/>
       <c r="J34" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" s="8">
         <v>0</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/DASHBOARD-METAS-PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="953" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19C13A6B-D556-42D8-BB0D-D9E89697FB1B}"/>
+  <xr:revisionPtr revIDLastSave="970" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AAC1ACB-C450-42BD-80CB-CB7ED84CBF1D}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -12633,7 +12633,9 @@
       <c r="C565" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D565" s="2"/>
+      <c r="D565" s="2">
+        <v>892.5</v>
+      </c>
       <c r="E565" s="18">
         <v>4252.5</v>
       </c>
@@ -12651,7 +12653,9 @@
       <c r="C566" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D566" s="2"/>
+      <c r="D566" s="2">
+        <v>839.5</v>
+      </c>
       <c r="E566" s="18">
         <v>3780</v>
       </c>
@@ -12669,7 +12673,9 @@
       <c r="C567" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D567" s="2"/>
+      <c r="D567" s="2">
+        <v>624.5</v>
+      </c>
       <c r="E567" s="18">
         <v>1417.5</v>
       </c>
@@ -12687,7 +12693,9 @@
       <c r="C568" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D568" s="2"/>
+      <c r="D568" s="2">
+        <v>711</v>
+      </c>
       <c r="E568" s="18">
         <v>3900</v>
       </c>
@@ -12705,7 +12713,9 @@
       <c r="C569" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D569" s="2"/>
+      <c r="D569" s="2">
+        <v>436.5</v>
+      </c>
       <c r="E569" s="18">
         <v>2600</v>
       </c>
@@ -12723,7 +12733,9 @@
       <c r="C570" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D570" s="2"/>
+      <c r="D570" s="2">
+        <v>751.5</v>
+      </c>
       <c r="E570" s="18">
         <v>1670</v>
       </c>
@@ -12741,7 +12753,9 @@
       <c r="C571" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D571" s="2"/>
+      <c r="D571" s="2">
+        <v>505.5</v>
+      </c>
       <c r="E571" s="18">
         <v>1610</v>
       </c>
@@ -12759,7 +12773,9 @@
       <c r="C572" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D572" s="2"/>
+      <c r="D572" s="2">
+        <v>258.5</v>
+      </c>
       <c r="E572" s="18">
         <v>1150</v>
       </c>
@@ -12777,7 +12793,9 @@
       <c r="C573" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D573" s="2"/>
+      <c r="D573" s="2">
+        <v>524</v>
+      </c>
       <c r="E573" s="18">
         <v>1405</v>
       </c>
@@ -12795,7 +12813,9 @@
       <c r="C574" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D574" s="2"/>
+      <c r="D574" s="2">
+        <v>159</v>
+      </c>
       <c r="E574" s="18">
         <v>1200</v>
       </c>
@@ -19725,7 +19745,7 @@
         <v>4</v>
       </c>
       <c r="K25" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25" s="8">
         <v>0</v>
@@ -19805,7 +19825,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="8">
         <v>0</v>
@@ -19885,7 +19905,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L27" s="8">
         <v>0</v>
@@ -19965,7 +19985,7 @@
         <v>1</v>
       </c>
       <c r="K28" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="8">
         <v>0</v>
@@ -20125,7 +20145,7 @@
         <v>1</v>
       </c>
       <c r="K30" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="8">
         <v>0</v>
@@ -20365,7 +20385,7 @@
         <v>1</v>
       </c>
       <c r="K33" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="8">
         <v>0</v>
@@ -20445,7 +20465,7 @@
         <v>1</v>
       </c>
       <c r="K34" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L34" s="8">
         <v>0</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/DASHBOARD-METAS-PROPOSTAS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="970" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AAC1ACB-C450-42BD-80CB-CB7ED84CBF1D}"/>
+  <xr:revisionPtr revIDLastSave="985" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9213D0EA-6791-46DD-BC0C-D07F8DD57F87}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -12833,7 +12833,9 @@
       <c r="C575" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D575" s="2"/>
+      <c r="D575" s="2">
+        <v>1020.5</v>
+      </c>
       <c r="E575" s="18">
         <v>4252.5</v>
       </c>
@@ -12851,7 +12853,9 @@
       <c r="C576" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D576" s="2"/>
+      <c r="D576" s="2">
+        <v>865.5</v>
+      </c>
       <c r="E576" s="18">
         <v>3780</v>
       </c>
@@ -12869,7 +12873,9 @@
       <c r="C577" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D577" s="2"/>
+      <c r="D577" s="2">
+        <v>662</v>
+      </c>
       <c r="E577" s="18">
         <v>1417.5</v>
       </c>
@@ -12887,7 +12893,9 @@
       <c r="C578" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D578" s="2"/>
+      <c r="D578" s="2">
+        <v>762</v>
+      </c>
       <c r="E578" s="18">
         <v>3900</v>
       </c>
@@ -12905,7 +12913,9 @@
       <c r="C579" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D579" s="2"/>
+      <c r="D579" s="2">
+        <v>502</v>
+      </c>
       <c r="E579" s="18">
         <v>2600</v>
       </c>
@@ -12923,7 +12933,9 @@
       <c r="C580" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D580" s="2"/>
+      <c r="D580" s="2">
+        <v>751.5</v>
+      </c>
       <c r="E580" s="18">
         <v>1670</v>
       </c>
@@ -12941,7 +12953,9 @@
       <c r="C581" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D581" s="2"/>
+      <c r="D581" s="2">
+        <v>508.5</v>
+      </c>
       <c r="E581" s="18">
         <v>1610</v>
       </c>
@@ -12959,7 +12973,9 @@
       <c r="C582" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D582" s="2"/>
+      <c r="D582" s="2">
+        <v>274</v>
+      </c>
       <c r="E582" s="18">
         <v>1150</v>
       </c>
@@ -12977,7 +12993,9 @@
       <c r="C583" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D583" s="2"/>
+      <c r="D583" s="2">
+        <v>534.5</v>
+      </c>
       <c r="E583" s="18">
         <v>1405</v>
       </c>
@@ -12995,7 +13013,9 @@
       <c r="C584" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D584" s="2"/>
+      <c r="D584" s="2">
+        <v>159</v>
+      </c>
       <c r="E584" s="18">
         <v>1200</v>
       </c>
@@ -19748,7 +19768,7 @@
         <v>2</v>
       </c>
       <c r="L25" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M25" s="8">
         <v>0</v>
@@ -19988,7 +20008,7 @@
         <v>1</v>
       </c>
       <c r="L28" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="8">
         <v>0</v>
@@ -20068,7 +20088,7 @@
         <v>0</v>
       </c>
       <c r="L29" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="8">
         <v>0</v>
@@ -20228,7 +20248,7 @@
         <v>0</v>
       </c>
       <c r="L31" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="8">
         <v>0</v>
@@ -20468,7 +20488,7 @@
         <v>4</v>
       </c>
       <c r="L34" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="8">
         <v>0</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/METAS PROPOSTAS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/C.I.V/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="985" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9213D0EA-6791-46DD-BC0C-D07F8DD57F87}"/>
+  <xr:revisionPtr revIDLastSave="1062" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41B515C8-2763-4DD2-A19D-21FCBFB36483}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20385" yWindow="-3135" windowWidth="23760" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -13033,7 +13033,9 @@
       <c r="C585" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D585" s="2"/>
+      <c r="D585" s="2">
+        <v>1090.5</v>
+      </c>
       <c r="E585" s="18">
         <v>4252.5</v>
       </c>
@@ -13051,7 +13053,9 @@
       <c r="C586" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D586" s="2"/>
+      <c r="D586" s="2">
+        <v>882.5</v>
+      </c>
       <c r="E586" s="18">
         <v>3780</v>
       </c>
@@ -13069,7 +13073,9 @@
       <c r="C587" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D587" s="2"/>
+      <c r="D587" s="2">
+        <v>684</v>
+      </c>
       <c r="E587" s="18">
         <v>1417.5</v>
       </c>
@@ -13087,7 +13093,9 @@
       <c r="C588" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D588" s="2"/>
+      <c r="D588" s="2">
+        <v>811.5</v>
+      </c>
       <c r="E588" s="18">
         <v>3900</v>
       </c>
@@ -13105,7 +13113,9 @@
       <c r="C589" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D589" s="2"/>
+      <c r="D589" s="2">
+        <v>563.5</v>
+      </c>
       <c r="E589" s="18">
         <v>2600</v>
       </c>
@@ -13123,7 +13133,9 @@
       <c r="C590" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D590" s="2"/>
+      <c r="D590" s="2">
+        <v>822.5</v>
+      </c>
       <c r="E590" s="18">
         <v>1670</v>
       </c>
@@ -13141,7 +13153,9 @@
       <c r="C591" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D591" s="2"/>
+      <c r="D591" s="2">
+        <v>577.5</v>
+      </c>
       <c r="E591" s="18">
         <v>1610</v>
       </c>
@@ -13159,7 +13173,9 @@
       <c r="C592" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D592" s="2"/>
+      <c r="D592" s="2">
+        <v>291.5</v>
+      </c>
       <c r="E592" s="18">
         <v>1150</v>
       </c>
@@ -13177,7 +13193,9 @@
       <c r="C593" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D593" s="2"/>
+      <c r="D593" s="2">
+        <v>657.5</v>
+      </c>
       <c r="E593" s="18">
         <v>1405</v>
       </c>
@@ -13195,7 +13213,9 @@
       <c r="C594" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D594" s="2"/>
+      <c r="D594" s="2">
+        <v>159</v>
+      </c>
       <c r="E594" s="18">
         <v>1200</v>
       </c>
@@ -13213,7 +13233,9 @@
       <c r="C595" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D595" s="2"/>
+      <c r="D595" s="2">
+        <v>1105</v>
+      </c>
       <c r="E595" s="18">
         <v>4252.5</v>
       </c>
@@ -13231,7 +13253,9 @@
       <c r="C596" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D596" s="2"/>
+      <c r="D596" s="2">
+        <v>890.5</v>
+      </c>
       <c r="E596" s="18">
         <v>3780</v>
       </c>
@@ -13249,7 +13273,9 @@
       <c r="C597" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D597" s="2"/>
+      <c r="D597" s="2">
+        <v>684</v>
+      </c>
       <c r="E597" s="18">
         <v>1417.5</v>
       </c>
@@ -13267,7 +13293,9 @@
       <c r="C598" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D598" s="2"/>
+      <c r="D598" s="2">
+        <v>851.5</v>
+      </c>
       <c r="E598" s="18">
         <v>3900</v>
       </c>
@@ -13285,7 +13313,9 @@
       <c r="C599" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D599" s="2"/>
+      <c r="D599" s="2">
+        <v>581.5</v>
+      </c>
       <c r="E599" s="18">
         <v>2600</v>
       </c>
@@ -13303,7 +13333,9 @@
       <c r="C600" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D600" s="2"/>
+      <c r="D600" s="2">
+        <v>862.5</v>
+      </c>
       <c r="E600" s="18">
         <v>1670</v>
       </c>
@@ -13321,7 +13353,9 @@
       <c r="C601" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D601" s="2"/>
+      <c r="D601" s="2">
+        <v>590</v>
+      </c>
       <c r="E601" s="18">
         <v>1610</v>
       </c>
@@ -13339,7 +13373,9 @@
       <c r="C602" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D602" s="2"/>
+      <c r="D602" s="2">
+        <v>291.5</v>
+      </c>
       <c r="E602" s="18">
         <v>1150</v>
       </c>
@@ -13357,7 +13393,9 @@
       <c r="C603" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D603" s="2"/>
+      <c r="D603" s="2">
+        <v>662.5</v>
+      </c>
       <c r="E603" s="18">
         <v>1405</v>
       </c>
@@ -13375,7 +13413,9 @@
       <c r="C604" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D604" s="2"/>
+      <c r="D604" s="2">
+        <v>159</v>
+      </c>
       <c r="E604" s="18">
         <v>1200</v>
       </c>
@@ -13393,7 +13433,9 @@
       <c r="C605" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D605" s="2"/>
+      <c r="D605" s="2">
+        <v>1243</v>
+      </c>
       <c r="E605" s="18">
         <v>4252.5</v>
       </c>
@@ -13411,7 +13453,9 @@
       <c r="C606" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D606" s="2"/>
+      <c r="D606" s="2">
+        <v>1024.5</v>
+      </c>
       <c r="E606" s="18">
         <v>3780</v>
       </c>
@@ -13429,7 +13473,9 @@
       <c r="C607" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D607" s="2"/>
+      <c r="D607" s="2">
+        <v>728.5</v>
+      </c>
       <c r="E607" s="18">
         <v>1417.5</v>
       </c>
@@ -13447,7 +13493,9 @@
       <c r="C608" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D608" s="2"/>
+      <c r="D608" s="2">
+        <v>898</v>
+      </c>
       <c r="E608" s="18">
         <v>3900</v>
       </c>
@@ -13465,7 +13513,9 @@
       <c r="C609" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D609" s="2"/>
+      <c r="D609" s="2">
+        <v>775.5</v>
+      </c>
       <c r="E609" s="18">
         <v>2600</v>
       </c>
@@ -13483,7 +13533,9 @@
       <c r="C610" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D610" s="2"/>
+      <c r="D610" s="2">
+        <v>894</v>
+      </c>
       <c r="E610" s="18">
         <v>1670</v>
       </c>
@@ -13501,7 +13553,9 @@
       <c r="C611" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D611" s="2"/>
+      <c r="D611" s="2">
+        <v>629.5</v>
+      </c>
       <c r="E611" s="18">
         <v>1610</v>
       </c>
@@ -13519,7 +13573,9 @@
       <c r="C612" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D612" s="2"/>
+      <c r="D612" s="2">
+        <v>323.5</v>
+      </c>
       <c r="E612" s="18">
         <v>1150</v>
       </c>
@@ -13537,7 +13593,9 @@
       <c r="C613" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D613" s="2"/>
+      <c r="D613" s="2">
+        <v>823</v>
+      </c>
       <c r="E613" s="18">
         <v>1405</v>
       </c>
@@ -13555,7 +13613,9 @@
       <c r="C614" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D614" s="2"/>
+      <c r="D614" s="2">
+        <v>159</v>
+      </c>
       <c r="E614" s="18">
         <v>1200</v>
       </c>
@@ -13573,7 +13633,9 @@
       <c r="C615" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D615" s="2"/>
+      <c r="D615" s="2">
+        <v>1460.5</v>
+      </c>
       <c r="E615" s="18">
         <v>4252.5</v>
       </c>
@@ -13591,7 +13653,9 @@
       <c r="C616" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D616" s="2"/>
+      <c r="D616" s="2">
+        <v>1111.5</v>
+      </c>
       <c r="E616" s="18">
         <v>3780</v>
       </c>
@@ -13609,7 +13673,9 @@
       <c r="C617" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D617" s="2"/>
+      <c r="D617" s="2">
+        <v>745</v>
+      </c>
       <c r="E617" s="18">
         <v>1417.5</v>
       </c>
@@ -13627,7 +13693,9 @@
       <c r="C618" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D618" s="2"/>
+      <c r="D618" s="2">
+        <v>933</v>
+      </c>
       <c r="E618" s="18">
         <v>3900</v>
       </c>
@@ -13645,7 +13713,9 @@
       <c r="C619" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D619" s="2"/>
+      <c r="D619" s="2">
+        <v>928.5</v>
+      </c>
       <c r="E619" s="18">
         <v>2600</v>
       </c>
@@ -13663,7 +13733,9 @@
       <c r="C620" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D620" s="2"/>
+      <c r="D620" s="2">
+        <v>937</v>
+      </c>
       <c r="E620" s="18">
         <v>1670</v>
       </c>
@@ -13681,7 +13753,9 @@
       <c r="C621" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D621" s="2"/>
+      <c r="D621" s="2">
+        <v>669.5</v>
+      </c>
       <c r="E621" s="18">
         <v>1610</v>
       </c>
@@ -13699,7 +13773,9 @@
       <c r="C622" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D622" s="2"/>
+      <c r="D622" s="2">
+        <v>406.5</v>
+      </c>
       <c r="E622" s="18">
         <v>1150</v>
       </c>
@@ -13717,7 +13793,9 @@
       <c r="C623" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D623" s="2"/>
+      <c r="D623" s="2">
+        <v>907.5</v>
+      </c>
       <c r="E623" s="18">
         <v>1405</v>
       </c>
@@ -13735,7 +13813,9 @@
       <c r="C624" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D624" s="2"/>
+      <c r="D624" s="2">
+        <v>210</v>
+      </c>
       <c r="E624" s="18">
         <v>1200</v>
       </c>
@@ -13753,7 +13833,9 @@
       <c r="C625" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D625" s="2"/>
+      <c r="D625" s="2">
+        <v>1615</v>
+      </c>
       <c r="E625" s="18">
         <v>4252.5</v>
       </c>
@@ -13771,7 +13853,9 @@
       <c r="C626" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D626" s="2"/>
+      <c r="D626" s="2">
+        <v>1490.5</v>
+      </c>
       <c r="E626" s="18">
         <v>3780</v>
       </c>
@@ -13789,7 +13873,9 @@
       <c r="C627" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D627" s="2"/>
+      <c r="D627" s="2">
+        <v>810.5</v>
+      </c>
       <c r="E627" s="18">
         <v>1417.5</v>
       </c>
@@ -13807,7 +13893,9 @@
       <c r="C628" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D628" s="2"/>
+      <c r="D628" s="2">
+        <v>1080</v>
+      </c>
       <c r="E628" s="18">
         <v>3900</v>
       </c>
@@ -13825,7 +13913,9 @@
       <c r="C629" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D629" s="2"/>
+      <c r="D629" s="2">
+        <v>1026.5</v>
+      </c>
       <c r="E629" s="18">
         <v>2600</v>
       </c>
@@ -13843,7 +13933,9 @@
       <c r="C630" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D630" s="2"/>
+      <c r="D630" s="2">
+        <v>982.5</v>
+      </c>
       <c r="E630" s="18">
         <v>1670</v>
       </c>
@@ -13861,7 +13953,9 @@
       <c r="C631" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D631" s="2"/>
+      <c r="D631" s="2">
+        <v>771</v>
+      </c>
       <c r="E631" s="18">
         <v>1610</v>
       </c>
@@ -13879,7 +13973,9 @@
       <c r="C632" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D632" s="2"/>
+      <c r="D632" s="2">
+        <v>450</v>
+      </c>
       <c r="E632" s="18">
         <v>1150</v>
       </c>
@@ -13897,7 +13993,9 @@
       <c r="C633" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D633" s="2"/>
+      <c r="D633" s="2">
+        <v>1003.5</v>
+      </c>
       <c r="E633" s="18">
         <v>1405</v>
       </c>
@@ -13915,7 +14013,9 @@
       <c r="C634" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D634" s="2"/>
+      <c r="D634" s="2">
+        <v>258</v>
+      </c>
       <c r="E634" s="18">
         <v>1200</v>
       </c>
@@ -19771,18 +19871,18 @@
         <v>3</v>
       </c>
       <c r="M25" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N25" s="8"/>
       <c r="O25" s="8"/>
       <c r="P25" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q25" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R25" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" s="8">
         <v>0</v>
@@ -19859,10 +19959,10 @@
         <v>0</v>
       </c>
       <c r="Q26" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R26" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" s="8">
         <v>0</v>
@@ -19931,15 +20031,15 @@
         <v>0</v>
       </c>
       <c r="M27" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" s="8"/>
       <c r="O27" s="8"/>
       <c r="P27" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q27" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R27" s="8">
         <v>0</v>
@@ -20016,7 +20116,7 @@
       <c r="N28" s="8"/>
       <c r="O28" s="8"/>
       <c r="P28" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28" s="8">
         <v>0</v>
@@ -20091,7 +20191,7 @@
         <v>1</v>
       </c>
       <c r="M29" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" s="8"/>
       <c r="O29" s="8"/>
@@ -20099,10 +20199,10 @@
         <v>0</v>
       </c>
       <c r="Q29" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S29" s="8">
         <v>0</v>
@@ -20182,7 +20282,7 @@
         <v>0</v>
       </c>
       <c r="R30" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" s="8">
         <v>0</v>
@@ -20251,18 +20351,18 @@
         <v>1</v>
       </c>
       <c r="M31" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N31" s="8"/>
       <c r="O31" s="8"/>
       <c r="P31" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" s="8">
         <v>0</v>
@@ -20419,10 +20519,10 @@
         <v>0</v>
       </c>
       <c r="Q33" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" s="8">
         <v>0</v>
@@ -20496,13 +20596,13 @@
       <c r="N34" s="8"/>
       <c r="O34" s="8"/>
       <c r="P34" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q34" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R34" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S34" s="8">
         <v>0</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/C.I.V/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1062" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41B515C8-2763-4DD2-A19D-21FCBFB36483}"/>
+  <xr:revisionPtr revIDLastSave="1078" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBDE8EB6-E68C-4160-A571-EDB211645033}"/>
   <bookViews>
-    <workbookView xWindow="20385" yWindow="-3135" windowWidth="23760" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -14033,7 +14033,9 @@
       <c r="C635" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D635" s="2"/>
+      <c r="D635" s="2">
+        <v>1970.5</v>
+      </c>
       <c r="E635" s="18">
         <v>4252.5</v>
       </c>
@@ -14051,7 +14053,9 @@
       <c r="C636" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D636" s="2"/>
+      <c r="D636" s="2">
+        <v>1786.5</v>
+      </c>
       <c r="E636" s="18">
         <v>3780</v>
       </c>
@@ -14069,7 +14073,9 @@
       <c r="C637" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D637" s="2"/>
+      <c r="D637" s="2">
+        <v>831.5</v>
+      </c>
       <c r="E637" s="18">
         <v>1417.5</v>
       </c>
@@ -14087,7 +14093,9 @@
       <c r="C638" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D638" s="2"/>
+      <c r="D638" s="2">
+        <v>1287.5</v>
+      </c>
       <c r="E638" s="18">
         <v>3900</v>
       </c>
@@ -14105,7 +14113,9 @@
       <c r="C639" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D639" s="2"/>
+      <c r="D639" s="2">
+        <v>1119</v>
+      </c>
       <c r="E639" s="18">
         <v>2600</v>
       </c>
@@ -14123,7 +14133,9 @@
       <c r="C640" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D640" s="2"/>
+      <c r="D640" s="2">
+        <v>1054.5</v>
+      </c>
       <c r="E640" s="18">
         <v>1670</v>
       </c>
@@ -14141,7 +14153,9 @@
       <c r="C641" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D641" s="2"/>
+      <c r="D641" s="2">
+        <v>832</v>
+      </c>
       <c r="E641" s="18">
         <v>1610</v>
       </c>
@@ -14159,7 +14173,9 @@
       <c r="C642" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D642" s="2"/>
+      <c r="D642" s="2">
+        <v>506.5</v>
+      </c>
       <c r="E642" s="18">
         <v>1150</v>
       </c>
@@ -14177,7 +14193,9 @@
       <c r="C643" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D643" s="2"/>
+      <c r="D643" s="2">
+        <v>1133</v>
+      </c>
       <c r="E643" s="18">
         <v>1405</v>
       </c>
@@ -14195,7 +14213,9 @@
       <c r="C644" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D644" s="2"/>
+      <c r="D644" s="2">
+        <v>304</v>
+      </c>
       <c r="E644" s="18">
         <v>1200</v>
       </c>
@@ -19965,7 +19985,7 @@
         <v>1</v>
       </c>
       <c r="S26" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" s="8">
         <v>0</v>
@@ -20045,7 +20065,7 @@
         <v>0</v>
       </c>
       <c r="S27" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T27" s="8">
         <v>0</v>
@@ -20125,7 +20145,7 @@
         <v>0</v>
       </c>
       <c r="S28" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T28" s="8">
         <v>0</v>
@@ -20525,7 +20545,7 @@
         <v>1</v>
       </c>
       <c r="S33" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T33" s="8">
         <v>0</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/C.I.V/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1078" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBDE8EB6-E68C-4160-A571-EDB211645033}"/>
+  <xr:revisionPtr revIDLastSave="1127" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20673F29-2279-4A93-B8BB-2936BBACCFC4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -14233,7 +14233,9 @@
       <c r="C645" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D645" s="2"/>
+      <c r="D645" s="2">
+        <v>2200</v>
+      </c>
       <c r="E645" s="18">
         <v>4252.5</v>
       </c>
@@ -14251,7 +14253,9 @@
       <c r="C646" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D646" s="2"/>
+      <c r="D646" s="2">
+        <v>2071.5</v>
+      </c>
       <c r="E646" s="18">
         <v>3780</v>
       </c>
@@ -14269,7 +14273,9 @@
       <c r="C647" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D647" s="2"/>
+      <c r="D647" s="2">
+        <v>913.5</v>
+      </c>
       <c r="E647" s="18">
         <v>1417.5</v>
       </c>
@@ -14287,7 +14293,9 @@
       <c r="C648" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D648" s="2"/>
+      <c r="D648" s="2">
+        <v>1651.5</v>
+      </c>
       <c r="E648" s="18">
         <v>3900</v>
       </c>
@@ -14305,7 +14313,9 @@
       <c r="C649" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D649" s="2"/>
+      <c r="D649" s="2">
+        <v>1197.5</v>
+      </c>
       <c r="E649" s="18">
         <v>2600</v>
       </c>
@@ -14323,7 +14333,9 @@
       <c r="C650" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D650" s="2"/>
+      <c r="D650" s="2">
+        <v>1146</v>
+      </c>
       <c r="E650" s="18">
         <v>1670</v>
       </c>
@@ -14341,7 +14353,9 @@
       <c r="C651" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D651" s="2"/>
+      <c r="D651" s="2">
+        <v>1006.5</v>
+      </c>
       <c r="E651" s="18">
         <v>1610</v>
       </c>
@@ -14359,7 +14373,9 @@
       <c r="C652" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D652" s="2"/>
+      <c r="D652" s="2">
+        <v>543</v>
+      </c>
       <c r="E652" s="18">
         <v>1150</v>
       </c>
@@ -14377,7 +14393,9 @@
       <c r="C653" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D653" s="2"/>
+      <c r="D653" s="2">
+        <v>1185</v>
+      </c>
       <c r="E653" s="18">
         <v>1405</v>
       </c>
@@ -14395,7 +14413,9 @@
       <c r="C654" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D654" s="2"/>
+      <c r="D654" s="2">
+        <v>336</v>
+      </c>
       <c r="E654" s="18">
         <v>1200</v>
       </c>
@@ -14413,7 +14433,9 @@
       <c r="C655" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D655" s="2"/>
+      <c r="D655" s="2">
+        <v>2200</v>
+      </c>
       <c r="E655" s="18">
         <v>4252.5</v>
       </c>
@@ -14431,7 +14453,9 @@
       <c r="C656" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D656" s="2"/>
+      <c r="D656" s="2">
+        <v>2071.5</v>
+      </c>
       <c r="E656" s="18">
         <v>3780</v>
       </c>
@@ -14449,7 +14473,9 @@
       <c r="C657" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D657" s="2"/>
+      <c r="D657" s="2">
+        <v>913.5</v>
+      </c>
       <c r="E657" s="18">
         <v>1417.5</v>
       </c>
@@ -14467,7 +14493,9 @@
       <c r="C658" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D658" s="2"/>
+      <c r="D658" s="2">
+        <v>1671.5</v>
+      </c>
       <c r="E658" s="18">
         <v>3900</v>
       </c>
@@ -14485,7 +14513,9 @@
       <c r="C659" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D659" s="2"/>
+      <c r="D659" s="2">
+        <v>1197.5</v>
+      </c>
       <c r="E659" s="18">
         <v>2600</v>
       </c>
@@ -14503,7 +14533,9 @@
       <c r="C660" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D660" s="2"/>
+      <c r="D660" s="2">
+        <v>1146</v>
+      </c>
       <c r="E660" s="18">
         <v>1670</v>
       </c>
@@ -14521,7 +14553,9 @@
       <c r="C661" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D661" s="2"/>
+      <c r="D661" s="2">
+        <v>1014.5</v>
+      </c>
       <c r="E661" s="18">
         <v>1610</v>
       </c>
@@ -14539,7 +14573,9 @@
       <c r="C662" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D662" s="2"/>
+      <c r="D662" s="2">
+        <v>543</v>
+      </c>
       <c r="E662" s="18">
         <v>1150</v>
       </c>
@@ -14557,7 +14593,9 @@
       <c r="C663" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D663" s="2"/>
+      <c r="D663" s="2">
+        <v>1185</v>
+      </c>
       <c r="E663" s="18">
         <v>1405</v>
       </c>
@@ -14575,7 +14613,9 @@
       <c r="C664" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D664" s="2"/>
+      <c r="D664" s="2">
+        <v>336</v>
+      </c>
       <c r="E664" s="18">
         <v>1200</v>
       </c>
@@ -14593,7 +14633,9 @@
       <c r="C665" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D665" s="2"/>
+      <c r="D665" s="2">
+        <v>2341.5</v>
+      </c>
       <c r="E665" s="18">
         <v>4252.5</v>
       </c>
@@ -14611,7 +14653,9 @@
       <c r="C666" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D666" s="2"/>
+      <c r="D666" s="2">
+        <v>2215</v>
+      </c>
       <c r="E666" s="18">
         <v>3780</v>
       </c>
@@ -14629,7 +14673,9 @@
       <c r="C667" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D667" s="2"/>
+      <c r="D667" s="2">
+        <v>954</v>
+      </c>
       <c r="E667" s="18">
         <v>1417.5</v>
       </c>
@@ -14647,7 +14693,9 @@
       <c r="C668" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D668" s="2"/>
+      <c r="D668" s="2">
+        <v>1742</v>
+      </c>
       <c r="E668" s="18">
         <v>3900</v>
       </c>
@@ -14665,7 +14713,9 @@
       <c r="C669" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D669" s="2"/>
+      <c r="D669" s="2">
+        <v>1406</v>
+      </c>
       <c r="E669" s="18">
         <v>2600</v>
       </c>
@@ -14683,7 +14733,9 @@
       <c r="C670" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D670" s="2"/>
+      <c r="D670" s="2">
+        <v>1207.5</v>
+      </c>
       <c r="E670" s="18">
         <v>1670</v>
       </c>
@@ -14701,7 +14753,9 @@
       <c r="C671" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D671" s="2"/>
+      <c r="D671" s="2">
+        <v>1059.5</v>
+      </c>
       <c r="E671" s="18">
         <v>1610</v>
       </c>
@@ -14719,7 +14773,9 @@
       <c r="C672" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D672" s="2"/>
+      <c r="D672" s="2">
+        <v>858</v>
+      </c>
       <c r="E672" s="18">
         <v>1150</v>
       </c>
@@ -14737,7 +14793,9 @@
       <c r="C673" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D673" s="2"/>
+      <c r="D673" s="2">
+        <v>1278</v>
+      </c>
       <c r="E673" s="18">
         <v>1405</v>
       </c>
@@ -14755,7 +14813,9 @@
       <c r="C674" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D674" s="2"/>
+      <c r="D674" s="2">
+        <v>362</v>
+      </c>
       <c r="E674" s="18">
         <v>1200</v>
       </c>
@@ -19908,12 +19968,12 @@
         <v>0</v>
       </c>
       <c r="T25" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="8"/>
       <c r="V25" s="8"/>
       <c r="W25" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X25" s="8">
         <v>0</v>
@@ -19988,12 +20048,12 @@
         <v>1</v>
       </c>
       <c r="T26" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U26" s="8"/>
       <c r="V26" s="8"/>
       <c r="W26" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X26" s="8">
         <v>0</v>
@@ -20068,12 +20128,12 @@
         <v>3</v>
       </c>
       <c r="T27" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U27" s="8"/>
       <c r="V27" s="8"/>
       <c r="W27" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X27" s="8">
         <v>0</v>
@@ -20153,7 +20213,7 @@
       <c r="U28" s="8"/>
       <c r="V28" s="8"/>
       <c r="W28" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" s="8">
         <v>0</v>
@@ -20228,12 +20288,12 @@
         <v>0</v>
       </c>
       <c r="T29" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U29" s="8"/>
       <c r="V29" s="8"/>
       <c r="W29" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X29" s="8">
         <v>0</v>
@@ -20313,7 +20373,7 @@
       <c r="U30" s="8"/>
       <c r="V30" s="8"/>
       <c r="W30" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X30" s="8">
         <v>0</v>
@@ -20393,7 +20453,7 @@
       <c r="U31" s="8"/>
       <c r="V31" s="8"/>
       <c r="W31" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X31" s="8">
         <v>0</v>
@@ -20548,12 +20608,12 @@
         <v>1</v>
       </c>
       <c r="T33" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U33" s="8"/>
       <c r="V33" s="8"/>
       <c r="W33" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X33" s="8">
         <v>0</v>
@@ -20628,7 +20688,7 @@
         <v>0</v>
       </c>
       <c r="T34" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U34" s="8"/>
       <c r="V34" s="8"/>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/C.I.V/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1127" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20673F29-2279-4A93-B8BB-2936BBACCFC4}"/>
+  <xr:revisionPtr revIDLastSave="1128" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FB1C498-52BB-445E-9655-F93077ADF859}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14774,7 +14774,7 @@
         <v>27</v>
       </c>
       <c r="D672" s="2">
-        <v>858</v>
+        <v>582</v>
       </c>
       <c r="E672" s="18">
         <v>1150</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/C.I.V/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1128" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FB1C498-52BB-445E-9655-F93077ADF859}"/>
+  <xr:revisionPtr revIDLastSave="1145" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5294F22F-863E-4D3E-B5C9-D4F4C401CB37}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -14833,7 +14833,9 @@
       <c r="C675" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D675" s="2"/>
+      <c r="D675" s="2">
+        <v>2579.5</v>
+      </c>
       <c r="E675" s="18">
         <v>4252.5</v>
       </c>
@@ -14851,7 +14853,9 @@
       <c r="C676" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D676" s="2"/>
+      <c r="D676" s="2">
+        <v>2547</v>
+      </c>
       <c r="E676" s="18">
         <v>3780</v>
       </c>
@@ -14869,7 +14873,9 @@
       <c r="C677" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D677" s="2"/>
+      <c r="D677" s="2">
+        <v>962</v>
+      </c>
       <c r="E677" s="18">
         <v>1417.5</v>
       </c>
@@ -14887,7 +14893,9 @@
       <c r="C678" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D678" s="2"/>
+      <c r="D678" s="2">
+        <v>1825</v>
+      </c>
       <c r="E678" s="18">
         <v>3900</v>
       </c>
@@ -14905,7 +14913,9 @@
       <c r="C679" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D679" s="2"/>
+      <c r="D679" s="2">
+        <v>1639.5</v>
+      </c>
       <c r="E679" s="18">
         <v>2600</v>
       </c>
@@ -14923,7 +14933,9 @@
       <c r="C680" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D680" s="2"/>
+      <c r="D680" s="2">
+        <v>1241</v>
+      </c>
       <c r="E680" s="18">
         <v>1670</v>
       </c>
@@ -14941,7 +14953,9 @@
       <c r="C681" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D681" s="2"/>
+      <c r="D681" s="2">
+        <v>601</v>
+      </c>
       <c r="E681" s="18">
         <v>1610</v>
       </c>
@@ -14959,7 +14973,9 @@
       <c r="C682" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D682" s="2"/>
+      <c r="D682" s="2">
+        <v>1114</v>
+      </c>
       <c r="E682" s="18">
         <v>1150</v>
       </c>
@@ -14977,7 +14993,9 @@
       <c r="C683" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D683" s="2"/>
+      <c r="D683" s="2">
+        <v>1300</v>
+      </c>
       <c r="E683" s="18">
         <v>1405</v>
       </c>
@@ -14995,7 +15013,9 @@
       <c r="C684" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D684" s="2"/>
+      <c r="D684" s="2">
+        <v>362</v>
+      </c>
       <c r="E684" s="18">
         <v>1200</v>
       </c>
@@ -19976,7 +19996,7 @@
         <v>3</v>
       </c>
       <c r="X25" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y25" s="8">
         <v>0</v>
@@ -20056,7 +20076,7 @@
         <v>2</v>
       </c>
       <c r="X26" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y26" s="8">
         <v>0</v>
@@ -20136,7 +20156,7 @@
         <v>2</v>
       </c>
       <c r="X27" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y27" s="8">
         <v>0</v>
@@ -20216,7 +20236,7 @@
         <v>1</v>
       </c>
       <c r="X28" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y28" s="8">
         <v>0</v>
@@ -20296,7 +20316,7 @@
         <v>1</v>
       </c>
       <c r="X29" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29" s="8">
         <v>0</v>
@@ -20456,7 +20476,7 @@
         <v>1</v>
       </c>
       <c r="X31" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y31" s="8">
         <v>0</v>
@@ -20696,7 +20716,7 @@
         <v>0</v>
       </c>
       <c r="X34" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34" s="8">
         <v>0</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/C.I.V/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1145" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5294F22F-863E-4D3E-B5C9-D4F4C401CB37}"/>
+  <xr:revisionPtr revIDLastSave="1147" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92D96A61-9F58-4EB1-A0AF-B204485EDC3E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -14954,7 +14954,7 @@
         <v>25</v>
       </c>
       <c r="D681" s="2">
-        <v>601</v>
+        <v>1114</v>
       </c>
       <c r="E681" s="18">
         <v>1610</v>
@@ -14974,7 +14974,7 @@
         <v>27</v>
       </c>
       <c r="D682" s="2">
-        <v>1114</v>
+        <v>601</v>
       </c>
       <c r="E682" s="18">
         <v>1150</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/C.I.V/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1147" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92D96A61-9F58-4EB1-A0AF-B204485EDC3E}"/>
+  <xr:revisionPtr revIDLastSave="1163" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E9D6BA0-1CE3-4C79-887A-AA633DF56BC0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -15033,7 +15033,9 @@
       <c r="C685" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D685" s="2"/>
+      <c r="D685" s="2">
+        <v>2730</v>
+      </c>
       <c r="E685" s="18">
         <v>4252.5</v>
       </c>
@@ -15051,7 +15053,9 @@
       <c r="C686" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D686" s="2"/>
+      <c r="D686" s="2">
+        <v>2610</v>
+      </c>
       <c r="E686" s="18">
         <v>3780</v>
       </c>
@@ -15069,7 +15073,9 @@
       <c r="C687" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D687" s="2"/>
+      <c r="D687" s="2">
+        <v>1050</v>
+      </c>
       <c r="E687" s="18">
         <v>1417.5</v>
       </c>
@@ -15087,7 +15093,9 @@
       <c r="C688" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D688" s="2"/>
+      <c r="D688" s="2">
+        <v>1901</v>
+      </c>
       <c r="E688" s="18">
         <v>3900</v>
       </c>
@@ -15105,7 +15113,9 @@
       <c r="C689" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D689" s="2"/>
+      <c r="D689" s="2">
+        <v>1765</v>
+      </c>
       <c r="E689" s="18">
         <v>2600</v>
       </c>
@@ -15123,7 +15133,9 @@
       <c r="C690" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D690" s="2"/>
+      <c r="D690" s="2">
+        <v>1273</v>
+      </c>
       <c r="E690" s="18">
         <v>1670</v>
       </c>
@@ -15141,7 +15153,9 @@
       <c r="C691" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D691" s="2"/>
+      <c r="D691" s="2">
+        <v>631.5</v>
+      </c>
       <c r="E691" s="18">
         <v>1610</v>
       </c>
@@ -15159,7 +15173,9 @@
       <c r="C692" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D692" s="2"/>
+      <c r="D692" s="2">
+        <v>1161.5</v>
+      </c>
       <c r="E692" s="18">
         <v>1150</v>
       </c>
@@ -15177,7 +15193,9 @@
       <c r="C693" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D693" s="2"/>
+      <c r="D693" s="2">
+        <v>1338.5</v>
+      </c>
       <c r="E693" s="18">
         <v>1405</v>
       </c>
@@ -15195,7 +15213,9 @@
       <c r="C694" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D694" s="2"/>
+      <c r="D694" s="2">
+        <v>390</v>
+      </c>
       <c r="E694" s="18">
         <v>1200</v>
       </c>
@@ -19999,7 +20019,7 @@
         <v>4</v>
       </c>
       <c r="Y25" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z25" s="8">
         <v>0</v>
@@ -20079,7 +20099,7 @@
         <v>2</v>
       </c>
       <c r="Y26" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z26" s="8">
         <v>0</v>
@@ -20159,7 +20179,7 @@
         <v>2</v>
       </c>
       <c r="Y27" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z27" s="8">
         <v>0</v>
@@ -20239,7 +20259,7 @@
         <v>1</v>
       </c>
       <c r="Y28" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z28" s="8">
         <v>0</v>
@@ -20399,7 +20419,7 @@
         <v>0</v>
       </c>
       <c r="Y30" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z30" s="8">
         <v>0</v>
@@ -20719,7 +20739,7 @@
         <v>1</v>
       </c>
       <c r="Y34" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z34" s="8">
         <v>0</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/C.I.V/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1163" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E9D6BA0-1CE3-4C79-887A-AA633DF56BC0}"/>
+  <xr:revisionPtr revIDLastSave="1166" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEBEEC85-B6BE-4FF8-BA4D-5925501CD8BA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -15154,7 +15154,7 @@
         <v>25</v>
       </c>
       <c r="D691" s="2">
-        <v>631.5</v>
+        <v>1161.5</v>
       </c>
       <c r="E691" s="18">
         <v>1610</v>
@@ -15174,7 +15174,7 @@
         <v>27</v>
       </c>
       <c r="D692" s="2">
-        <v>1161.5</v>
+        <v>631.5</v>
       </c>
       <c r="E692" s="18">
         <v>1150</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/C.I.V/Dashbord/METAS PROPOSTAS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1166" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEBEEC85-B6BE-4FF8-BA4D-5925501CD8BA}"/>
+  <xr:revisionPtr revIDLastSave="1190" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3C91840-2E5D-4F22-8ECE-BC039C5A152F}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -301,7 +301,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -352,6 +352,26 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFF00"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -425,7 +445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -501,6 +521,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -970,22 +1008,22 @@
       <c r="H7" s="7"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="28">
         <v>116</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="29">
         <v>427.5</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="30">
         <v>46204</v>
       </c>
       <c r="H8" s="7"/>
@@ -1159,22 +1197,22 @@
       <c r="H16" s="7"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="28">
         <v>213</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="29">
         <v>427.5</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="30">
         <v>46205</v>
       </c>
       <c r="H17" s="7"/>
@@ -1348,22 +1386,22 @@
       <c r="H25" s="7"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="28">
         <v>246</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="29">
         <v>427.5</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="30">
         <v>46206</v>
       </c>
       <c r="H26" s="7"/>
@@ -1537,22 +1575,22 @@
       <c r="H34" s="7"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="28">
         <v>254</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E35" s="29">
         <v>427.5</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="30">
         <v>46207</v>
       </c>
       <c r="H35" s="7"/>
@@ -1726,22 +1764,22 @@
       <c r="H43" s="7"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="28">
         <v>348</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="29">
         <v>427.5</v>
       </c>
-      <c r="F44" s="5">
+      <c r="F44" s="30">
         <v>46209</v>
       </c>
       <c r="H44" s="7"/>
@@ -1915,22 +1953,22 @@
       <c r="H52" s="7"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C53" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D53" s="19">
+      <c r="D53" s="28">
         <v>452</v>
       </c>
-      <c r="E53" s="3">
+      <c r="E53" s="29">
         <v>427.5</v>
       </c>
-      <c r="F53" s="5">
+      <c r="F53" s="30">
         <v>46210</v>
       </c>
       <c r="H53" s="7"/>
@@ -2104,22 +2142,22 @@
       <c r="H61" s="7"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C62" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D62" s="19">
+      <c r="D62" s="28">
         <v>508.5</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E62" s="29">
         <v>427.5</v>
       </c>
-      <c r="F62" s="5">
+      <c r="F62" s="30">
         <v>46211</v>
       </c>
       <c r="H62" s="7"/>
@@ -2293,22 +2331,22 @@
       <c r="H70" s="7"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="4" t="s">
+      <c r="A71" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B71" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="C71" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D71" s="19">
+      <c r="D71" s="28">
         <v>641.5</v>
       </c>
-      <c r="E71" s="3">
+      <c r="E71" s="29">
         <v>427.5</v>
       </c>
-      <c r="F71" s="5">
+      <c r="F71" s="30">
         <v>46212</v>
       </c>
       <c r="H71" s="7"/>
@@ -2482,22 +2520,22 @@
       <c r="H79" s="7"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="4" t="s">
+      <c r="A80" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B80" s="4" t="s">
+      <c r="B80" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="C80" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D80" s="19">
+      <c r="D80" s="28">
         <v>712</v>
       </c>
-      <c r="E80" s="3">
+      <c r="E80" s="29">
         <v>855</v>
       </c>
-      <c r="F80" s="5">
+      <c r="F80" s="30">
         <v>46213</v>
       </c>
       <c r="H80" s="7"/>
@@ -2671,22 +2709,22 @@
       <c r="H88" s="7"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="4" t="s">
+      <c r="A89" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="B89" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C89" s="4" t="s">
+      <c r="C89" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D89" s="19">
+      <c r="D89" s="28">
         <v>712.5</v>
       </c>
-      <c r="E89" s="3">
+      <c r="E89" s="29">
         <v>855</v>
       </c>
-      <c r="F89" s="5">
+      <c r="F89" s="30">
         <v>46214</v>
       </c>
       <c r="H89" s="7"/>
@@ -2860,22 +2898,22 @@
       <c r="H97" s="7"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="4" t="s">
+      <c r="A98" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="B98" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="C98" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D98" s="19">
+      <c r="D98" s="28">
         <v>786</v>
       </c>
-      <c r="E98" s="3">
+      <c r="E98" s="29">
         <v>855</v>
       </c>
-      <c r="F98" s="5">
+      <c r="F98" s="30">
         <v>46216</v>
       </c>
       <c r="H98" s="7"/>
@@ -3049,22 +3087,22 @@
       <c r="H106" s="7"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="4" t="s">
+      <c r="A107" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B107" s="4" t="s">
+      <c r="B107" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C107" s="4" t="s">
+      <c r="C107" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D107" s="19">
+      <c r="D107" s="28">
         <v>894.5</v>
       </c>
-      <c r="E107" s="3">
+      <c r="E107" s="29">
         <v>855</v>
       </c>
-      <c r="F107" s="5">
+      <c r="F107" s="30">
         <v>46217</v>
       </c>
       <c r="H107" s="7"/>
@@ -3238,22 +3276,22 @@
       <c r="H115" s="7"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116" s="4" t="s">
+      <c r="A116" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="B116" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C116" s="4" t="s">
+      <c r="C116" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D116" s="19">
+      <c r="D116" s="28">
         <v>938.5</v>
       </c>
-      <c r="E116" s="3">
+      <c r="E116" s="29">
         <v>855</v>
       </c>
-      <c r="F116" s="5">
+      <c r="F116" s="30">
         <v>46218</v>
       </c>
       <c r="H116" s="7"/>
@@ -3427,22 +3465,22 @@
       <c r="H124" s="7"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A125" s="4" t="s">
+      <c r="A125" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B125" s="4" t="s">
+      <c r="B125" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C125" s="4" t="s">
+      <c r="C125" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D125" s="19">
+      <c r="D125" s="28">
         <v>1005.5</v>
       </c>
-      <c r="E125" s="3">
+      <c r="E125" s="29">
         <v>855</v>
       </c>
-      <c r="F125" s="5">
+      <c r="F125" s="30">
         <v>46219</v>
       </c>
       <c r="H125" s="7"/>
@@ -3616,22 +3654,22 @@
       <c r="H133" s="7"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A134" s="4" t="s">
+      <c r="A134" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B134" s="4" t="s">
+      <c r="B134" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C134" s="4" t="s">
+      <c r="C134" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D134" s="19">
+      <c r="D134" s="28">
         <v>1077.5</v>
       </c>
-      <c r="E134" s="3">
+      <c r="E134" s="29">
         <v>1282.5</v>
       </c>
-      <c r="F134" s="5">
+      <c r="F134" s="30">
         <v>46220</v>
       </c>
       <c r="H134" s="7"/>
@@ -3805,22 +3843,22 @@
       <c r="H142" s="7"/>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A143" s="4" t="s">
+      <c r="A143" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B143" s="4" t="s">
+      <c r="B143" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C143" s="4" t="s">
+      <c r="C143" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D143" s="19">
+      <c r="D143" s="28">
         <v>1077.5</v>
       </c>
-      <c r="E143" s="3">
+      <c r="E143" s="29">
         <v>1282.5</v>
       </c>
-      <c r="F143" s="5">
+      <c r="F143" s="30">
         <v>46221</v>
       </c>
       <c r="H143" s="7"/>
@@ -3994,22 +4032,22 @@
       <c r="H151" s="7"/>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A152" s="4" t="s">
+      <c r="A152" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B152" s="4" t="s">
+      <c r="B152" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C152" s="4" t="s">
+      <c r="C152" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D152" s="19">
+      <c r="D152" s="28">
         <v>1144</v>
       </c>
-      <c r="E152" s="3">
+      <c r="E152" s="29">
         <v>1282.5</v>
       </c>
-      <c r="F152" s="5">
+      <c r="F152" s="30">
         <v>46223</v>
       </c>
       <c r="H152" s="7"/>
@@ -4183,22 +4221,22 @@
       <c r="H160" s="7"/>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A161" s="4" t="s">
+      <c r="A161" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B161" s="4" t="s">
+      <c r="B161" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C161" s="4" t="s">
+      <c r="C161" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D161" s="19">
+      <c r="D161" s="28">
         <v>1300.5</v>
       </c>
-      <c r="E161" s="3">
+      <c r="E161" s="29">
         <v>1282.5</v>
       </c>
-      <c r="F161" s="5">
+      <c r="F161" s="30">
         <v>46224</v>
       </c>
       <c r="H161" s="7"/>
@@ -4372,22 +4410,22 @@
       <c r="H169" s="7"/>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A170" s="4" t="s">
+      <c r="A170" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B170" s="4" t="s">
+      <c r="B170" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C170" s="4" t="s">
+      <c r="C170" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D170" s="19">
+      <c r="D170" s="28">
         <v>1321.5</v>
       </c>
-      <c r="E170" s="3">
+      <c r="E170" s="29">
         <v>1282.5</v>
       </c>
-      <c r="F170" s="5">
+      <c r="F170" s="30">
         <v>46225</v>
       </c>
       <c r="H170" s="7"/>
@@ -4561,22 +4599,22 @@
       <c r="H178" s="7"/>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A179" s="4" t="s">
+      <c r="A179" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B179" s="4" t="s">
+      <c r="B179" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C179" s="4" t="s">
+      <c r="C179" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D179" s="19">
+      <c r="D179" s="28">
         <v>1326.5</v>
       </c>
-      <c r="E179" s="3">
+      <c r="E179" s="29">
         <v>1282.5</v>
       </c>
-      <c r="F179" s="5">
+      <c r="F179" s="30">
         <v>46226</v>
       </c>
       <c r="H179" s="7"/>
@@ -4750,22 +4788,22 @@
       <c r="H187" s="7"/>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A188" s="4" t="s">
+      <c r="A188" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B188" s="4" t="s">
+      <c r="B188" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C188" s="4" t="s">
+      <c r="C188" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D188" s="19">
+      <c r="D188" s="28">
         <v>1326.5</v>
       </c>
-      <c r="E188" s="3">
+      <c r="E188" s="29">
         <v>1710</v>
       </c>
-      <c r="F188" s="5">
+      <c r="F188" s="30">
         <v>46227</v>
       </c>
       <c r="H188" s="7"/>
@@ -4939,22 +4977,22 @@
       <c r="H196" s="7"/>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A197" s="4" t="s">
+      <c r="A197" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B197" s="4" t="s">
+      <c r="B197" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C197" s="4" t="s">
+      <c r="C197" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D197" s="19">
+      <c r="D197" s="28">
         <v>1326.5</v>
       </c>
-      <c r="E197" s="3">
+      <c r="E197" s="29">
         <v>1710</v>
       </c>
-      <c r="F197" s="5">
+      <c r="F197" s="30">
         <v>46228</v>
       </c>
       <c r="H197" s="7"/>
@@ -5128,22 +5166,22 @@
       <c r="H205" s="7"/>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A206" s="4" t="s">
+      <c r="A206" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B206" s="4" t="s">
+      <c r="B206" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C206" s="4" t="s">
+      <c r="C206" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D206" s="19">
+      <c r="D206" s="28">
         <v>1340</v>
       </c>
-      <c r="E206" s="3">
+      <c r="E206" s="29">
         <v>1710</v>
       </c>
-      <c r="F206" s="5">
+      <c r="F206" s="30">
         <v>46230</v>
       </c>
       <c r="H206" s="7"/>
@@ -5317,22 +5355,22 @@
       <c r="H214" s="7"/>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A215" s="4" t="s">
+      <c r="A215" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B215" s="4" t="s">
+      <c r="B215" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C215" s="4" t="s">
+      <c r="C215" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D215" s="19">
+      <c r="D215" s="28">
         <v>1391</v>
       </c>
-      <c r="E215" s="3">
+      <c r="E215" s="29">
         <v>1710</v>
       </c>
-      <c r="F215" s="5">
+      <c r="F215" s="30">
         <v>46231</v>
       </c>
       <c r="H215" s="7"/>
@@ -5506,22 +5544,22 @@
       <c r="H223" s="7"/>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A224" s="4" t="s">
+      <c r="A224" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B224" s="4" t="s">
+      <c r="B224" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C224" s="4" t="s">
+      <c r="C224" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D224" s="19">
+      <c r="D224" s="28">
         <v>1455</v>
       </c>
-      <c r="E224" s="3">
+      <c r="E224" s="29">
         <v>1710</v>
       </c>
-      <c r="F224" s="5">
+      <c r="F224" s="30">
         <v>46232</v>
       </c>
       <c r="H224" s="7"/>
@@ -5695,22 +5733,22 @@
       <c r="H232" s="7"/>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A233" s="4" t="s">
+      <c r="A233" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B233" s="4" t="s">
+      <c r="B233" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C233" s="4" t="s">
+      <c r="C233" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D233" s="19">
+      <c r="D233" s="28">
         <v>1495.5</v>
       </c>
-      <c r="E233" s="3">
+      <c r="E233" s="29">
         <v>1710</v>
       </c>
-      <c r="F233" s="5">
+      <c r="F233" s="30">
         <v>46233</v>
       </c>
       <c r="H233" s="7"/>
@@ -5890,22 +5928,22 @@
       <c r="J241" s="7"/>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A242" s="4" t="s">
+      <c r="A242" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B242" s="4" t="s">
+      <c r="B242" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C242" s="4" t="s">
+      <c r="C242" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D242" s="19">
+      <c r="D242" s="28">
         <v>1564</v>
       </c>
-      <c r="E242" s="3">
+      <c r="E242" s="29">
         <v>1710</v>
       </c>
-      <c r="F242" s="5">
+      <c r="F242" s="30">
         <v>46234</v>
       </c>
       <c r="H242" s="7"/>
@@ -6088,22 +6126,22 @@
       <c r="J250" s="7"/>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A251" s="4" t="s">
+      <c r="A251" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B251" s="4" t="s">
+      <c r="B251" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C251" s="4" t="s">
+      <c r="C251" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D251" s="19">
+      <c r="D251" s="28">
         <v>46</v>
       </c>
-      <c r="E251" s="3">
+      <c r="E251" s="29">
         <v>402.5</v>
       </c>
-      <c r="F251" s="5">
+      <c r="F251" s="30">
         <v>46235</v>
       </c>
       <c r="H251" s="7"/>
@@ -6306,22 +6344,22 @@
       <c r="J260" s="7"/>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A261" s="4" t="s">
+      <c r="A261" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B261" s="4" t="s">
+      <c r="B261" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C261" s="4" t="s">
+      <c r="C261" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D261" s="19">
+      <c r="D261" s="28">
         <v>213.5</v>
       </c>
-      <c r="E261" s="3">
+      <c r="E261" s="29">
         <v>402.5</v>
       </c>
-      <c r="F261" s="5">
+      <c r="F261" s="30">
         <v>46237</v>
       </c>
       <c r="H261" s="7"/>
@@ -6520,22 +6558,22 @@
       <c r="J270" s="7"/>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A271" s="4" t="s">
+      <c r="A271" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B271" s="4" t="s">
+      <c r="B271" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C271" s="4" t="s">
+      <c r="C271" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D271" s="19">
+      <c r="D271" s="28">
         <v>305.5</v>
       </c>
-      <c r="E271" s="3">
+      <c r="E271" s="29">
         <v>402.5</v>
       </c>
-      <c r="F271" s="5">
+      <c r="F271" s="30">
         <v>46238</v>
       </c>
       <c r="J271" s="7"/>
@@ -6730,22 +6768,22 @@
       <c r="J280" s="7"/>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A281" s="4" t="s">
+      <c r="A281" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B281" s="4" t="s">
+      <c r="B281" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C281" s="4" t="s">
+      <c r="C281" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D281" s="19">
+      <c r="D281" s="28">
         <v>390.5</v>
       </c>
-      <c r="E281" s="3">
+      <c r="E281" s="29">
         <v>402.5</v>
       </c>
-      <c r="F281" s="5">
+      <c r="F281" s="30">
         <v>46239</v>
       </c>
       <c r="J281" s="7"/>
@@ -6940,22 +6978,22 @@
       <c r="J290" s="7"/>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A291" s="4" t="s">
+      <c r="A291" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B291" s="4" t="s">
+      <c r="B291" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C291" s="4" t="s">
+      <c r="C291" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D291" s="19">
+      <c r="D291" s="28">
         <v>446</v>
       </c>
-      <c r="E291" s="3">
+      <c r="E291" s="29">
         <v>402.5</v>
       </c>
-      <c r="F291" s="5">
+      <c r="F291" s="30">
         <v>46240</v>
       </c>
       <c r="J291" s="7"/>
@@ -7150,22 +7188,22 @@
       <c r="J300" s="7"/>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A301" s="4" t="s">
+      <c r="A301" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B301" s="4" t="s">
+      <c r="B301" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C301" s="4" t="s">
+      <c r="C301" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D301" s="19">
+      <c r="D301" s="28">
         <v>490.5</v>
       </c>
-      <c r="E301" s="3">
+      <c r="E301" s="29">
         <v>402.5</v>
       </c>
-      <c r="F301" s="5">
+      <c r="F301" s="30">
         <v>46241</v>
       </c>
       <c r="J301" s="7"/>
@@ -7360,22 +7398,22 @@
       <c r="J310" s="7"/>
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A311" s="4" t="s">
+      <c r="A311" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B311" s="4" t="s">
+      <c r="B311" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C311" s="4" t="s">
+      <c r="C311" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D311" s="19">
+      <c r="D311" s="28">
         <v>490.5</v>
       </c>
-      <c r="E311" s="3">
+      <c r="E311" s="29">
         <v>402.5</v>
       </c>
-      <c r="F311" s="5">
+      <c r="F311" s="30">
         <v>46242</v>
       </c>
       <c r="J311" s="7"/>
@@ -7570,22 +7608,22 @@
       <c r="J320" s="7"/>
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A321" s="4" t="s">
+      <c r="A321" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B321" s="4" t="s">
+      <c r="B321" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C321" s="4" t="s">
+      <c r="C321" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D321" s="19">
+      <c r="D321" s="28">
         <v>538.5</v>
       </c>
-      <c r="E321" s="3">
+      <c r="E321" s="29">
         <v>402.5</v>
       </c>
-      <c r="F321" s="5">
+      <c r="F321" s="30">
         <v>46244</v>
       </c>
       <c r="J321" s="7"/>
@@ -7780,22 +7818,22 @@
       <c r="J330" s="7"/>
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A331" s="4" t="s">
+      <c r="A331" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B331" s="4" t="s">
+      <c r="B331" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C331" s="4" t="s">
+      <c r="C331" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D331" s="19">
+      <c r="D331" s="28">
         <v>668.5</v>
       </c>
-      <c r="E331" s="3">
+      <c r="E331" s="29">
         <v>805</v>
       </c>
-      <c r="F331" s="5">
+      <c r="F331" s="30">
         <v>46245</v>
       </c>
       <c r="J331" s="7"/>
@@ -7990,22 +8028,22 @@
       <c r="J340" s="7"/>
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A341" s="4" t="s">
+      <c r="A341" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B341" s="4" t="s">
+      <c r="B341" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C341" s="4" t="s">
+      <c r="C341" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D341" s="19">
+      <c r="D341" s="28">
         <v>809.5</v>
       </c>
-      <c r="E341" s="3">
+      <c r="E341" s="29">
         <v>805</v>
       </c>
-      <c r="F341" s="5">
+      <c r="F341" s="30">
         <v>46246</v>
       </c>
       <c r="J341" s="7"/>
@@ -8200,22 +8238,22 @@
       <c r="J350" s="7"/>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A351" s="4" t="s">
+      <c r="A351" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B351" s="4" t="s">
+      <c r="B351" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C351" s="4" t="s">
+      <c r="C351" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D351" s="19">
+      <c r="D351" s="28">
         <v>966.5</v>
       </c>
-      <c r="E351" s="3">
+      <c r="E351" s="29">
         <v>805</v>
       </c>
-      <c r="F351" s="5">
+      <c r="F351" s="30">
         <v>46247</v>
       </c>
       <c r="J351" s="7"/>
@@ -8410,22 +8448,22 @@
       <c r="J360" s="7"/>
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A361" s="4" t="s">
+      <c r="A361" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B361" s="4" t="s">
+      <c r="B361" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C361" s="4" t="s">
+      <c r="C361" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D361" s="19">
+      <c r="D361" s="28">
         <v>1148.5</v>
       </c>
-      <c r="E361" s="3">
+      <c r="E361" s="29">
         <v>805</v>
       </c>
-      <c r="F361" s="5">
+      <c r="F361" s="30">
         <v>46248</v>
       </c>
       <c r="J361" s="7"/>
@@ -8620,22 +8658,22 @@
       <c r="J370" s="7"/>
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A371" s="4" t="s">
+      <c r="A371" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B371" s="4" t="s">
+      <c r="B371" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C371" s="4" t="s">
+      <c r="C371" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D371" s="19">
+      <c r="D371" s="28">
         <v>1223</v>
       </c>
-      <c r="E371" s="3">
+      <c r="E371" s="29">
         <v>805</v>
       </c>
-      <c r="F371" s="5">
+      <c r="F371" s="30">
         <v>46249</v>
       </c>
       <c r="J371" s="7"/>
@@ -8830,22 +8868,22 @@
       <c r="J380" s="7"/>
     </row>
     <row r="381" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A381" s="4" t="s">
+      <c r="A381" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B381" s="4" t="s">
+      <c r="B381" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C381" s="4" t="s">
+      <c r="C381" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D381" s="19">
+      <c r="D381" s="28">
         <v>1395.5</v>
       </c>
-      <c r="E381" s="3">
+      <c r="E381" s="29">
         <v>805</v>
       </c>
-      <c r="F381" s="5">
+      <c r="F381" s="30">
         <v>46251</v>
       </c>
       <c r="J381" s="7"/>
@@ -9040,22 +9078,22 @@
       <c r="J390" s="7"/>
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A391" s="4" t="s">
+      <c r="A391" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B391" s="4" t="s">
+      <c r="B391" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C391" s="4" t="s">
+      <c r="C391" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D391" s="19">
+      <c r="D391" s="28">
         <v>1509.5</v>
       </c>
-      <c r="E391" s="3">
+      <c r="E391" s="29">
         <v>1207.5</v>
       </c>
-      <c r="F391" s="5">
+      <c r="F391" s="30">
         <v>46252</v>
       </c>
       <c r="J391" s="7"/>
@@ -9250,22 +9288,22 @@
       <c r="J400" s="7"/>
     </row>
     <row r="401" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A401" s="4" t="s">
+      <c r="A401" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B401" s="4" t="s">
+      <c r="B401" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C401" s="4" t="s">
+      <c r="C401" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D401" s="19">
+      <c r="D401" s="28">
         <v>1644</v>
       </c>
-      <c r="E401" s="3">
+      <c r="E401" s="29">
         <v>1207.5</v>
       </c>
-      <c r="F401" s="5">
+      <c r="F401" s="30">
         <v>46253</v>
       </c>
       <c r="J401" s="7"/>
@@ -9460,22 +9498,22 @@
       <c r="J410" s="7"/>
     </row>
     <row r="411" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A411" s="4" t="s">
+      <c r="A411" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B411" s="4" t="s">
+      <c r="B411" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C411" s="4" t="s">
+      <c r="C411" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D411" s="19">
+      <c r="D411" s="28">
         <v>1809</v>
       </c>
-      <c r="E411" s="3">
+      <c r="E411" s="29">
         <v>1207.5</v>
       </c>
-      <c r="F411" s="5">
+      <c r="F411" s="30">
         <v>46254</v>
       </c>
       <c r="J411" s="7"/>
@@ -9670,22 +9708,22 @@
       <c r="J420" s="7"/>
     </row>
     <row r="421" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A421" s="4" t="s">
+      <c r="A421" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B421" s="4" t="s">
+      <c r="B421" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C421" s="4" t="s">
+      <c r="C421" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D421" s="19">
+      <c r="D421" s="28">
         <v>1913.5</v>
       </c>
-      <c r="E421" s="3">
+      <c r="E421" s="29">
         <v>1207.5</v>
       </c>
-      <c r="F421" s="5">
+      <c r="F421" s="30">
         <v>46255</v>
       </c>
       <c r="J421" s="7"/>
@@ -9880,22 +9918,22 @@
       <c r="J430" s="7"/>
     </row>
     <row r="431" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A431" s="4" t="s">
+      <c r="A431" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B431" s="4" t="s">
+      <c r="B431" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C431" s="4" t="s">
+      <c r="C431" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D431" s="19">
+      <c r="D431" s="28">
         <v>1921.5</v>
       </c>
-      <c r="E431" s="3">
+      <c r="E431" s="29">
         <v>1207.5</v>
       </c>
-      <c r="F431" s="5">
+      <c r="F431" s="30">
         <v>46256</v>
       </c>
       <c r="J431" s="7"/>
@@ -10090,22 +10128,22 @@
       <c r="J440" s="7"/>
     </row>
     <row r="441" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A441" s="4" t="s">
+      <c r="A441" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B441" s="4" t="s">
+      <c r="B441" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C441" s="4" t="s">
+      <c r="C441" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D441" s="19">
+      <c r="D441" s="28">
         <v>2041.5</v>
       </c>
-      <c r="E441" s="3">
+      <c r="E441" s="29">
         <v>1207.5</v>
       </c>
-      <c r="F441" s="5">
+      <c r="F441" s="30">
         <v>46258</v>
       </c>
       <c r="J441" s="7"/>
@@ -10300,22 +10338,22 @@
       <c r="J450" s="7"/>
     </row>
     <row r="451" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A451" s="4" t="s">
+      <c r="A451" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B451" s="4" t="s">
+      <c r="B451" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C451" s="4" t="s">
+      <c r="C451" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D451" s="19">
+      <c r="D451" s="28">
         <v>2213.5</v>
       </c>
-      <c r="E451" s="3">
+      <c r="E451" s="29">
         <v>1610</v>
       </c>
-      <c r="F451" s="5">
+      <c r="F451" s="30">
         <v>46259</v>
       </c>
       <c r="J451" s="7"/>
@@ -10510,22 +10548,22 @@
       <c r="J460" s="7"/>
     </row>
     <row r="461" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A461" s="4" t="s">
+      <c r="A461" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B461" s="4" t="s">
+      <c r="B461" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C461" s="4" t="s">
+      <c r="C461" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D461" s="19">
+      <c r="D461" s="28">
         <v>2342</v>
       </c>
-      <c r="E461" s="3">
+      <c r="E461" s="29">
         <v>1610</v>
       </c>
-      <c r="F461" s="5">
+      <c r="F461" s="30">
         <v>46260</v>
       </c>
       <c r="J461" s="7"/>
@@ -10720,22 +10758,22 @@
       <c r="J470" s="7"/>
     </row>
     <row r="471" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A471" s="4" t="s">
+      <c r="A471" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B471" s="4" t="s">
+      <c r="B471" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C471" s="4" t="s">
+      <c r="C471" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D471" s="19">
+      <c r="D471" s="28">
         <v>2442.5</v>
       </c>
-      <c r="E471" s="3">
+      <c r="E471" s="29">
         <v>1610</v>
       </c>
-      <c r="F471" s="5">
+      <c r="F471" s="30">
         <v>46261</v>
       </c>
       <c r="J471" s="7"/>
@@ -10930,22 +10968,22 @@
       <c r="J480" s="7"/>
     </row>
     <row r="481" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A481" s="4" t="s">
+      <c r="A481" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B481" s="4" t="s">
+      <c r="B481" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C481" s="4" t="s">
+      <c r="C481" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D481" s="19">
+      <c r="D481" s="28">
         <v>2514.5</v>
       </c>
-      <c r="E481" s="3">
+      <c r="E481" s="29">
         <v>1610</v>
       </c>
-      <c r="F481" s="5">
+      <c r="F481" s="30">
         <v>46262</v>
       </c>
       <c r="J481" s="7"/>
@@ -11140,22 +11178,22 @@
       <c r="J490" s="7"/>
     </row>
     <row r="491" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A491" s="4" t="s">
+      <c r="A491" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B491" s="4" t="s">
+      <c r="B491" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C491" s="4" t="s">
+      <c r="C491" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D491" s="19">
+      <c r="D491" s="28">
         <v>2535.5</v>
       </c>
-      <c r="E491" s="3">
+      <c r="E491" s="29">
         <v>1610</v>
       </c>
-      <c r="F491" s="5">
+      <c r="F491" s="30">
         <v>46263</v>
       </c>
       <c r="J491" s="7"/>
@@ -11344,22 +11382,22 @@
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A501" s="4" t="s">
+      <c r="A501" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B501" s="4" t="s">
+      <c r="B501" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C501" s="4" t="s">
+      <c r="C501" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D501" s="19">
+      <c r="D501" s="28">
         <v>2551.5</v>
       </c>
-      <c r="E501" s="3">
+      <c r="E501" s="29">
         <v>1610</v>
       </c>
-      <c r="F501" s="5">
+      <c r="F501" s="30">
         <v>46265</v>
       </c>
     </row>
@@ -11544,22 +11582,22 @@
       </c>
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A511" s="4" t="s">
+      <c r="A511" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B511" s="4" t="s">
+      <c r="B511" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C511" s="4" t="s">
+      <c r="C511" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D511" s="19">
+      <c r="D511" s="28">
         <v>62.5</v>
       </c>
-      <c r="E511" s="18">
+      <c r="E511" s="31">
         <v>1610</v>
       </c>
-      <c r="F511" s="5">
+      <c r="F511" s="30">
         <v>46266</v>
       </c>
     </row>
@@ -11744,22 +11782,22 @@
       </c>
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A521" s="4" t="s">
+      <c r="A521" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B521" s="4" t="s">
+      <c r="B521" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C521" s="4" t="s">
+      <c r="C521" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D521" s="19">
+      <c r="D521" s="28">
         <v>170.5</v>
       </c>
-      <c r="E521" s="18">
+      <c r="E521" s="31">
         <v>1610</v>
       </c>
-      <c r="F521" s="5">
+      <c r="F521" s="30">
         <v>46267</v>
       </c>
     </row>
@@ -11944,22 +11982,22 @@
       </c>
     </row>
     <row r="531" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A531" s="4" t="s">
+      <c r="A531" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B531" s="4" t="s">
+      <c r="B531" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C531" s="4" t="s">
+      <c r="C531" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D531" s="2">
+      <c r="D531" s="32">
         <v>255.5</v>
       </c>
-      <c r="E531" s="18">
+      <c r="E531" s="31">
         <v>1610</v>
       </c>
-      <c r="F531" s="5">
+      <c r="F531" s="30">
         <v>46268</v>
       </c>
     </row>
@@ -12144,22 +12182,22 @@
       </c>
     </row>
     <row r="541" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A541" s="4" t="s">
+      <c r="A541" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B541" s="4" t="s">
+      <c r="B541" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C541" s="4" t="s">
+      <c r="C541" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D541" s="2">
+      <c r="D541" s="32">
         <v>332.5</v>
       </c>
-      <c r="E541" s="18">
+      <c r="E541" s="31">
         <v>1610</v>
       </c>
-      <c r="F541" s="5">
+      <c r="F541" s="30">
         <v>46269</v>
       </c>
     </row>
@@ -12344,22 +12382,22 @@
       </c>
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A551" s="4" t="s">
+      <c r="A551" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B551" s="4" t="s">
+      <c r="B551" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C551" s="4" t="s">
+      <c r="C551" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D551" s="2">
+      <c r="D551" s="32">
         <v>332.5</v>
       </c>
-      <c r="E551" s="18">
+      <c r="E551" s="31">
         <v>1610</v>
       </c>
-      <c r="F551" s="5">
+      <c r="F551" s="30">
         <v>46270</v>
       </c>
     </row>
@@ -12544,22 +12582,22 @@
       </c>
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A561" s="4" t="s">
+      <c r="A561" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B561" s="4" t="s">
+      <c r="B561" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C561" s="4" t="s">
+      <c r="C561" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D561" s="2">
+      <c r="D561" s="32">
         <v>421.5</v>
       </c>
-      <c r="E561" s="18">
+      <c r="E561" s="31">
         <v>1610</v>
       </c>
-      <c r="F561" s="5">
+      <c r="F561" s="30">
         <v>46273</v>
       </c>
     </row>
@@ -12744,22 +12782,22 @@
       </c>
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A571" s="4" t="s">
+      <c r="A571" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B571" s="4" t="s">
+      <c r="B571" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C571" s="4" t="s">
+      <c r="C571" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D571" s="2">
+      <c r="D571" s="32">
         <v>505.5</v>
       </c>
-      <c r="E571" s="18">
+      <c r="E571" s="31">
         <v>1610</v>
       </c>
-      <c r="F571" s="5">
+      <c r="F571" s="30">
         <v>46274</v>
       </c>
     </row>
@@ -12944,22 +12982,22 @@
       </c>
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A581" s="4" t="s">
+      <c r="A581" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B581" s="4" t="s">
+      <c r="B581" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C581" s="4" t="s">
+      <c r="C581" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D581" s="2">
+      <c r="D581" s="32">
         <v>508.5</v>
       </c>
-      <c r="E581" s="18">
+      <c r="E581" s="31">
         <v>1610</v>
       </c>
-      <c r="F581" s="5">
+      <c r="F581" s="30">
         <v>46275</v>
       </c>
     </row>
@@ -13144,22 +13182,22 @@
       </c>
     </row>
     <row r="591" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A591" s="4" t="s">
+      <c r="A591" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B591" s="4" t="s">
+      <c r="B591" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C591" s="4" t="s">
+      <c r="C591" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D591" s="2">
+      <c r="D591" s="32">
         <v>577.5</v>
       </c>
-      <c r="E591" s="18">
+      <c r="E591" s="31">
         <v>1610</v>
       </c>
-      <c r="F591" s="5">
+      <c r="F591" s="30">
         <v>46276</v>
       </c>
     </row>
@@ -13344,22 +13382,22 @@
       </c>
     </row>
     <row r="601" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A601" s="4" t="s">
+      <c r="A601" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B601" s="4" t="s">
+      <c r="B601" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C601" s="4" t="s">
+      <c r="C601" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D601" s="2">
+      <c r="D601" s="32">
         <v>590</v>
       </c>
-      <c r="E601" s="18">
+      <c r="E601" s="31">
         <v>1610</v>
       </c>
-      <c r="F601" s="5">
+      <c r="F601" s="30">
         <v>46277</v>
       </c>
     </row>
@@ -13544,22 +13582,22 @@
       </c>
     </row>
     <row r="611" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A611" s="4" t="s">
+      <c r="A611" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B611" s="4" t="s">
+      <c r="B611" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C611" s="4" t="s">
+      <c r="C611" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D611" s="2">
+      <c r="D611" s="32">
         <v>629.5</v>
       </c>
-      <c r="E611" s="18">
+      <c r="E611" s="31">
         <v>1610</v>
       </c>
-      <c r="F611" s="5">
+      <c r="F611" s="30">
         <v>46279</v>
       </c>
     </row>
@@ -13744,22 +13782,22 @@
       </c>
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A621" s="4" t="s">
+      <c r="A621" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B621" s="4" t="s">
+      <c r="B621" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C621" s="4" t="s">
+      <c r="C621" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D621" s="2">
+      <c r="D621" s="32">
         <v>669.5</v>
       </c>
-      <c r="E621" s="18">
+      <c r="E621" s="31">
         <v>1610</v>
       </c>
-      <c r="F621" s="5">
+      <c r="F621" s="30">
         <v>46280</v>
       </c>
     </row>
@@ -13944,22 +13982,22 @@
       </c>
     </row>
     <row r="631" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A631" s="4" t="s">
+      <c r="A631" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B631" s="4" t="s">
+      <c r="B631" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C631" s="4" t="s">
+      <c r="C631" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D631" s="2">
+      <c r="D631" s="32">
         <v>771</v>
       </c>
-      <c r="E631" s="18">
+      <c r="E631" s="31">
         <v>1610</v>
       </c>
-      <c r="F631" s="5">
+      <c r="F631" s="30">
         <v>46281</v>
       </c>
     </row>
@@ -14144,22 +14182,22 @@
       </c>
     </row>
     <row r="641" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A641" s="4" t="s">
+      <c r="A641" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B641" s="4" t="s">
+      <c r="B641" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C641" s="4" t="s">
+      <c r="C641" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D641" s="2">
+      <c r="D641" s="32">
         <v>832</v>
       </c>
-      <c r="E641" s="18">
+      <c r="E641" s="31">
         <v>1610</v>
       </c>
-      <c r="F641" s="5">
+      <c r="F641" s="30">
         <v>46282</v>
       </c>
     </row>
@@ -14344,22 +14382,22 @@
       </c>
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A651" s="4" t="s">
+      <c r="A651" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B651" s="4" t="s">
+      <c r="B651" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C651" s="4" t="s">
+      <c r="C651" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D651" s="2">
+      <c r="D651" s="32">
         <v>1006.5</v>
       </c>
-      <c r="E651" s="18">
+      <c r="E651" s="31">
         <v>1610</v>
       </c>
-      <c r="F651" s="5">
+      <c r="F651" s="30">
         <v>46283</v>
       </c>
     </row>
@@ -14544,22 +14582,22 @@
       </c>
     </row>
     <row r="661" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A661" s="4" t="s">
+      <c r="A661" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B661" s="4" t="s">
+      <c r="B661" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C661" s="4" t="s">
+      <c r="C661" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D661" s="2">
+      <c r="D661" s="32">
         <v>1014.5</v>
       </c>
-      <c r="E661" s="18">
+      <c r="E661" s="31">
         <v>1610</v>
       </c>
-      <c r="F661" s="5">
+      <c r="F661" s="30">
         <v>46284</v>
       </c>
     </row>
@@ -14744,22 +14782,22 @@
       </c>
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A671" s="4" t="s">
+      <c r="A671" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B671" s="4" t="s">
+      <c r="B671" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C671" s="4" t="s">
+      <c r="C671" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D671" s="2">
+      <c r="D671" s="32">
         <v>1059.5</v>
       </c>
-      <c r="E671" s="18">
+      <c r="E671" s="31">
         <v>1610</v>
       </c>
-      <c r="F671" s="5">
+      <c r="F671" s="30">
         <v>46286</v>
       </c>
     </row>
@@ -14944,22 +14982,22 @@
       </c>
     </row>
     <row r="681" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A681" s="4" t="s">
+      <c r="A681" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B681" s="4" t="s">
+      <c r="B681" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C681" s="4" t="s">
+      <c r="C681" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D681" s="2">
+      <c r="D681" s="32">
         <v>1114</v>
       </c>
-      <c r="E681" s="18">
+      <c r="E681" s="31">
         <v>1610</v>
       </c>
-      <c r="F681" s="5">
+      <c r="F681" s="30">
         <v>46287</v>
       </c>
     </row>
@@ -15144,22 +15182,22 @@
       </c>
     </row>
     <row r="691" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A691" s="4" t="s">
+      <c r="A691" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B691" s="4" t="s">
+      <c r="B691" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C691" s="4" t="s">
+      <c r="C691" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D691" s="2">
+      <c r="D691" s="32">
         <v>1161.5</v>
       </c>
-      <c r="E691" s="18">
+      <c r="E691" s="31">
         <v>1610</v>
       </c>
-      <c r="F691" s="5">
+      <c r="F691" s="30">
         <v>46288</v>
       </c>
     </row>
@@ -15233,7 +15271,9 @@
       <c r="C695" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D695" s="2"/>
+      <c r="D695" s="2">
+        <v>2877.5</v>
+      </c>
       <c r="E695" s="18">
         <v>4252.5</v>
       </c>
@@ -15251,7 +15291,9 @@
       <c r="C696" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D696" s="2"/>
+      <c r="D696" s="2">
+        <v>2865.5</v>
+      </c>
       <c r="E696" s="18">
         <v>3780</v>
       </c>
@@ -15269,7 +15311,9 @@
       <c r="C697" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D697" s="2"/>
+      <c r="D697" s="2">
+        <v>1068</v>
+      </c>
       <c r="E697" s="18">
         <v>1417.5</v>
       </c>
@@ -15287,7 +15331,9 @@
       <c r="C698" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D698" s="2"/>
+      <c r="D698" s="2">
+        <v>2161.5</v>
+      </c>
       <c r="E698" s="18">
         <v>3900</v>
       </c>
@@ -15305,7 +15351,9 @@
       <c r="C699" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D699" s="2"/>
+      <c r="D699" s="2">
+        <v>1880</v>
+      </c>
       <c r="E699" s="18">
         <v>2600</v>
       </c>
@@ -15323,7 +15371,9 @@
       <c r="C700" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D700" s="2"/>
+      <c r="D700" s="2">
+        <v>1350</v>
+      </c>
       <c r="E700" s="18">
         <v>1670</v>
       </c>
@@ -15332,20 +15382,22 @@
       </c>
     </row>
     <row r="701" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A701" s="4" t="s">
+      <c r="A701" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B701" s="4" t="s">
+      <c r="B701" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C701" s="4" t="s">
+      <c r="C701" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D701" s="2"/>
-      <c r="E701" s="18">
+      <c r="D701" s="32">
+        <v>1235</v>
+      </c>
+      <c r="E701" s="31">
         <v>1610</v>
       </c>
-      <c r="F701" s="5">
+      <c r="F701" s="30">
         <v>46289</v>
       </c>
     </row>
@@ -15359,7 +15411,9 @@
       <c r="C702" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D702" s="2"/>
+      <c r="D702" s="2">
+        <v>660.5</v>
+      </c>
       <c r="E702" s="18">
         <v>1150</v>
       </c>
@@ -15377,7 +15431,9 @@
       <c r="C703" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D703" s="2"/>
+      <c r="D703" s="2">
+        <v>1376</v>
+      </c>
       <c r="E703" s="18">
         <v>1405</v>
       </c>
@@ -15395,7 +15451,9 @@
       <c r="C704" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D704" s="2"/>
+      <c r="D704" s="2">
+        <v>452</v>
+      </c>
       <c r="E704" s="18">
         <v>1200</v>
       </c>
@@ -15512,20 +15570,20 @@
       </c>
     </row>
     <row r="711" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A711" s="4" t="s">
+      <c r="A711" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B711" s="4" t="s">
+      <c r="B711" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C711" s="4" t="s">
+      <c r="C711" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D711" s="2"/>
-      <c r="E711" s="18">
+      <c r="D711" s="32"/>
+      <c r="E711" s="31">
         <v>1610</v>
       </c>
-      <c r="F711" s="5">
+      <c r="F711" s="30">
         <v>46290</v>
       </c>
     </row>
@@ -15692,20 +15750,20 @@
       </c>
     </row>
     <row r="721" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A721" s="4" t="s">
+      <c r="A721" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B721" s="4" t="s">
+      <c r="B721" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C721" s="4" t="s">
+      <c r="C721" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D721" s="2"/>
-      <c r="E721" s="18">
+      <c r="D721" s="32"/>
+      <c r="E721" s="31">
         <v>1610</v>
       </c>
-      <c r="F721" s="5">
+      <c r="F721" s="30">
         <v>46291</v>
       </c>
     </row>
@@ -15872,20 +15930,20 @@
       </c>
     </row>
     <row r="731" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A731" s="4" t="s">
+      <c r="A731" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B731" s="4" t="s">
+      <c r="B731" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C731" s="4" t="s">
+      <c r="C731" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D731" s="2"/>
-      <c r="E731" s="18">
+      <c r="D731" s="32"/>
+      <c r="E731" s="31">
         <v>1610</v>
       </c>
-      <c r="F731" s="5">
+      <c r="F731" s="30">
         <v>46293</v>
       </c>
     </row>
@@ -16052,20 +16110,20 @@
       </c>
     </row>
     <row r="741" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A741" s="4" t="s">
+      <c r="A741" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B741" s="4" t="s">
+      <c r="B741" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C741" s="4" t="s">
+      <c r="C741" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D741" s="2"/>
-      <c r="E741" s="18">
+      <c r="D741" s="32"/>
+      <c r="E741" s="31">
         <v>1610</v>
       </c>
-      <c r="F741" s="5">
+      <c r="F741" s="30">
         <v>46294</v>
       </c>
     </row>
@@ -16232,20 +16290,20 @@
       </c>
     </row>
     <row r="751" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A751" s="4" t="s">
+      <c r="A751" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B751" s="4" t="s">
+      <c r="B751" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C751" s="4" t="s">
+      <c r="C751" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D751" s="2"/>
-      <c r="E751" s="18">
+      <c r="D751" s="32"/>
+      <c r="E751" s="31">
         <v>1610</v>
       </c>
-      <c r="F751" s="5">
+      <c r="F751" s="30">
         <v>46295</v>
       </c>
     </row>
@@ -20022,7 +20080,7 @@
         <v>3</v>
       </c>
       <c r="Z25" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA25" s="8">
         <v>0</v>
@@ -20182,7 +20240,7 @@
         <v>3</v>
       </c>
       <c r="Z27" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA27" s="8">
         <v>0</v>
@@ -20422,7 +20480,7 @@
         <v>1</v>
       </c>
       <c r="Z30" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA30" s="8">
         <v>0</v>
@@ -20502,7 +20560,7 @@
         <v>0</v>
       </c>
       <c r="Z31" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA31" s="8">
         <v>0</v>
@@ -20742,7 +20800,7 @@
         <v>3</v>
       </c>
       <c r="Z34" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA34" s="8">
         <v>0</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1190" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3C91840-2E5D-4F22-8ECE-BC039C5A152F}"/>
+  <xr:revisionPtr revIDLastSave="1206" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F3249A1-7FC3-42A3-96F5-89FB189BA502}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -15471,7 +15471,9 @@
       <c r="C705" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D705" s="2"/>
+      <c r="D705" s="2">
+        <v>2959</v>
+      </c>
       <c r="E705" s="18">
         <v>4252.5</v>
       </c>
@@ -15489,7 +15491,9 @@
       <c r="C706" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D706" s="2"/>
+      <c r="D706" s="2">
+        <v>3158</v>
+      </c>
       <c r="E706" s="18">
         <v>3780</v>
       </c>
@@ -15507,7 +15511,9 @@
       <c r="C707" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D707" s="2"/>
+      <c r="D707" s="2">
+        <v>1119.5</v>
+      </c>
       <c r="E707" s="18">
         <v>1417.5</v>
       </c>
@@ -15525,7 +15531,9 @@
       <c r="C708" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D708" s="2"/>
+      <c r="D708" s="2">
+        <v>2238</v>
+      </c>
       <c r="E708" s="18">
         <v>3900</v>
       </c>
@@ -15543,7 +15551,9 @@
       <c r="C709" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D709" s="2"/>
+      <c r="D709" s="2">
+        <v>2025</v>
+      </c>
       <c r="E709" s="18">
         <v>2600</v>
       </c>
@@ -15561,7 +15571,9 @@
       <c r="C710" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D710" s="2"/>
+      <c r="D710" s="2">
+        <v>1478</v>
+      </c>
       <c r="E710" s="18">
         <v>1670</v>
       </c>
@@ -15579,7 +15591,9 @@
       <c r="C711" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D711" s="32"/>
+      <c r="D711" s="32">
+        <v>1327</v>
+      </c>
       <c r="E711" s="31">
         <v>1610</v>
       </c>
@@ -15597,7 +15611,9 @@
       <c r="C712" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D712" s="2"/>
+      <c r="D712" s="2">
+        <v>679</v>
+      </c>
       <c r="E712" s="18">
         <v>1150</v>
       </c>
@@ -15615,7 +15631,9 @@
       <c r="C713" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D713" s="2"/>
+      <c r="D713" s="2">
+        <v>1493</v>
+      </c>
       <c r="E713" s="18">
         <v>1405</v>
       </c>
@@ -15633,7 +15651,9 @@
       <c r="C714" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D714" s="2"/>
+      <c r="D714" s="2">
+        <v>490</v>
+      </c>
       <c r="E714" s="18">
         <v>1200</v>
       </c>
@@ -20083,7 +20103,7 @@
         <v>3</v>
       </c>
       <c r="AA25" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB25" s="8"/>
       <c r="AC25" s="8"/>
@@ -20243,7 +20263,7 @@
         <v>1</v>
       </c>
       <c r="AA27" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB27" s="8"/>
       <c r="AC27" s="8"/>
@@ -20323,7 +20343,7 @@
         <v>0</v>
       </c>
       <c r="AA28" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB28" s="8"/>
       <c r="AC28" s="8"/>
@@ -20403,7 +20423,7 @@
         <v>0</v>
       </c>
       <c r="AA29" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB29" s="8"/>
       <c r="AC29" s="8"/>
@@ -20723,7 +20743,7 @@
         <v>0</v>
       </c>
       <c r="AA33" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB33" s="8"/>
       <c r="AC33" s="8"/>
@@ -20803,7 +20823,7 @@
         <v>1</v>
       </c>
       <c r="AA34" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB34" s="8"/>
       <c r="AC34" s="8"/>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/Dashbord/METAS PROPOSTAS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/Dados/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1206" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F3249A1-7FC3-42A3-96F5-89FB189BA502}"/>
+  <xr:revisionPtr revIDLastSave="1258" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D54FAA04-7931-4469-A76C-3E50DD3CD788}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -301,7 +301,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -358,23 +358,16 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFFFF00"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFF00"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFFFF00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -532,10 +525,10 @@
     <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -15671,7 +15664,9 @@
       <c r="C715" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D715" s="2"/>
+      <c r="D715" s="2">
+        <v>2955</v>
+      </c>
       <c r="E715" s="18">
         <v>4252.5</v>
       </c>
@@ -15689,7 +15684,9 @@
       <c r="C716" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D716" s="2"/>
+      <c r="D716" s="2">
+        <v>3145</v>
+      </c>
       <c r="E716" s="18">
         <v>3780</v>
       </c>
@@ -15707,7 +15704,9 @@
       <c r="C717" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D717" s="2"/>
+      <c r="D717" s="2">
+        <v>1111.5</v>
+      </c>
       <c r="E717" s="18">
         <v>1417.5</v>
       </c>
@@ -15725,7 +15724,9 @@
       <c r="C718" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D718" s="2"/>
+      <c r="D718" s="2">
+        <v>2238</v>
+      </c>
       <c r="E718" s="18">
         <v>3900</v>
       </c>
@@ -15743,7 +15744,9 @@
       <c r="C719" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D719" s="2"/>
+      <c r="D719" s="2">
+        <v>2015.5</v>
+      </c>
       <c r="E719" s="18">
         <v>2600</v>
       </c>
@@ -15761,7 +15764,9 @@
       <c r="C720" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D720" s="2"/>
+      <c r="D720" s="2">
+        <v>1472</v>
+      </c>
       <c r="E720" s="18">
         <v>1670</v>
       </c>
@@ -15779,7 +15784,9 @@
       <c r="C721" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D721" s="32"/>
+      <c r="D721" s="32">
+        <v>1327</v>
+      </c>
       <c r="E721" s="31">
         <v>1610</v>
       </c>
@@ -15797,7 +15804,9 @@
       <c r="C722" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D722" s="2"/>
+      <c r="D722" s="2">
+        <v>679</v>
+      </c>
       <c r="E722" s="18">
         <v>1150</v>
       </c>
@@ -15815,7 +15824,9 @@
       <c r="C723" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D723" s="2"/>
+      <c r="D723" s="2">
+        <v>1493</v>
+      </c>
       <c r="E723" s="18">
         <v>1405</v>
       </c>
@@ -15833,7 +15844,9 @@
       <c r="C724" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D724" s="2"/>
+      <c r="D724" s="2">
+        <v>490</v>
+      </c>
       <c r="E724" s="18">
         <v>1200</v>
       </c>
@@ -15851,7 +15864,9 @@
       <c r="C725" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D725" s="2"/>
+      <c r="D725" s="2">
+        <v>3158.5</v>
+      </c>
       <c r="E725" s="18">
         <v>4252.5</v>
       </c>
@@ -15869,7 +15884,9 @@
       <c r="C726" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D726" s="2"/>
+      <c r="D726" s="2">
+        <v>3285.5</v>
+      </c>
       <c r="E726" s="18">
         <v>3780</v>
       </c>
@@ -15887,7 +15904,9 @@
       <c r="C727" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D727" s="2"/>
+      <c r="D727" s="2">
+        <v>1181.5</v>
+      </c>
       <c r="E727" s="18">
         <v>1417.5</v>
       </c>
@@ -15905,7 +15924,9 @@
       <c r="C728" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D728" s="2"/>
+      <c r="D728" s="2">
+        <v>2395</v>
+      </c>
       <c r="E728" s="18">
         <v>3900</v>
       </c>
@@ -15923,7 +15944,9 @@
       <c r="C729" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D729" s="2"/>
+      <c r="D729" s="2">
+        <v>2110.5</v>
+      </c>
       <c r="E729" s="18">
         <v>2600</v>
       </c>
@@ -15941,7 +15964,9 @@
       <c r="C730" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D730" s="2"/>
+      <c r="D730" s="2">
+        <v>1590.5</v>
+      </c>
       <c r="E730" s="18">
         <v>1670</v>
       </c>
@@ -15959,7 +15984,9 @@
       <c r="C731" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D731" s="32"/>
+      <c r="D731" s="32">
+        <v>1392</v>
+      </c>
       <c r="E731" s="31">
         <v>1610</v>
       </c>
@@ -15977,7 +16004,9 @@
       <c r="C732" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D732" s="2"/>
+      <c r="D732" s="2">
+        <v>769</v>
+      </c>
       <c r="E732" s="18">
         <v>1150</v>
       </c>
@@ -15995,7 +16024,9 @@
       <c r="C733" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D733" s="2"/>
+      <c r="D733" s="2">
+        <v>1538.5</v>
+      </c>
       <c r="E733" s="18">
         <v>1405</v>
       </c>
@@ -16013,7 +16044,9 @@
       <c r="C734" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D734" s="2"/>
+      <c r="D734" s="2">
+        <v>520</v>
+      </c>
       <c r="E734" s="18">
         <v>1200</v>
       </c>
@@ -16031,7 +16064,9 @@
       <c r="C735" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D735" s="2"/>
+      <c r="D735" s="2">
+        <v>3230.5</v>
+      </c>
       <c r="E735" s="18">
         <v>4252.5</v>
       </c>
@@ -16049,7 +16084,9 @@
       <c r="C736" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D736" s="2"/>
+      <c r="D736" s="2">
+        <v>3392</v>
+      </c>
       <c r="E736" s="18">
         <v>3780</v>
       </c>
@@ -16067,7 +16104,9 @@
       <c r="C737" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D737" s="2"/>
+      <c r="D737" s="2">
+        <v>1284.5</v>
+      </c>
       <c r="E737" s="18">
         <v>1417.5</v>
       </c>
@@ -16085,7 +16124,9 @@
       <c r="C738" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D738" s="2"/>
+      <c r="D738" s="2">
+        <v>2581.5</v>
+      </c>
       <c r="E738" s="18">
         <v>3900</v>
       </c>
@@ -16103,7 +16144,9 @@
       <c r="C739" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D739" s="2"/>
+      <c r="D739" s="2">
+        <v>2319.5</v>
+      </c>
       <c r="E739" s="18">
         <v>2600</v>
       </c>
@@ -16121,7 +16164,9 @@
       <c r="C740" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D740" s="2"/>
+      <c r="D740" s="2">
+        <v>1634.5</v>
+      </c>
       <c r="E740" s="18">
         <v>1670</v>
       </c>
@@ -16139,7 +16184,9 @@
       <c r="C741" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D741" s="32"/>
+      <c r="D741" s="32">
+        <v>1438.5</v>
+      </c>
       <c r="E741" s="31">
         <v>1610</v>
       </c>
@@ -16157,7 +16204,9 @@
       <c r="C742" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D742" s="2"/>
+      <c r="D742" s="2">
+        <v>810</v>
+      </c>
       <c r="E742" s="18">
         <v>1150</v>
       </c>
@@ -16175,7 +16224,9 @@
       <c r="C743" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D743" s="2"/>
+      <c r="D743" s="2">
+        <v>1585</v>
+      </c>
       <c r="E743" s="18">
         <v>1405</v>
       </c>
@@ -16193,7 +16244,9 @@
       <c r="C744" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D744" s="2"/>
+      <c r="D744" s="2">
+        <v>544</v>
+      </c>
       <c r="E744" s="18">
         <v>1200</v>
       </c>
@@ -20108,10 +20161,10 @@
       <c r="AB25" s="8"/>
       <c r="AC25" s="8"/>
       <c r="AD25" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE25" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF25" s="8">
         <v>0</v>
@@ -20188,10 +20241,10 @@
       <c r="AB26" s="8"/>
       <c r="AC26" s="8"/>
       <c r="AD26" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE26" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF26" s="8">
         <v>0</v>
@@ -20268,10 +20321,10 @@
       <c r="AB27" s="8"/>
       <c r="AC27" s="8"/>
       <c r="AD27" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE27" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF27" s="8">
         <v>0</v>
@@ -20348,10 +20401,10 @@
       <c r="AB28" s="8"/>
       <c r="AC28" s="8"/>
       <c r="AD28" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE28" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF28" s="8">
         <v>0</v>
@@ -20428,10 +20481,10 @@
       <c r="AB29" s="8"/>
       <c r="AC29" s="8"/>
       <c r="AD29" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE29" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF29" s="8">
         <v>0</v>
@@ -20508,7 +20561,7 @@
       <c r="AB30" s="8"/>
       <c r="AC30" s="8"/>
       <c r="AD30" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE30" s="8">
         <v>0</v>
@@ -20588,10 +20641,10 @@
       <c r="AB31" s="8"/>
       <c r="AC31" s="8"/>
       <c r="AD31" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE31" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF31" s="8">
         <v>0</v>
@@ -20660,7 +20713,7 @@
         <v>0</v>
       </c>
       <c r="Z32" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA32" s="8">
         <v>0</v>
@@ -20668,7 +20721,7 @@
       <c r="AB32" s="8"/>
       <c r="AC32" s="8"/>
       <c r="AD32" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE32" s="8">
         <v>0</v>
@@ -20748,10 +20801,10 @@
       <c r="AB33" s="8"/>
       <c r="AC33" s="8"/>
       <c r="AD33" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE33" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF33" s="8">
         <v>0</v>
@@ -20828,10 +20881,10 @@
       <c r="AB34" s="8"/>
       <c r="AC34" s="8"/>
       <c r="AD34" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE34" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF34" s="8">
         <v>0</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/Dados/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1407" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FEDC16F-08C2-4054-9334-823A9D93C1DA}"/>
+  <xr:revisionPtr revIDLastSave="1414" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC89C83B-7788-4583-8F87-F2426DB0A612}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20385" yWindow="-3135" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -11475,7 +11475,7 @@
         <v>46265</v>
       </c>
     </row>
-    <row r="505" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A505" s="4" t="s">
         <v>6</v>
       </c>
@@ -11495,7 +11495,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="506" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A506" s="4" t="s">
         <v>6</v>
       </c>
@@ -11515,7 +11515,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="507" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A507" s="4" t="s">
         <v>6</v>
       </c>
@@ -11535,7 +11535,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="508" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A508" s="4" t="s">
         <v>11</v>
       </c>
@@ -11555,7 +11555,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="509" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A509" s="4" t="s">
         <v>11</v>
       </c>
@@ -11575,7 +11575,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="510" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A510" s="4" t="s">
         <v>24</v>
       </c>
@@ -11595,7 +11595,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="511" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A511" s="27" t="s">
         <v>26</v>
       </c>
@@ -11615,7 +11615,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="512" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A512" s="4" t="s">
         <v>28</v>
       </c>
@@ -11635,7 +11635,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="513" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A513" s="4" t="s">
         <v>30</v>
       </c>
@@ -11655,7 +11655,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="514" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A514" s="4" t="s">
         <v>68</v>
       </c>
@@ -11675,7 +11675,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="515" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A515" s="4" t="s">
         <v>6</v>
       </c>
@@ -11695,7 +11695,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="516" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A516" s="4" t="s">
         <v>6</v>
       </c>
@@ -11715,7 +11715,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="517" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A517" s="4" t="s">
         <v>6</v>
       </c>
@@ -11735,7 +11735,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="518" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A518" s="4" t="s">
         <v>11</v>
       </c>
@@ -11755,7 +11755,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="519" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A519" s="4" t="s">
         <v>11</v>
       </c>
@@ -11775,7 +11775,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="520" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A520" s="4" t="s">
         <v>24</v>
       </c>
@@ -11795,7 +11795,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="521" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A521" s="27" t="s">
         <v>26</v>
       </c>
@@ -11815,7 +11815,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="522" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A522" s="4" t="s">
         <v>28</v>
       </c>
@@ -11835,7 +11835,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="523" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A523" s="4" t="s">
         <v>30</v>
       </c>
@@ -11855,7 +11855,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="524" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A524" s="4" t="s">
         <v>68</v>
       </c>
@@ -11875,7 +11875,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="525" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A525" s="4" t="s">
         <v>6</v>
       </c>
@@ -11895,7 +11895,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="526" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A526" s="4" t="s">
         <v>6</v>
       </c>
@@ -11915,7 +11915,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="527" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A527" s="4" t="s">
         <v>6</v>
       </c>
@@ -11935,7 +11935,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="528" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A528" s="4" t="s">
         <v>11</v>
       </c>
@@ -11955,7 +11955,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="529" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A529" s="4" t="s">
         <v>11</v>
       </c>
@@ -11975,7 +11975,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="530" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A530" s="4" t="s">
         <v>24</v>
       </c>
@@ -11995,7 +11995,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="531" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A531" s="27" t="s">
         <v>26</v>
       </c>
@@ -12015,7 +12015,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="532" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A532" s="4" t="s">
         <v>28</v>
       </c>
@@ -12035,7 +12035,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="533" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A533" s="4" t="s">
         <v>30</v>
       </c>
@@ -12055,7 +12055,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="534" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A534" s="4" t="s">
         <v>68</v>
       </c>
@@ -12075,7 +12075,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="535" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A535" s="4" t="s">
         <v>6</v>
       </c>
@@ -12095,7 +12095,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="536" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A536" s="4" t="s">
         <v>6</v>
       </c>
@@ -12115,7 +12115,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="537" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A537" s="4" t="s">
         <v>6</v>
       </c>
@@ -12135,7 +12135,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="538" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A538" s="4" t="s">
         <v>11</v>
       </c>
@@ -12155,7 +12155,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="539" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A539" s="4" t="s">
         <v>11</v>
       </c>
@@ -12175,7 +12175,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="540" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A540" s="4" t="s">
         <v>24</v>
       </c>
@@ -12195,7 +12195,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="541" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A541" s="27" t="s">
         <v>26</v>
       </c>
@@ -12215,7 +12215,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="542" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A542" s="4" t="s">
         <v>28</v>
       </c>
@@ -12235,7 +12235,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="543" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A543" s="4" t="s">
         <v>30</v>
       </c>
@@ -12255,7 +12255,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="544" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A544" s="4" t="s">
         <v>68</v>
       </c>
@@ -12275,7 +12275,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="545" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A545" s="4" t="s">
         <v>6</v>
       </c>
@@ -12295,7 +12295,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="546" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A546" s="4" t="s">
         <v>6</v>
       </c>
@@ -12315,7 +12315,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="547" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A547" s="4" t="s">
         <v>6</v>
       </c>
@@ -12335,7 +12335,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="548" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A548" s="4" t="s">
         <v>11</v>
       </c>
@@ -12355,7 +12355,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="549" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A549" s="4" t="s">
         <v>11</v>
       </c>
@@ -12375,7 +12375,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="550" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A550" s="4" t="s">
         <v>24</v>
       </c>
@@ -12395,7 +12395,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="551" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A551" s="27" t="s">
         <v>26</v>
       </c>
@@ -12415,7 +12415,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="552" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A552" s="4" t="s">
         <v>28</v>
       </c>
@@ -12435,7 +12435,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="553" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A553" s="4" t="s">
         <v>30</v>
       </c>
@@ -12455,7 +12455,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="554" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A554" s="4" t="s">
         <v>68</v>
       </c>
@@ -12475,7 +12475,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="555" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A555" s="4" t="s">
         <v>6</v>
       </c>
@@ -12495,7 +12495,7 @@
         <v>46273</v>
       </c>
     </row>
-    <row r="556" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A556" s="4" t="s">
         <v>6</v>
       </c>
@@ -12515,7 +12515,7 @@
         <v>46273</v>
       </c>
     </row>
-    <row r="557" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A557" s="4" t="s">
         <v>6</v>
       </c>
@@ -12535,7 +12535,7 @@
         <v>46273</v>
       </c>
     </row>
-    <row r="558" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A558" s="4" t="s">
         <v>11</v>
       </c>
@@ -12555,7 +12555,7 @@
         <v>46273</v>
       </c>
     </row>
-    <row r="559" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A559" s="4" t="s">
         <v>11</v>
       </c>
@@ -12575,7 +12575,7 @@
         <v>46273</v>
       </c>
     </row>
-    <row r="560" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A560" s="4" t="s">
         <v>24</v>
       </c>
@@ -12595,7 +12595,7 @@
         <v>46273</v>
       </c>
     </row>
-    <row r="561" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A561" s="27" t="s">
         <v>26</v>
       </c>
@@ -12615,7 +12615,7 @@
         <v>46273</v>
       </c>
     </row>
-    <row r="562" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A562" s="4" t="s">
         <v>28</v>
       </c>
@@ -12635,7 +12635,7 @@
         <v>46273</v>
       </c>
     </row>
-    <row r="563" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A563" s="4" t="s">
         <v>30</v>
       </c>
@@ -12655,7 +12655,7 @@
         <v>46273</v>
       </c>
     </row>
-    <row r="564" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A564" s="4" t="s">
         <v>68</v>
       </c>
@@ -12675,7 +12675,7 @@
         <v>46273</v>
       </c>
     </row>
-    <row r="565" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A565" s="4" t="s">
         <v>6</v>
       </c>
@@ -12695,7 +12695,7 @@
         <v>46274</v>
       </c>
     </row>
-    <row r="566" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A566" s="4" t="s">
         <v>6</v>
       </c>
@@ -12715,7 +12715,7 @@
         <v>46274</v>
       </c>
     </row>
-    <row r="567" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A567" s="4" t="s">
         <v>6</v>
       </c>
@@ -12735,7 +12735,7 @@
         <v>46274</v>
       </c>
     </row>
-    <row r="568" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A568" s="4" t="s">
         <v>11</v>
       </c>
@@ -12755,7 +12755,7 @@
         <v>46274</v>
       </c>
     </row>
-    <row r="569" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A569" s="4" t="s">
         <v>11</v>
       </c>
@@ -12775,7 +12775,7 @@
         <v>46274</v>
       </c>
     </row>
-    <row r="570" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A570" s="4" t="s">
         <v>24</v>
       </c>
@@ -12795,7 +12795,7 @@
         <v>46274</v>
       </c>
     </row>
-    <row r="571" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A571" s="27" t="s">
         <v>26</v>
       </c>
@@ -12815,7 +12815,7 @@
         <v>46274</v>
       </c>
     </row>
-    <row r="572" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A572" s="4" t="s">
         <v>28</v>
       </c>
@@ -12835,7 +12835,7 @@
         <v>46274</v>
       </c>
     </row>
-    <row r="573" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A573" s="4" t="s">
         <v>30</v>
       </c>
@@ -12855,7 +12855,7 @@
         <v>46274</v>
       </c>
     </row>
-    <row r="574" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A574" s="4" t="s">
         <v>68</v>
       </c>
@@ -12875,7 +12875,7 @@
         <v>46274</v>
       </c>
     </row>
-    <row r="575" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A575" s="4" t="s">
         <v>6</v>
       </c>
@@ -12895,7 +12895,7 @@
         <v>46275</v>
       </c>
     </row>
-    <row r="576" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A576" s="4" t="s">
         <v>6</v>
       </c>
@@ -12915,7 +12915,7 @@
         <v>46275</v>
       </c>
     </row>
-    <row r="577" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A577" s="4" t="s">
         <v>6</v>
       </c>
@@ -12935,7 +12935,7 @@
         <v>46275</v>
       </c>
     </row>
-    <row r="578" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A578" s="4" t="s">
         <v>11</v>
       </c>
@@ -12955,7 +12955,7 @@
         <v>46275</v>
       </c>
     </row>
-    <row r="579" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A579" s="4" t="s">
         <v>11</v>
       </c>
@@ -12975,7 +12975,7 @@
         <v>46275</v>
       </c>
     </row>
-    <row r="580" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A580" s="4" t="s">
         <v>24</v>
       </c>
@@ -12995,7 +12995,7 @@
         <v>46275</v>
       </c>
     </row>
-    <row r="581" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A581" s="27" t="s">
         <v>26</v>
       </c>
@@ -13015,7 +13015,7 @@
         <v>46275</v>
       </c>
     </row>
-    <row r="582" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A582" s="4" t="s">
         <v>28</v>
       </c>
@@ -13035,7 +13035,7 @@
         <v>46275</v>
       </c>
     </row>
-    <row r="583" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A583" s="4" t="s">
         <v>30</v>
       </c>
@@ -13055,7 +13055,7 @@
         <v>46275</v>
       </c>
     </row>
-    <row r="584" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A584" s="4" t="s">
         <v>68</v>
       </c>
@@ -13075,7 +13075,7 @@
         <v>46275</v>
       </c>
     </row>
-    <row r="585" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A585" s="4" t="s">
         <v>6</v>
       </c>
@@ -13095,7 +13095,7 @@
         <v>46276</v>
       </c>
     </row>
-    <row r="586" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A586" s="4" t="s">
         <v>6</v>
       </c>
@@ -13115,7 +13115,7 @@
         <v>46276</v>
       </c>
     </row>
-    <row r="587" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A587" s="4" t="s">
         <v>6</v>
       </c>
@@ -13135,7 +13135,7 @@
         <v>46276</v>
       </c>
     </row>
-    <row r="588" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A588" s="4" t="s">
         <v>11</v>
       </c>
@@ -13155,7 +13155,7 @@
         <v>46276</v>
       </c>
     </row>
-    <row r="589" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A589" s="4" t="s">
         <v>11</v>
       </c>
@@ -13175,7 +13175,7 @@
         <v>46276</v>
       </c>
     </row>
-    <row r="590" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A590" s="4" t="s">
         <v>24</v>
       </c>
@@ -13195,7 +13195,7 @@
         <v>46276</v>
       </c>
     </row>
-    <row r="591" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A591" s="27" t="s">
         <v>26</v>
       </c>
@@ -13215,7 +13215,7 @@
         <v>46276</v>
       </c>
     </row>
-    <row r="592" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A592" s="4" t="s">
         <v>28</v>
       </c>
@@ -13235,7 +13235,7 @@
         <v>46276</v>
       </c>
     </row>
-    <row r="593" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A593" s="4" t="s">
         <v>30</v>
       </c>
@@ -13255,7 +13255,7 @@
         <v>46276</v>
       </c>
     </row>
-    <row r="594" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A594" s="4" t="s">
         <v>68</v>
       </c>
@@ -13275,7 +13275,7 @@
         <v>46276</v>
       </c>
     </row>
-    <row r="595" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A595" s="4" t="s">
         <v>6</v>
       </c>
@@ -13295,7 +13295,7 @@
         <v>46277</v>
       </c>
     </row>
-    <row r="596" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A596" s="4" t="s">
         <v>6</v>
       </c>
@@ -13315,7 +13315,7 @@
         <v>46277</v>
       </c>
     </row>
-    <row r="597" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A597" s="4" t="s">
         <v>6</v>
       </c>
@@ -13335,7 +13335,7 @@
         <v>46277</v>
       </c>
     </row>
-    <row r="598" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A598" s="4" t="s">
         <v>11</v>
       </c>
@@ -13355,7 +13355,7 @@
         <v>46277</v>
       </c>
     </row>
-    <row r="599" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A599" s="4" t="s">
         <v>11</v>
       </c>
@@ -13375,7 +13375,7 @@
         <v>46277</v>
       </c>
     </row>
-    <row r="600" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A600" s="4" t="s">
         <v>24</v>
       </c>
@@ -13395,7 +13395,7 @@
         <v>46277</v>
       </c>
     </row>
-    <row r="601" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A601" s="27" t="s">
         <v>26</v>
       </c>
@@ -13415,7 +13415,7 @@
         <v>46277</v>
       </c>
     </row>
-    <row r="602" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A602" s="4" t="s">
         <v>28</v>
       </c>
@@ -13435,7 +13435,7 @@
         <v>46277</v>
       </c>
     </row>
-    <row r="603" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A603" s="4" t="s">
         <v>30</v>
       </c>
@@ -13455,7 +13455,7 @@
         <v>46277</v>
       </c>
     </row>
-    <row r="604" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A604" s="4" t="s">
         <v>68</v>
       </c>
@@ -13475,7 +13475,7 @@
         <v>46277</v>
       </c>
     </row>
-    <row r="605" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A605" s="4" t="s">
         <v>6</v>
       </c>
@@ -13495,7 +13495,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="606" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A606" s="4" t="s">
         <v>6</v>
       </c>
@@ -13515,7 +13515,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="607" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A607" s="4" t="s">
         <v>6</v>
       </c>
@@ -13535,7 +13535,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="608" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A608" s="4" t="s">
         <v>11</v>
       </c>
@@ -13555,7 +13555,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="609" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A609" s="4" t="s">
         <v>11</v>
       </c>
@@ -13575,7 +13575,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="610" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A610" s="4" t="s">
         <v>24</v>
       </c>
@@ -13595,7 +13595,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="611" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A611" s="27" t="s">
         <v>26</v>
       </c>
@@ -13615,7 +13615,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="612" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A612" s="4" t="s">
         <v>28</v>
       </c>
@@ -13635,7 +13635,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="613" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A613" s="4" t="s">
         <v>30</v>
       </c>
@@ -13655,7 +13655,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="614" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A614" s="4" t="s">
         <v>68</v>
       </c>
@@ -13675,7 +13675,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="615" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A615" s="4" t="s">
         <v>6</v>
       </c>
@@ -13695,7 +13695,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="616" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A616" s="4" t="s">
         <v>6</v>
       </c>
@@ -13715,7 +13715,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="617" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A617" s="4" t="s">
         <v>6</v>
       </c>
@@ -13735,7 +13735,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="618" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A618" s="4" t="s">
         <v>11</v>
       </c>
@@ -13755,7 +13755,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="619" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A619" s="4" t="s">
         <v>11</v>
       </c>
@@ -13775,7 +13775,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="620" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A620" s="4" t="s">
         <v>24</v>
       </c>
@@ -13795,7 +13795,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="621" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A621" s="27" t="s">
         <v>26</v>
       </c>
@@ -13815,7 +13815,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="622" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A622" s="4" t="s">
         <v>28</v>
       </c>
@@ -13835,7 +13835,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="623" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A623" s="4" t="s">
         <v>30</v>
       </c>
@@ -13855,7 +13855,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="624" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A624" s="4" t="s">
         <v>68</v>
       </c>
@@ -13875,7 +13875,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="625" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A625" s="4" t="s">
         <v>6</v>
       </c>
@@ -13895,7 +13895,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="626" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A626" s="4" t="s">
         <v>6</v>
       </c>
@@ -13915,7 +13915,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="627" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A627" s="4" t="s">
         <v>6</v>
       </c>
@@ -13935,7 +13935,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="628" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A628" s="4" t="s">
         <v>11</v>
       </c>
@@ -13955,7 +13955,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="629" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A629" s="4" t="s">
         <v>11</v>
       </c>
@@ -13975,7 +13975,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="630" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A630" s="4" t="s">
         <v>24</v>
       </c>
@@ -13995,7 +13995,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="631" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A631" s="27" t="s">
         <v>26</v>
       </c>
@@ -14015,7 +14015,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="632" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A632" s="4" t="s">
         <v>28</v>
       </c>
@@ -14035,7 +14035,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="633" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A633" s="4" t="s">
         <v>30</v>
       </c>
@@ -14055,7 +14055,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="634" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A634" s="4" t="s">
         <v>68</v>
       </c>
@@ -14075,7 +14075,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="635" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A635" s="4" t="s">
         <v>6</v>
       </c>
@@ -14095,7 +14095,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="636" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A636" s="4" t="s">
         <v>6</v>
       </c>
@@ -14115,7 +14115,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="637" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A637" s="4" t="s">
         <v>6</v>
       </c>
@@ -14135,7 +14135,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="638" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A638" s="4" t="s">
         <v>11</v>
       </c>
@@ -14155,7 +14155,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="639" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A639" s="4" t="s">
         <v>11</v>
       </c>
@@ -14175,7 +14175,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="640" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A640" s="4" t="s">
         <v>24</v>
       </c>
@@ -14195,7 +14195,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="641" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A641" s="27" t="s">
         <v>26</v>
       </c>
@@ -14215,7 +14215,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="642" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A642" s="4" t="s">
         <v>28</v>
       </c>
@@ -14235,7 +14235,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="643" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A643" s="4" t="s">
         <v>30</v>
       </c>
@@ -14255,7 +14255,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="644" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A644" s="4" t="s">
         <v>68</v>
       </c>
@@ -14275,7 +14275,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="645" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A645" s="4" t="s">
         <v>6</v>
       </c>
@@ -14295,7 +14295,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="646" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A646" s="4" t="s">
         <v>6</v>
       </c>
@@ -14315,7 +14315,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="647" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A647" s="4" t="s">
         <v>6</v>
       </c>
@@ -14335,7 +14335,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="648" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A648" s="4" t="s">
         <v>11</v>
       </c>
@@ -14355,7 +14355,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="649" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A649" s="4" t="s">
         <v>11</v>
       </c>
@@ -14375,7 +14375,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="650" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A650" s="4" t="s">
         <v>24</v>
       </c>
@@ -14395,7 +14395,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="651" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A651" s="27" t="s">
         <v>26</v>
       </c>
@@ -14415,7 +14415,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="652" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A652" s="4" t="s">
         <v>28</v>
       </c>
@@ -14435,7 +14435,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="653" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A653" s="4" t="s">
         <v>30</v>
       </c>
@@ -14455,7 +14455,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="654" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A654" s="4" t="s">
         <v>68</v>
       </c>
@@ -14475,7 +14475,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="655" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A655" s="4" t="s">
         <v>6</v>
       </c>
@@ -14495,7 +14495,7 @@
         <v>46284</v>
       </c>
     </row>
-    <row r="656" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A656" s="4" t="s">
         <v>6</v>
       </c>
@@ -14515,7 +14515,7 @@
         <v>46284</v>
       </c>
     </row>
-    <row r="657" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A657" s="4" t="s">
         <v>6</v>
       </c>
@@ -14535,7 +14535,7 @@
         <v>46284</v>
       </c>
     </row>
-    <row r="658" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A658" s="4" t="s">
         <v>11</v>
       </c>
@@ -14555,7 +14555,7 @@
         <v>46284</v>
       </c>
     </row>
-    <row r="659" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A659" s="4" t="s">
         <v>11</v>
       </c>
@@ -14575,7 +14575,7 @@
         <v>46284</v>
       </c>
     </row>
-    <row r="660" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A660" s="4" t="s">
         <v>24</v>
       </c>
@@ -14595,7 +14595,7 @@
         <v>46284</v>
       </c>
     </row>
-    <row r="661" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A661" s="27" t="s">
         <v>26</v>
       </c>
@@ -14615,7 +14615,7 @@
         <v>46284</v>
       </c>
     </row>
-    <row r="662" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A662" s="4" t="s">
         <v>28</v>
       </c>
@@ -14635,7 +14635,7 @@
         <v>46284</v>
       </c>
     </row>
-    <row r="663" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A663" s="4" t="s">
         <v>30</v>
       </c>
@@ -14655,7 +14655,7 @@
         <v>46284</v>
       </c>
     </row>
-    <row r="664" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A664" s="4" t="s">
         <v>68</v>
       </c>
@@ -14675,7 +14675,7 @@
         <v>46284</v>
       </c>
     </row>
-    <row r="665" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A665" s="4" t="s">
         <v>6</v>
       </c>
@@ -14695,7 +14695,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="666" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A666" s="4" t="s">
         <v>6</v>
       </c>
@@ -14715,7 +14715,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="667" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A667" s="4" t="s">
         <v>6</v>
       </c>
@@ -14735,7 +14735,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="668" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A668" s="4" t="s">
         <v>11</v>
       </c>
@@ -14755,7 +14755,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="669" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A669" s="4" t="s">
         <v>11</v>
       </c>
@@ -14775,7 +14775,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="670" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A670" s="4" t="s">
         <v>24</v>
       </c>
@@ -14795,7 +14795,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="671" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A671" s="27" t="s">
         <v>26</v>
       </c>
@@ -14815,7 +14815,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="672" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A672" s="4" t="s">
         <v>28</v>
       </c>
@@ -14835,7 +14835,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="673" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A673" s="4" t="s">
         <v>30</v>
       </c>
@@ -14855,7 +14855,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="674" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A674" s="4" t="s">
         <v>68</v>
       </c>
@@ -14875,7 +14875,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="675" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A675" s="4" t="s">
         <v>6</v>
       </c>
@@ -14895,7 +14895,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="676" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A676" s="4" t="s">
         <v>6</v>
       </c>
@@ -14915,7 +14915,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="677" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A677" s="4" t="s">
         <v>6</v>
       </c>
@@ -14935,7 +14935,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="678" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A678" s="4" t="s">
         <v>11</v>
       </c>
@@ -14955,7 +14955,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="679" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A679" s="4" t="s">
         <v>11</v>
       </c>
@@ -14975,7 +14975,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="680" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A680" s="4" t="s">
         <v>24</v>
       </c>
@@ -14995,7 +14995,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="681" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A681" s="27" t="s">
         <v>26</v>
       </c>
@@ -15015,7 +15015,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="682" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A682" s="4" t="s">
         <v>28</v>
       </c>
@@ -15035,7 +15035,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="683" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A683" s="4" t="s">
         <v>30</v>
       </c>
@@ -15055,7 +15055,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="684" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A684" s="4" t="s">
         <v>68</v>
       </c>
@@ -15075,7 +15075,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="685" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A685" s="4" t="s">
         <v>6</v>
       </c>
@@ -15095,7 +15095,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="686" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A686" s="4" t="s">
         <v>6</v>
       </c>
@@ -15115,7 +15115,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="687" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A687" s="4" t="s">
         <v>6</v>
       </c>
@@ -15135,7 +15135,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="688" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A688" s="4" t="s">
         <v>11</v>
       </c>
@@ -15155,7 +15155,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="689" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A689" s="4" t="s">
         <v>11</v>
       </c>
@@ -15175,7 +15175,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="690" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A690" s="4" t="s">
         <v>24</v>
       </c>
@@ -15195,7 +15195,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="691" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A691" s="27" t="s">
         <v>26</v>
       </c>
@@ -15215,7 +15215,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="692" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A692" s="4" t="s">
         <v>28</v>
       </c>
@@ -15235,7 +15235,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="693" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A693" s="4" t="s">
         <v>30</v>
       </c>
@@ -15255,7 +15255,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="694" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A694" s="4" t="s">
         <v>68</v>
       </c>
@@ -15275,7 +15275,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="695" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A695" s="4" t="s">
         <v>6</v>
       </c>
@@ -15295,7 +15295,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="696" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A696" s="4" t="s">
         <v>6</v>
       </c>
@@ -15315,7 +15315,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="697" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A697" s="4" t="s">
         <v>6</v>
       </c>
@@ -15335,7 +15335,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="698" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A698" s="4" t="s">
         <v>11</v>
       </c>
@@ -15355,7 +15355,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="699" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A699" s="4" t="s">
         <v>11</v>
       </c>
@@ -15375,7 +15375,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="700" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A700" s="4" t="s">
         <v>24</v>
       </c>
@@ -15395,7 +15395,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="701" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A701" s="27" t="s">
         <v>26</v>
       </c>
@@ -15415,7 +15415,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="702" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A702" s="4" t="s">
         <v>28</v>
       </c>
@@ -15435,7 +15435,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="703" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A703" s="4" t="s">
         <v>30</v>
       </c>
@@ -15455,7 +15455,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="704" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A704" s="4" t="s">
         <v>68</v>
       </c>
@@ -15475,7 +15475,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="705" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A705" s="4" t="s">
         <v>6</v>
       </c>
@@ -15495,7 +15495,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="706" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A706" s="4" t="s">
         <v>6</v>
       </c>
@@ -15515,7 +15515,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="707" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A707" s="4" t="s">
         <v>6</v>
       </c>
@@ -15535,7 +15535,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="708" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A708" s="4" t="s">
         <v>11</v>
       </c>
@@ -15555,7 +15555,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="709" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A709" s="4" t="s">
         <v>11</v>
       </c>
@@ -15575,7 +15575,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="710" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A710" s="4" t="s">
         <v>24</v>
       </c>
@@ -15595,7 +15595,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="711" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A711" s="27" t="s">
         <v>26</v>
       </c>
@@ -15615,7 +15615,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="712" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A712" s="4" t="s">
         <v>28</v>
       </c>
@@ -15635,7 +15635,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="713" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A713" s="4" t="s">
         <v>30</v>
       </c>
@@ -15655,7 +15655,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="714" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A714" s="4" t="s">
         <v>68</v>
       </c>
@@ -15675,7 +15675,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="715" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A715" s="4" t="s">
         <v>6</v>
       </c>
@@ -15695,7 +15695,7 @@
         <v>46291</v>
       </c>
     </row>
-    <row r="716" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A716" s="4" t="s">
         <v>6</v>
       </c>
@@ -15715,7 +15715,7 @@
         <v>46291</v>
       </c>
     </row>
-    <row r="717" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A717" s="4" t="s">
         <v>6</v>
       </c>
@@ -15735,7 +15735,7 @@
         <v>46291</v>
       </c>
     </row>
-    <row r="718" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A718" s="4" t="s">
         <v>11</v>
       </c>
@@ -15755,7 +15755,7 @@
         <v>46291</v>
       </c>
     </row>
-    <row r="719" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A719" s="4" t="s">
         <v>11</v>
       </c>
@@ -15775,7 +15775,7 @@
         <v>46291</v>
       </c>
     </row>
-    <row r="720" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A720" s="4" t="s">
         <v>24</v>
       </c>
@@ -15795,7 +15795,7 @@
         <v>46291</v>
       </c>
     </row>
-    <row r="721" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A721" s="27" t="s">
         <v>26</v>
       </c>
@@ -15815,7 +15815,7 @@
         <v>46291</v>
       </c>
     </row>
-    <row r="722" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A722" s="4" t="s">
         <v>28</v>
       </c>
@@ -15835,7 +15835,7 @@
         <v>46291</v>
       </c>
     </row>
-    <row r="723" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A723" s="4" t="s">
         <v>30</v>
       </c>
@@ -15855,7 +15855,7 @@
         <v>46291</v>
       </c>
     </row>
-    <row r="724" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A724" s="4" t="s">
         <v>68</v>
       </c>
@@ -15875,7 +15875,7 @@
         <v>46291</v>
       </c>
     </row>
-    <row r="725" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A725" s="4" t="s">
         <v>6</v>
       </c>
@@ -15895,7 +15895,7 @@
         <v>46293</v>
       </c>
     </row>
-    <row r="726" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A726" s="4" t="s">
         <v>6</v>
       </c>
@@ -15915,7 +15915,7 @@
         <v>46293</v>
       </c>
     </row>
-    <row r="727" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A727" s="4" t="s">
         <v>6</v>
       </c>
@@ -15935,7 +15935,7 @@
         <v>46293</v>
       </c>
     </row>
-    <row r="728" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A728" s="4" t="s">
         <v>11</v>
       </c>
@@ -15955,7 +15955,7 @@
         <v>46293</v>
       </c>
     </row>
-    <row r="729" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A729" s="4" t="s">
         <v>11</v>
       </c>
@@ -15975,7 +15975,7 @@
         <v>46293</v>
       </c>
     </row>
-    <row r="730" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A730" s="4" t="s">
         <v>24</v>
       </c>
@@ -15995,7 +15995,7 @@
         <v>46293</v>
       </c>
     </row>
-    <row r="731" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A731" s="27" t="s">
         <v>26</v>
       </c>
@@ -16015,7 +16015,7 @@
         <v>46293</v>
       </c>
     </row>
-    <row r="732" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A732" s="4" t="s">
         <v>28</v>
       </c>
@@ -16035,7 +16035,7 @@
         <v>46293</v>
       </c>
     </row>
-    <row r="733" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A733" s="4" t="s">
         <v>30</v>
       </c>
@@ -16055,7 +16055,7 @@
         <v>46293</v>
       </c>
     </row>
-    <row r="734" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A734" s="4" t="s">
         <v>68</v>
       </c>
@@ -16075,7 +16075,7 @@
         <v>46293</v>
       </c>
     </row>
-    <row r="735" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A735" s="4" t="s">
         <v>6</v>
       </c>
@@ -16095,7 +16095,7 @@
         <v>46294</v>
       </c>
     </row>
-    <row r="736" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A736" s="4" t="s">
         <v>6</v>
       </c>
@@ -16115,7 +16115,7 @@
         <v>46294</v>
       </c>
     </row>
-    <row r="737" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A737" s="4" t="s">
         <v>6</v>
       </c>
@@ -16135,7 +16135,7 @@
         <v>46294</v>
       </c>
     </row>
-    <row r="738" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A738" s="4" t="s">
         <v>11</v>
       </c>
@@ -16155,7 +16155,7 @@
         <v>46294</v>
       </c>
     </row>
-    <row r="739" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A739" s="4" t="s">
         <v>11</v>
       </c>
@@ -16175,7 +16175,7 @@
         <v>46294</v>
       </c>
     </row>
-    <row r="740" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A740" s="4" t="s">
         <v>24</v>
       </c>
@@ -16195,7 +16195,7 @@
         <v>46294</v>
       </c>
     </row>
-    <row r="741" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A741" s="27" t="s">
         <v>26</v>
       </c>
@@ -16215,7 +16215,7 @@
         <v>46294</v>
       </c>
     </row>
-    <row r="742" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A742" s="4" t="s">
         <v>28</v>
       </c>
@@ -16235,7 +16235,7 @@
         <v>46294</v>
       </c>
     </row>
-    <row r="743" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A743" s="4" t="s">
         <v>30</v>
       </c>
@@ -16255,7 +16255,7 @@
         <v>46294</v>
       </c>
     </row>
-    <row r="744" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A744" s="4" t="s">
         <v>68</v>
       </c>
@@ -16275,7 +16275,7 @@
         <v>46294</v>
       </c>
     </row>
-    <row r="745" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A745" s="4" t="s">
         <v>6</v>
       </c>
@@ -16295,7 +16295,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="746" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A746" s="4" t="s">
         <v>6</v>
       </c>
@@ -16315,7 +16315,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="747" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A747" s="4" t="s">
         <v>6</v>
       </c>
@@ -16335,7 +16335,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="748" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A748" s="4" t="s">
         <v>11</v>
       </c>
@@ -16355,7 +16355,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="749" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A749" s="4" t="s">
         <v>11</v>
       </c>
@@ -16375,7 +16375,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="750" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A750" s="4" t="s">
         <v>24</v>
       </c>
@@ -16395,7 +16395,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="751" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A751" s="27" t="s">
         <v>26</v>
       </c>
@@ -16406,7 +16406,7 @@
         <v>25</v>
       </c>
       <c r="D751" s="32">
-        <v>810</v>
+        <v>1478</v>
       </c>
       <c r="E751" s="31">
         <v>1610</v>
@@ -16415,7 +16415,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="752" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A752" s="4" t="s">
         <v>28</v>
       </c>
@@ -16426,7 +16426,7 @@
         <v>27</v>
       </c>
       <c r="D752" s="2">
-        <v>1478.5</v>
+        <v>810</v>
       </c>
       <c r="E752" s="18">
         <v>1150</v>
@@ -16435,7 +16435,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="753" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A753" s="4" t="s">
         <v>30</v>
       </c>
@@ -16455,7 +16455,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="754" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A754" s="4" t="s">
         <v>68</v>
       </c>
@@ -21124,6 +21124,7 @@
   <autoFilter ref="A1:F1024" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="5">
       <filters>
+        <dateGroupItem year="2026" month="9" dateTimeGrouping="month"/>
         <dateGroupItem year="2026" month="10" dateTimeGrouping="month"/>
       </filters>
     </filterColumn>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/Dados/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1414" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC89C83B-7788-4583-8F87-F2426DB0A612}"/>
+  <xr:revisionPtr revIDLastSave="1466" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B17F7B33-1B61-4F54-9400-15763C7C9989}"/>
   <bookViews>
-    <workbookView xWindow="20385" yWindow="-3135" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -16485,6 +16485,9 @@
       <c r="C755" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="D755" s="6">
+        <v>109</v>
+      </c>
       <c r="E755" s="18">
         <v>1029.375</v>
       </c>
@@ -16507,6 +16510,9 @@
       <c r="C756" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="D756" s="6">
+        <v>275</v>
+      </c>
       <c r="E756" s="18">
         <v>915</v>
       </c>
@@ -16529,6 +16535,9 @@
       <c r="C757" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="D757" s="6">
+        <v>8</v>
+      </c>
       <c r="E757" s="18">
         <v>343.125</v>
       </c>
@@ -16551,6 +16560,9 @@
       <c r="C758" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="D758" s="6">
+        <v>100</v>
+      </c>
       <c r="E758" s="18">
         <v>862.5</v>
       </c>
@@ -16573,6 +16585,9 @@
       <c r="C759" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D759" s="6">
+        <v>74.5</v>
+      </c>
       <c r="E759" s="18">
         <v>575</v>
       </c>
@@ -16595,6 +16610,9 @@
       <c r="C760" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="D760" s="6">
+        <v>30.5</v>
+      </c>
       <c r="E760" s="18">
         <v>375</v>
       </c>
@@ -16617,6 +16635,9 @@
       <c r="C761" s="27" t="s">
         <v>25</v>
       </c>
+      <c r="D761" s="6">
+        <v>80.5</v>
+      </c>
       <c r="E761" s="18">
         <v>377.5</v>
       </c>
@@ -16639,6 +16660,9 @@
       <c r="C762" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="D762" s="6">
+        <v>13.5</v>
+      </c>
       <c r="E762" s="18">
         <v>250</v>
       </c>
@@ -16661,6 +16685,9 @@
       <c r="C763" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="D763" s="6">
+        <v>0</v>
+      </c>
       <c r="E763" s="18">
         <v>326.25</v>
       </c>
@@ -16683,6 +16710,9 @@
       <c r="C764" s="4" t="s">
         <v>70</v>
       </c>
+      <c r="D764" s="6">
+        <v>0</v>
+      </c>
       <c r="E764" s="18">
         <v>200</v>
       </c>
@@ -16705,6 +16735,9 @@
       <c r="C765" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="D765" s="6">
+        <v>245</v>
+      </c>
       <c r="E765" s="18">
         <v>1029.375</v>
       </c>
@@ -16727,6 +16760,9 @@
       <c r="C766" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="D766" s="6">
+        <v>353</v>
+      </c>
       <c r="E766" s="18">
         <v>915</v>
       </c>
@@ -16743,6 +16779,9 @@
       </c>
       <c r="C767" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="D767" s="6">
+        <v>79.5</v>
       </c>
       <c r="E767" s="18">
         <v>343.125</v>
@@ -16761,6 +16800,9 @@
       <c r="C768" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="D768" s="6">
+        <v>316.5</v>
+      </c>
       <c r="E768" s="18">
         <v>862.5</v>
       </c>
@@ -16778,6 +16820,9 @@
       <c r="C769" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D769" s="6">
+        <v>202.5</v>
+      </c>
       <c r="E769" s="18">
         <v>575</v>
       </c>
@@ -16795,6 +16840,9 @@
       <c r="C770" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="D770" s="6">
+        <v>102.5</v>
+      </c>
       <c r="E770" s="18">
         <v>375</v>
       </c>
@@ -16812,6 +16860,9 @@
       <c r="C771" s="27" t="s">
         <v>25</v>
       </c>
+      <c r="D771" s="6">
+        <v>173.5</v>
+      </c>
       <c r="E771" s="18">
         <v>377.5</v>
       </c>
@@ -16829,6 +16880,9 @@
       <c r="C772" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="D772" s="6">
+        <v>63.5</v>
+      </c>
       <c r="E772" s="18">
         <v>250</v>
       </c>
@@ -16846,6 +16900,9 @@
       <c r="C773" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="D773" s="6">
+        <v>50.5</v>
+      </c>
       <c r="E773" s="18">
         <v>326.25</v>
       </c>
@@ -16863,6 +16920,9 @@
       <c r="C774" s="4" t="s">
         <v>70</v>
       </c>
+      <c r="D774" s="6">
+        <v>45</v>
+      </c>
       <c r="E774" s="18">
         <v>200</v>
       </c>
@@ -16880,6 +16940,9 @@
       <c r="C775" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="D775" s="6">
+        <v>302</v>
+      </c>
       <c r="E775" s="18">
         <v>1029.375</v>
       </c>
@@ -16897,6 +16960,9 @@
       <c r="C776" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="D776" s="6">
+        <v>361</v>
+      </c>
       <c r="E776" s="18">
         <v>915</v>
       </c>
@@ -16913,6 +16979,9 @@
       </c>
       <c r="C777" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="D777" s="6">
+        <v>87.5</v>
       </c>
       <c r="E777" s="18">
         <v>343.125</v>
@@ -16931,6 +17000,9 @@
       <c r="C778" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="D778" s="6">
+        <v>375.5</v>
+      </c>
       <c r="E778" s="18">
         <v>862.5</v>
       </c>
@@ -16948,6 +17020,9 @@
       <c r="C779" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D779" s="6">
+        <v>299</v>
+      </c>
       <c r="E779" s="18">
         <v>575</v>
       </c>
@@ -16965,6 +17040,9 @@
       <c r="C780" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="D780" s="6">
+        <v>121</v>
+      </c>
       <c r="E780" s="18">
         <v>375</v>
       </c>
@@ -16982,6 +17060,9 @@
       <c r="C781" s="27" t="s">
         <v>25</v>
       </c>
+      <c r="D781" s="6">
+        <v>173.5</v>
+      </c>
       <c r="E781" s="18">
         <v>377.5</v>
       </c>
@@ -16999,6 +17080,9 @@
       <c r="C782" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="D782" s="6">
+        <v>63.5</v>
+      </c>
       <c r="E782" s="18">
         <v>250</v>
       </c>
@@ -17016,6 +17100,9 @@
       <c r="C783" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="D783" s="6">
+        <v>95.5</v>
+      </c>
       <c r="E783" s="18">
         <v>326.25</v>
       </c>
@@ -17032,6 +17119,9 @@
       </c>
       <c r="C784" s="4" t="s">
         <v>70</v>
+      </c>
+      <c r="D784" s="6">
+        <v>45</v>
       </c>
       <c r="E784" s="18">
         <v>200</v>
@@ -25247,7 +25337,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G36" s="6">
         <v>0</v>
@@ -25321,7 +25411,7 @@
         <v>0</v>
       </c>
       <c r="D37" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G37" s="6">
         <v>0</v>
@@ -25392,10 +25482,10 @@
         <v>23</v>
       </c>
       <c r="C38" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D38" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" s="6">
         <v>0</v>
@@ -25469,7 +25559,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" s="6">
         <v>0</v>
@@ -25540,7 +25630,7 @@
         <v>9</v>
       </c>
       <c r="C40" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40" s="6">
         <v>0</v>
@@ -25617,7 +25707,7 @@
         <v>0</v>
       </c>
       <c r="D41" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" s="6">
         <v>0</v>
@@ -25691,7 +25781,7 @@
         <v>0</v>
       </c>
       <c r="D42" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" s="6">
         <v>0</v>
@@ -25836,10 +25926,10 @@
         <v>13</v>
       </c>
       <c r="C44" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" s="6">
         <v>0</v>
@@ -25910,10 +26000,10 @@
         <v>67</v>
       </c>
       <c r="C45" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G45" s="6">
         <v>0</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/Dados/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1466" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B17F7B33-1B61-4F54-9400-15763C7C9989}"/>
+  <xr:revisionPtr revIDLastSave="1481" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FB8B3C6-35F2-4DBF-B130-4CDE323B9361}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17140,6 +17140,9 @@
       <c r="C785" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="D785" s="6">
+        <v>434</v>
+      </c>
       <c r="E785" s="18">
         <v>1029.375</v>
       </c>
@@ -17157,6 +17160,9 @@
       <c r="C786" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="D786" s="6">
+        <v>800</v>
+      </c>
       <c r="E786" s="18">
         <v>915</v>
       </c>
@@ -17173,6 +17179,9 @@
       </c>
       <c r="C787" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="D787" s="6">
+        <v>116.5</v>
       </c>
       <c r="E787" s="18">
         <v>343.125</v>
@@ -17191,6 +17200,9 @@
       <c r="C788" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="D788" s="6">
+        <v>461</v>
+      </c>
       <c r="E788" s="18">
         <v>862.5</v>
       </c>
@@ -17208,6 +17220,9 @@
       <c r="C789" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D789" s="6">
+        <v>355.5</v>
+      </c>
       <c r="E789" s="18">
         <v>575</v>
       </c>
@@ -17225,6 +17240,9 @@
       <c r="C790" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="D790" s="6">
+        <v>139</v>
+      </c>
       <c r="E790" s="18">
         <v>375</v>
       </c>
@@ -17242,6 +17260,9 @@
       <c r="C791" s="27" t="s">
         <v>25</v>
       </c>
+      <c r="D791" s="6">
+        <v>220.5</v>
+      </c>
       <c r="E791" s="18">
         <v>377.5</v>
       </c>
@@ -17259,6 +17280,9 @@
       <c r="C792" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="D792" s="6">
+        <v>102.5</v>
+      </c>
       <c r="E792" s="18">
         <v>250</v>
       </c>
@@ -17276,6 +17300,9 @@
       <c r="C793" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="D793" s="6">
+        <v>169</v>
+      </c>
       <c r="E793" s="18">
         <v>326.25</v>
       </c>
@@ -17292,6 +17319,9 @@
       </c>
       <c r="C794" s="4" t="s">
         <v>70</v>
+      </c>
+      <c r="D794" s="6">
+        <v>45</v>
       </c>
       <c r="E794" s="18">
         <v>200</v>
@@ -25340,7 +25370,7 @@
         <v>2</v>
       </c>
       <c r="G36" s="6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H36" s="6">
         <v>0</v>
@@ -25636,7 +25666,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" s="6">
         <v>0</v>
@@ -25710,7 +25740,7 @@
         <v>1</v>
       </c>
       <c r="G41" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="6">
         <v>0</v>
@@ -25784,7 +25814,7 @@
         <v>1</v>
       </c>
       <c r="G42" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" s="6">
         <v>0</v>
@@ -25932,7 +25962,7 @@
         <v>1</v>
       </c>
       <c r="G44" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" s="6">
         <v>0</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/Dados/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1481" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FB8B3C6-35F2-4DBF-B130-4CDE323B9361}"/>
+  <xr:revisionPtr revIDLastSave="1499" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DE8A15B-28A4-4D49-9546-42D9D718C0CB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17340,6 +17340,9 @@
       <c r="C795" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="D795" s="6">
+        <v>506</v>
+      </c>
       <c r="E795" s="18">
         <v>1029.375</v>
       </c>
@@ -17357,6 +17360,9 @@
       <c r="C796" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="D796" s="6">
+        <v>965</v>
+      </c>
       <c r="E796" s="18">
         <v>915</v>
       </c>
@@ -17373,6 +17379,9 @@
       </c>
       <c r="C797" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="D797" s="6">
+        <v>116.5</v>
       </c>
       <c r="E797" s="18">
         <v>343.125</v>
@@ -17391,6 +17400,9 @@
       <c r="C798" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="D798" s="6">
+        <v>486.5</v>
+      </c>
       <c r="E798" s="18">
         <v>862.5</v>
       </c>
@@ -17408,6 +17420,9 @@
       <c r="C799" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D799" s="6">
+        <v>405.5</v>
+      </c>
       <c r="E799" s="18">
         <v>575</v>
       </c>
@@ -17425,6 +17440,9 @@
       <c r="C800" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="D800" s="6">
+        <v>155</v>
+      </c>
       <c r="E800" s="18">
         <v>375</v>
       </c>
@@ -17442,6 +17460,9 @@
       <c r="C801" s="27" t="s">
         <v>25</v>
       </c>
+      <c r="D801" s="6">
+        <v>22.5</v>
+      </c>
       <c r="E801" s="18">
         <v>377.5</v>
       </c>
@@ -17459,6 +17480,9 @@
       <c r="C802" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="D802" s="6">
+        <v>102.5</v>
+      </c>
       <c r="E802" s="18">
         <v>250</v>
       </c>
@@ -17476,6 +17500,9 @@
       <c r="C803" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="D803" s="6">
+        <v>260.5</v>
+      </c>
       <c r="E803" s="18">
         <v>326.25</v>
       </c>
@@ -17492,6 +17519,9 @@
       </c>
       <c r="C804" s="4" t="s">
         <v>70</v>
+      </c>
+      <c r="D804" s="6">
+        <v>48</v>
       </c>
       <c r="E804" s="18">
         <v>200</v>
@@ -25373,7 +25403,7 @@
         <v>5</v>
       </c>
       <c r="H36" s="6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I36" s="6">
         <v>0</v>
@@ -25447,7 +25477,7 @@
         <v>0</v>
       </c>
       <c r="H37" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I37" s="6">
         <v>0</v>
@@ -25521,7 +25551,7 @@
         <v>0</v>
       </c>
       <c r="H38" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" s="6">
         <v>0</v>
@@ -25595,7 +25625,7 @@
         <v>0</v>
       </c>
       <c r="H39" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" s="6">
         <v>0</v>
@@ -25743,7 +25773,7 @@
         <v>1</v>
       </c>
       <c r="H41" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" s="6">
         <v>0</v>
@@ -25817,7 +25847,7 @@
         <v>1</v>
       </c>
       <c r="H42" s="6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I42" s="6">
         <v>0</v>
@@ -25888,7 +25918,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" s="6">
         <v>0</v>
@@ -25965,7 +25995,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" s="6">
         <v>0</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/Dados/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1499" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DE8A15B-28A4-4D49-9546-42D9D718C0CB}"/>
+  <xr:revisionPtr revIDLastSave="1500" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FAD4804-427D-4CA7-8ABF-EBA2AEBCD548}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -17461,7 +17461,7 @@
         <v>25</v>
       </c>
       <c r="D801" s="6">
-        <v>22.5</v>
+        <v>222.5</v>
       </c>
       <c r="E801" s="18">
         <v>377.5</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/Dados/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1500" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FAD4804-427D-4CA7-8ABF-EBA2AEBCD548}"/>
+  <xr:revisionPtr revIDLastSave="1517" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{823522C3-2779-4BE3-B86C-0A64E0DDC70E}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -17540,6 +17540,9 @@
       <c r="C805" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="D805" s="6">
+        <v>641</v>
+      </c>
       <c r="E805" s="18">
         <v>1029.375</v>
       </c>
@@ -17557,6 +17560,9 @@
       <c r="C806" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="D806" s="6">
+        <v>1059</v>
+      </c>
       <c r="E806" s="18">
         <v>915</v>
       </c>
@@ -17573,6 +17579,9 @@
       </c>
       <c r="C807" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="D807" s="6">
+        <v>170.5</v>
       </c>
       <c r="E807" s="18">
         <v>343.125</v>
@@ -17591,6 +17600,9 @@
       <c r="C808" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="D808" s="6">
+        <v>577.5</v>
+      </c>
       <c r="E808" s="18">
         <v>862.5</v>
       </c>
@@ -17608,6 +17620,9 @@
       <c r="C809" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D809" s="6">
+        <v>527</v>
+      </c>
       <c r="E809" s="18">
         <v>575</v>
       </c>
@@ -17625,6 +17640,9 @@
       <c r="C810" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="D810" s="6">
+        <v>176</v>
+      </c>
       <c r="E810" s="18">
         <v>375</v>
       </c>
@@ -17642,6 +17660,9 @@
       <c r="C811" s="27" t="s">
         <v>25</v>
       </c>
+      <c r="D811" s="6">
+        <v>313</v>
+      </c>
       <c r="E811" s="18">
         <v>377.5</v>
       </c>
@@ -17659,6 +17680,9 @@
       <c r="C812" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="D812" s="6">
+        <v>109.5</v>
+      </c>
       <c r="E812" s="18">
         <v>250</v>
       </c>
@@ -17676,6 +17700,9 @@
       <c r="C813" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="D813" s="6">
+        <v>366</v>
+      </c>
       <c r="E813" s="18">
         <v>326.25</v>
       </c>
@@ -17692,6 +17719,9 @@
       </c>
       <c r="C814" s="4" t="s">
         <v>70</v>
+      </c>
+      <c r="D814" s="6">
+        <v>67</v>
       </c>
       <c r="E814" s="18">
         <v>200</v>
@@ -25554,7 +25584,7 @@
         <v>1</v>
       </c>
       <c r="I38" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J38" s="6">
         <v>0</v>
@@ -25628,7 +25658,7 @@
         <v>1</v>
       </c>
       <c r="I39" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" s="6">
         <v>0</v>
@@ -25702,7 +25732,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="6">
         <v>0</v>
@@ -25776,7 +25806,7 @@
         <v>1</v>
       </c>
       <c r="I41" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" s="6">
         <v>0</v>
@@ -25850,7 +25880,7 @@
         <v>5</v>
       </c>
       <c r="I42" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J42" s="6">
         <v>0</v>
@@ -25998,7 +26028,7 @@
         <v>1</v>
       </c>
       <c r="I44" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" s="6">
         <v>0</v>
@@ -26072,7 +26102,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J45" s="6">
         <v>0</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/Dados/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1517" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{823522C3-2779-4BE3-B86C-0A64E0DDC70E}"/>
+  <xr:revisionPtr revIDLastSave="1533" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B6B2C77-8281-492A-AE9C-C777F9ECC37C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -17740,6 +17740,9 @@
       <c r="C815" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="D815" s="6">
+        <v>933.5</v>
+      </c>
       <c r="E815" s="18">
         <v>1029.375</v>
       </c>
@@ -17757,6 +17760,9 @@
       <c r="C816" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="D816" s="6">
+        <v>1276</v>
+      </c>
       <c r="E816" s="18">
         <v>915</v>
       </c>
@@ -17773,6 +17779,9 @@
       </c>
       <c r="C817" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="D817" s="6">
+        <v>193</v>
       </c>
       <c r="E817" s="18">
         <v>343.125</v>
@@ -17791,6 +17800,9 @@
       <c r="C818" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="D818" s="6">
+        <v>705</v>
+      </c>
       <c r="E818" s="18">
         <v>862.5</v>
       </c>
@@ -17808,6 +17820,9 @@
       <c r="C819" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D819" s="6">
+        <v>601.5</v>
+      </c>
       <c r="E819" s="18">
         <v>575</v>
       </c>
@@ -17825,6 +17840,9 @@
       <c r="C820" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="D820" s="6">
+        <v>271.5</v>
+      </c>
       <c r="E820" s="18">
         <v>375</v>
       </c>
@@ -17842,6 +17860,9 @@
       <c r="C821" s="27" t="s">
         <v>25</v>
       </c>
+      <c r="D821" s="6">
+        <v>333.5</v>
+      </c>
       <c r="E821" s="18">
         <v>377.5</v>
       </c>
@@ -17859,6 +17880,9 @@
       <c r="C822" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="D822" s="6">
+        <v>205</v>
+      </c>
       <c r="E822" s="18">
         <v>250</v>
       </c>
@@ -17876,6 +17900,9 @@
       <c r="C823" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="D823" s="6">
+        <v>449</v>
+      </c>
       <c r="E823" s="18">
         <v>326.25</v>
       </c>
@@ -17892,6 +17919,9 @@
       </c>
       <c r="C824" s="4" t="s">
         <v>70</v>
+      </c>
+      <c r="D824" s="6">
+        <v>99</v>
       </c>
       <c r="E824" s="18">
         <v>200</v>
@@ -25439,7 +25469,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K36" s="6">
         <v>0</v>
@@ -25513,7 +25543,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K37" s="6">
         <v>0</v>
@@ -25735,7 +25765,7 @@
         <v>1</v>
       </c>
       <c r="J40" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" s="6">
         <v>0</v>
@@ -25809,7 +25839,7 @@
         <v>1</v>
       </c>
       <c r="J41" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K41" s="6">
         <v>0</v>
@@ -26031,7 +26061,7 @@
         <v>1</v>
       </c>
       <c r="J44" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K44" s="6">
         <v>0</v>
@@ -26105,7 +26135,7 @@
         <v>5</v>
       </c>
       <c r="J45" s="6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K45" s="6">
         <v>0</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/Dados/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1533" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B6B2C77-8281-492A-AE9C-C777F9ECC37C}"/>
+  <xr:revisionPtr revIDLastSave="1556" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{256EE485-F349-42A1-9540-712D9D01209D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -17940,6 +17940,9 @@
       <c r="C825" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="D825" s="6">
+        <v>1040.5</v>
+      </c>
       <c r="E825" s="18">
         <v>1029.375</v>
       </c>
@@ -17957,6 +17960,9 @@
       <c r="C826" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="D826" s="6">
+        <v>1338</v>
+      </c>
       <c r="E826" s="18">
         <v>915</v>
       </c>
@@ -17973,6 +17979,9 @@
       </c>
       <c r="C827" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="D827" s="6">
+        <v>227</v>
       </c>
       <c r="E827" s="18">
         <v>343.125</v>
@@ -17991,6 +18000,9 @@
       <c r="C828" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="D828" s="6">
+        <v>814</v>
+      </c>
       <c r="E828" s="18">
         <v>862.5</v>
       </c>
@@ -18008,6 +18020,9 @@
       <c r="C829" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D829" s="6">
+        <v>714.5</v>
+      </c>
       <c r="E829" s="18">
         <v>575</v>
       </c>
@@ -18025,6 +18040,9 @@
       <c r="C830" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="D830" s="6">
+        <v>271.5</v>
+      </c>
       <c r="E830" s="18">
         <v>375</v>
       </c>
@@ -18042,6 +18060,9 @@
       <c r="C831" s="27" t="s">
         <v>25</v>
       </c>
+      <c r="D831" s="6">
+        <v>380</v>
+      </c>
       <c r="E831" s="18">
         <v>377.5</v>
       </c>
@@ -18059,6 +18080,9 @@
       <c r="C832" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="D832" s="6">
+        <v>221</v>
+      </c>
       <c r="E832" s="18">
         <v>250</v>
       </c>
@@ -18076,6 +18100,9 @@
       <c r="C833" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="D833" s="6">
+        <v>493.5</v>
+      </c>
       <c r="E833" s="18">
         <v>326.25</v>
       </c>
@@ -18093,6 +18120,9 @@
       <c r="C834" s="4" t="s">
         <v>70</v>
       </c>
+      <c r="D834" s="6">
+        <v>99</v>
+      </c>
       <c r="E834" s="18">
         <v>200</v>
       </c>
@@ -18110,6 +18140,9 @@
       <c r="C835" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="D835" s="6">
+        <v>1089</v>
+      </c>
       <c r="E835" s="18">
         <v>2058.75</v>
       </c>
@@ -18127,6 +18160,9 @@
       <c r="C836" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="D836" s="6">
+        <v>1352</v>
+      </c>
       <c r="E836" s="18">
         <v>1830</v>
       </c>
@@ -18143,6 +18179,9 @@
       </c>
       <c r="C837" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="D837" s="6">
+        <v>227</v>
       </c>
       <c r="E837" s="18">
         <v>686.25</v>
@@ -18161,6 +18200,9 @@
       <c r="C838" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="D838" s="6">
+        <v>839.5</v>
+      </c>
       <c r="E838" s="18">
         <v>1725</v>
       </c>
@@ -18178,6 +18220,9 @@
       <c r="C839" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D839" s="6">
+        <v>744</v>
+      </c>
       <c r="E839" s="18">
         <v>1150</v>
       </c>
@@ -18195,6 +18240,9 @@
       <c r="C840" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="D840" s="6">
+        <v>284</v>
+      </c>
       <c r="E840" s="18">
         <v>750</v>
       </c>
@@ -18212,6 +18260,9 @@
       <c r="C841" s="27" t="s">
         <v>25</v>
       </c>
+      <c r="D841" s="6">
+        <v>380</v>
+      </c>
       <c r="E841" s="18">
         <v>755</v>
       </c>
@@ -18229,6 +18280,9 @@
       <c r="C842" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="D842" s="6">
+        <v>221</v>
+      </c>
       <c r="E842" s="18">
         <v>500</v>
       </c>
@@ -18246,6 +18300,9 @@
       <c r="C843" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="D843" s="6">
+        <v>493.5</v>
+      </c>
       <c r="E843" s="18">
         <v>652.5</v>
       </c>
@@ -18262,6 +18319,9 @@
       </c>
       <c r="C844" s="4" t="s">
         <v>70</v>
+      </c>
+      <c r="D844" s="6">
+        <v>112</v>
       </c>
       <c r="E844" s="18">
         <v>400</v>
@@ -25990,7 +26050,7 @@
         <v>0</v>
       </c>
       <c r="K43" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N43" s="6">
         <v>0</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/Dados/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1556" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{256EE485-F349-42A1-9540-712D9D01209D}"/>
+  <xr:revisionPtr revIDLastSave="1574" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{893424B2-DFB0-451D-AFF4-4A2D43F0698A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -18340,6 +18340,9 @@
       <c r="C845" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="D845" s="6">
+        <v>1089</v>
+      </c>
       <c r="E845" s="18">
         <v>2058.75</v>
       </c>
@@ -18357,6 +18360,9 @@
       <c r="C846" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="D846" s="6">
+        <v>1352</v>
+      </c>
       <c r="E846" s="18">
         <v>1830</v>
       </c>
@@ -18373,6 +18379,9 @@
       </c>
       <c r="C847" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="D847" s="6">
+        <v>227</v>
       </c>
       <c r="E847" s="18">
         <v>686.25</v>
@@ -18391,6 +18400,9 @@
       <c r="C848" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="D848" s="6">
+        <v>839.5</v>
+      </c>
       <c r="E848" s="18">
         <v>1725</v>
       </c>
@@ -18408,6 +18420,9 @@
       <c r="C849" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D849" s="6">
+        <v>744</v>
+      </c>
       <c r="E849" s="18">
         <v>1150</v>
       </c>
@@ -18425,6 +18440,9 @@
       <c r="C850" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="D850" s="6">
+        <v>284</v>
+      </c>
       <c r="E850" s="18">
         <v>750</v>
       </c>
@@ -18442,6 +18460,9 @@
       <c r="C851" s="27" t="s">
         <v>25</v>
       </c>
+      <c r="D851" s="6">
+        <v>380</v>
+      </c>
       <c r="E851" s="18">
         <v>755</v>
       </c>
@@ -18459,6 +18480,9 @@
       <c r="C852" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="D852" s="6">
+        <v>221</v>
+      </c>
       <c r="E852" s="18">
         <v>500</v>
       </c>
@@ -18476,6 +18500,9 @@
       <c r="C853" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="D853" s="6">
+        <v>493.5</v>
+      </c>
       <c r="E853" s="18">
         <v>652.5</v>
       </c>
@@ -18493,6 +18520,9 @@
       <c r="C854" s="4" t="s">
         <v>70</v>
       </c>
+      <c r="D854" s="6">
+        <v>112</v>
+      </c>
       <c r="E854" s="18">
         <v>400</v>
       </c>
@@ -18510,6 +18540,9 @@
       <c r="C855" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="D855" s="6">
+        <v>1089</v>
+      </c>
       <c r="E855" s="18">
         <v>2058.75</v>
       </c>
@@ -18527,6 +18560,9 @@
       <c r="C856" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="D856" s="6">
+        <v>1365</v>
+      </c>
       <c r="E856" s="18">
         <v>1830</v>
       </c>
@@ -18543,6 +18579,9 @@
       </c>
       <c r="C857" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="D857" s="6">
+        <v>281</v>
       </c>
       <c r="E857" s="18">
         <v>686.25</v>
@@ -18561,6 +18600,9 @@
       <c r="C858" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="D858" s="6">
+        <v>839.5</v>
+      </c>
       <c r="E858" s="18">
         <v>1725</v>
       </c>
@@ -18578,6 +18620,9 @@
       <c r="C859" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D859" s="6">
+        <v>744</v>
+      </c>
       <c r="E859" s="18">
         <v>1150</v>
       </c>
@@ -18595,6 +18640,9 @@
       <c r="C860" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="D860" s="6">
+        <v>314</v>
+      </c>
       <c r="E860" s="18">
         <v>750</v>
       </c>
@@ -18612,6 +18660,9 @@
       <c r="C861" s="27" t="s">
         <v>25</v>
       </c>
+      <c r="D861" s="6">
+        <v>388</v>
+      </c>
       <c r="E861" s="18">
         <v>755</v>
       </c>
@@ -18629,6 +18680,9 @@
       <c r="C862" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="D862" s="6">
+        <v>226</v>
+      </c>
       <c r="E862" s="18">
         <v>500</v>
       </c>
@@ -18646,6 +18700,9 @@
       <c r="C863" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="D863" s="6">
+        <v>499.5</v>
+      </c>
       <c r="E863" s="18">
         <v>652.5</v>
       </c>
@@ -18662,6 +18719,9 @@
       </c>
       <c r="C864" s="4" t="s">
         <v>70</v>
+      </c>
+      <c r="D864" s="6">
+        <v>112</v>
       </c>
       <c r="E864" s="18">
         <v>400</v>
@@ -25686,7 +25746,7 @@
         <v>0</v>
       </c>
       <c r="O38" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P38" s="6">
         <v>0</v>
@@ -25760,7 +25820,7 @@
         <v>0</v>
       </c>
       <c r="O39" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P39" s="6">
         <v>0</v>
@@ -25834,7 +25894,7 @@
         <v>0</v>
       </c>
       <c r="O40" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P40" s="6">
         <v>0</v>
@@ -25982,7 +26042,7 @@
         <v>0</v>
       </c>
       <c r="O42" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P42" s="6">
         <v>0</v>
@@ -26130,7 +26190,7 @@
         <v>0</v>
       </c>
       <c r="O44" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P44" s="6">
         <v>0</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/Dados/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1574" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{893424B2-DFB0-451D-AFF4-4A2D43F0698A}"/>
+  <xr:revisionPtr revIDLastSave="1588" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0216A2DD-ADB6-45E4-8205-E18AACC8FA4D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18740,6 +18740,9 @@
       <c r="C865" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="D865" s="6">
+        <v>1095</v>
+      </c>
       <c r="E865" s="18">
         <v>2058.75</v>
       </c>
@@ -18757,6 +18760,9 @@
       <c r="C866" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="D866" s="6">
+        <v>1411</v>
+      </c>
       <c r="E866" s="18">
         <v>1830</v>
       </c>
@@ -18773,6 +18779,9 @@
       </c>
       <c r="C867" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="D867" s="6">
+        <v>287</v>
       </c>
       <c r="E867" s="18">
         <v>686.25</v>
@@ -18791,6 +18800,9 @@
       <c r="C868" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="D868" s="6">
+        <v>910</v>
+      </c>
       <c r="E868" s="18">
         <v>1725</v>
       </c>
@@ -18808,6 +18820,9 @@
       <c r="C869" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D869" s="6">
+        <v>788.5</v>
+      </c>
       <c r="E869" s="18">
         <v>1150</v>
       </c>
@@ -18825,6 +18840,9 @@
       <c r="C870" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="D870" s="6">
+        <v>401</v>
+      </c>
       <c r="E870" s="18">
         <v>750</v>
       </c>
@@ -18842,6 +18860,9 @@
       <c r="C871" s="27" t="s">
         <v>25</v>
       </c>
+      <c r="D871" s="6">
+        <v>388</v>
+      </c>
       <c r="E871" s="18">
         <v>755</v>
       </c>
@@ -18859,6 +18880,9 @@
       <c r="C872" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="D872" s="6">
+        <v>226</v>
+      </c>
       <c r="E872" s="18">
         <v>500</v>
       </c>
@@ -18876,6 +18900,9 @@
       <c r="C873" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="D873" s="6">
+        <v>499.5</v>
+      </c>
       <c r="E873" s="18">
         <v>652.5</v>
       </c>
@@ -18892,6 +18919,9 @@
       </c>
       <c r="C874" s="4" t="s">
         <v>70</v>
+      </c>
+      <c r="D874" s="6">
+        <v>115</v>
       </c>
       <c r="E874" s="18">
         <v>400</v>
@@ -25897,7 +25927,7 @@
         <v>3</v>
       </c>
       <c r="P40" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q40" s="6">
         <v>0</v>
@@ -26045,7 +26075,7 @@
         <v>1</v>
       </c>
       <c r="P42" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q42" s="6">
         <v>0</v>
@@ -26267,7 +26297,7 @@
         <v>0</v>
       </c>
       <c r="P45" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q45" s="6">
         <v>0</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/Dados/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1588" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0216A2DD-ADB6-45E4-8205-E18AACC8FA4D}"/>
+  <xr:revisionPtr revIDLastSave="1602" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FDDF424-A4C9-450B-988B-EEF16A617578}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18940,6 +18940,9 @@
       <c r="C875" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="D875" s="6">
+        <v>1099</v>
+      </c>
       <c r="E875" s="18">
         <v>2058.75</v>
       </c>
@@ -18957,6 +18960,9 @@
       <c r="C876" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="D876" s="6">
+        <v>1462</v>
+      </c>
       <c r="E876" s="18">
         <v>1830</v>
       </c>
@@ -18973,6 +18979,9 @@
       </c>
       <c r="C877" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="D877" s="6">
+        <v>467</v>
       </c>
       <c r="E877" s="18">
         <v>686.25</v>
@@ -18991,6 +19000,9 @@
       <c r="C878" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="D878" s="6">
+        <v>1043.5</v>
+      </c>
       <c r="E878" s="18">
         <v>1725</v>
       </c>
@@ -19008,6 +19020,9 @@
       <c r="C879" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D879" s="6">
+        <v>838.5</v>
+      </c>
       <c r="E879" s="18">
         <v>1150</v>
       </c>
@@ -19025,6 +19040,9 @@
       <c r="C880" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="D880" s="6">
+        <v>457</v>
+      </c>
       <c r="E880" s="18">
         <v>750</v>
       </c>
@@ -19042,6 +19060,9 @@
       <c r="C881" s="27" t="s">
         <v>25</v>
       </c>
+      <c r="D881" s="6">
+        <v>519</v>
+      </c>
       <c r="E881" s="18">
         <v>755</v>
       </c>
@@ -19059,6 +19080,9 @@
       <c r="C882" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="D882" s="6">
+        <v>250</v>
+      </c>
       <c r="E882" s="18">
         <v>500</v>
       </c>
@@ -19076,6 +19100,9 @@
       <c r="C883" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="D883" s="6">
+        <v>517.5</v>
+      </c>
       <c r="E883" s="18">
         <v>652.5</v>
       </c>
@@ -19092,6 +19119,9 @@
       </c>
       <c r="C884" s="4" t="s">
         <v>70</v>
+      </c>
+      <c r="D884" s="6">
+        <v>172.5</v>
       </c>
       <c r="E884" s="18">
         <v>400</v>
@@ -25634,7 +25664,7 @@
         <v>0</v>
       </c>
       <c r="Q36" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R36" s="6">
         <v>0</v>
@@ -25856,7 +25886,7 @@
         <v>0</v>
       </c>
       <c r="Q39" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" s="6">
         <v>0</v>
@@ -26226,7 +26256,7 @@
         <v>0</v>
       </c>
       <c r="Q44" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" s="6">
         <v>0</v>
@@ -26300,7 +26330,7 @@
         <v>1</v>
       </c>
       <c r="Q45" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" s="6">
         <v>0</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/Dados/Dashbord/METAS PROPOSTAS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1602" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FDDF424-A4C9-450B-988B-EEF16A617578}"/>
+  <xr:revisionPtr revIDLastSave="1628" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FC11934-4D03-4EDF-AFFE-EC68AF765A2F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -19140,6 +19140,9 @@
       <c r="C885" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="D885" s="6">
+        <v>1373</v>
+      </c>
       <c r="E885" s="18">
         <v>2058.75</v>
       </c>
@@ -19157,6 +19160,9 @@
       <c r="C886" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="D886" s="6">
+        <v>1589.5</v>
+      </c>
       <c r="E886" s="18">
         <v>1830</v>
       </c>
@@ -19173,6 +19179,9 @@
       </c>
       <c r="C887" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="D887" s="6">
+        <v>489.5</v>
       </c>
       <c r="E887" s="18">
         <v>686.25</v>
@@ -19191,6 +19200,9 @@
       <c r="C888" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="D888" s="6">
+        <v>1125.5</v>
+      </c>
       <c r="E888" s="18">
         <v>1725</v>
       </c>
@@ -19208,6 +19220,9 @@
       <c r="C889" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D889" s="6">
+        <v>971.5</v>
+      </c>
       <c r="E889" s="18">
         <v>1150</v>
       </c>
@@ -19225,6 +19240,9 @@
       <c r="C890" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="D890" s="6">
+        <v>463.5</v>
+      </c>
       <c r="E890" s="18">
         <v>750</v>
       </c>
@@ -19242,6 +19260,9 @@
       <c r="C891" s="27" t="s">
         <v>25</v>
       </c>
+      <c r="D891" s="6">
+        <v>699.5</v>
+      </c>
       <c r="E891" s="18">
         <v>755</v>
       </c>
@@ -19259,6 +19280,9 @@
       <c r="C892" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="D892" s="6">
+        <v>270</v>
+      </c>
       <c r="E892" s="18">
         <v>500</v>
       </c>
@@ -19276,6 +19300,9 @@
       <c r="C893" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="D893" s="6">
+        <v>566</v>
+      </c>
       <c r="E893" s="18">
         <v>652.5</v>
       </c>
@@ -19293,6 +19320,9 @@
       <c r="C894" s="4" t="s">
         <v>70</v>
       </c>
+      <c r="D894" s="6">
+        <v>172.5</v>
+      </c>
       <c r="E894" s="18">
         <v>400</v>
       </c>
@@ -19310,6 +19340,9 @@
       <c r="C895" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="D895" s="6">
+        <v>1425</v>
+      </c>
       <c r="E895" s="18">
         <v>3088.125</v>
       </c>
@@ -19327,6 +19360,9 @@
       <c r="C896" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="D896" s="6">
+        <v>1626.5</v>
+      </c>
       <c r="E896" s="18">
         <v>2745</v>
       </c>
@@ -19343,6 +19379,9 @@
       </c>
       <c r="C897" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="D897" s="6">
+        <v>503.5</v>
       </c>
       <c r="E897" s="18">
         <v>1029.375</v>
@@ -19361,6 +19400,9 @@
       <c r="C898" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="D898" s="6">
+        <v>1318</v>
+      </c>
       <c r="E898" s="18">
         <v>2587.5</v>
       </c>
@@ -19378,6 +19420,9 @@
       <c r="C899" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D899" s="6">
+        <v>1119</v>
+      </c>
       <c r="E899" s="18">
         <v>1725</v>
       </c>
@@ -19395,6 +19440,9 @@
       <c r="C900" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="D900" s="6">
+        <v>495.5</v>
+      </c>
       <c r="E900" s="18">
         <v>1125</v>
       </c>
@@ -19412,6 +19460,9 @@
       <c r="C901" s="27" t="s">
         <v>25</v>
       </c>
+      <c r="D901" s="6">
+        <v>718</v>
+      </c>
       <c r="E901" s="18">
         <v>1132.5</v>
       </c>
@@ -19429,6 +19480,9 @@
       <c r="C902" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="D902" s="6">
+        <v>293</v>
+      </c>
       <c r="E902" s="18">
         <v>750</v>
       </c>
@@ -19446,6 +19500,9 @@
       <c r="C903" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="D903" s="6">
+        <v>599</v>
+      </c>
       <c r="E903" s="18">
         <v>978.75</v>
       </c>
@@ -19462,6 +19519,9 @@
       </c>
       <c r="C904" s="4" t="s">
         <v>70</v>
+      </c>
+      <c r="D904" s="6">
+        <v>172.5</v>
       </c>
       <c r="E904" s="18">
         <v>600</v>
@@ -25667,7 +25727,7 @@
         <v>2</v>
       </c>
       <c r="R36" s="6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U36" s="6">
         <v>0</v>
@@ -25741,7 +25801,7 @@
         <v>0</v>
       </c>
       <c r="R37" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U37" s="6">
         <v>0</v>
@@ -25889,7 +25949,7 @@
         <v>1</v>
       </c>
       <c r="R39" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U39" s="6">
         <v>0</v>
@@ -25963,7 +26023,7 @@
         <v>0</v>
       </c>
       <c r="R40" s="6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U40" s="6">
         <v>0</v>
@@ -26111,7 +26171,7 @@
         <v>0</v>
       </c>
       <c r="R42" s="6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U42" s="6">
         <v>0</v>
@@ -26333,7 +26393,7 @@
         <v>1</v>
       </c>
       <c r="R45" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U45" s="6">
         <v>0</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1628" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FC11934-4D03-4EDF-AFFE-EC68AF765A2F}"/>
+  <xr:revisionPtr revIDLastSave="1647" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2471E40-0899-40A2-8A72-6C1A1438896D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -19540,6 +19540,9 @@
       <c r="C905" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="D905" s="6">
+        <v>1433</v>
+      </c>
       <c r="E905" s="18">
         <v>3088.125</v>
       </c>
@@ -19557,6 +19560,9 @@
       <c r="C906" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="D906" s="6">
+        <v>1662.5</v>
+      </c>
       <c r="E906" s="18">
         <v>2745</v>
       </c>
@@ -19573,6 +19579,9 @@
       </c>
       <c r="C907" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="D907" s="6">
+        <v>513.5</v>
       </c>
       <c r="E907" s="18">
         <v>1029.375</v>
@@ -19591,6 +19600,9 @@
       <c r="C908" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="D908" s="6">
+        <v>1338</v>
+      </c>
       <c r="E908" s="18">
         <v>2587.5</v>
       </c>
@@ -19608,6 +19620,9 @@
       <c r="C909" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D909" s="6">
+        <v>1119</v>
+      </c>
       <c r="E909" s="18">
         <v>1725</v>
       </c>
@@ -19625,6 +19640,9 @@
       <c r="C910" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="D910" s="6">
+        <v>498.5</v>
+      </c>
       <c r="E910" s="18">
         <v>1125</v>
       </c>
@@ -19642,6 +19660,9 @@
       <c r="C911" s="27" t="s">
         <v>25</v>
       </c>
+      <c r="D911" s="6">
+        <v>728</v>
+      </c>
       <c r="E911" s="18">
         <v>1132.5</v>
       </c>
@@ -19659,6 +19680,9 @@
       <c r="C912" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="D912" s="6">
+        <v>293</v>
+      </c>
       <c r="E912" s="18">
         <v>750</v>
       </c>
@@ -19676,6 +19700,9 @@
       <c r="C913" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="D913" s="6">
+        <v>625</v>
+      </c>
       <c r="E913" s="18">
         <v>978.75</v>
       </c>
@@ -19692,6 +19719,9 @@
       </c>
       <c r="C914" s="4" t="s">
         <v>70</v>
+      </c>
+      <c r="D914" s="6">
+        <v>180.5</v>
       </c>
       <c r="E914" s="18">
         <v>600</v>
@@ -25730,7 +25760,7 @@
         <v>10</v>
       </c>
       <c r="U36" s="6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V36" s="6">
         <v>0</v>
@@ -25804,7 +25834,7 @@
         <v>2</v>
       </c>
       <c r="U37" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V37" s="6">
         <v>0</v>
@@ -25878,7 +25908,7 @@
         <v>0</v>
       </c>
       <c r="U38" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V38" s="6">
         <v>0</v>
@@ -25952,7 +25982,7 @@
         <v>1</v>
       </c>
       <c r="U39" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V39" s="6">
         <v>0</v>
@@ -26026,7 +26056,7 @@
         <v>4</v>
       </c>
       <c r="U40" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V40" s="6">
         <v>0</v>
@@ -26100,7 +26130,7 @@
         <v>0</v>
       </c>
       <c r="U41" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V41" s="6">
         <v>0</v>
@@ -26174,7 +26204,7 @@
         <v>5</v>
       </c>
       <c r="U42" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V42" s="6">
         <v>0</v>
@@ -26396,7 +26426,7 @@
         <v>1</v>
       </c>
       <c r="U45" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V45" s="6">
         <v>0</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1647" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2471E40-0899-40A2-8A72-6C1A1438896D}"/>
+  <xr:revisionPtr revIDLastSave="1682" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCA5871A-F980-4705-8AD5-6EE87CC77DF7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -19541,7 +19541,7 @@
         <v>8</v>
       </c>
       <c r="D905" s="6">
-        <v>1433</v>
+        <v>1525.5</v>
       </c>
       <c r="E905" s="18">
         <v>3088.125</v>
@@ -19561,7 +19561,7 @@
         <v>9</v>
       </c>
       <c r="D906" s="6">
-        <v>1662.5</v>
+        <v>1870.5</v>
       </c>
       <c r="E906" s="18">
         <v>2745</v>
@@ -19581,7 +19581,7 @@
         <v>10</v>
       </c>
       <c r="D907" s="6">
-        <v>513.5</v>
+        <v>549.5</v>
       </c>
       <c r="E907" s="18">
         <v>1029.375</v>
@@ -19601,7 +19601,7 @@
         <v>13</v>
       </c>
       <c r="D908" s="6">
-        <v>1338</v>
+        <v>1521.5</v>
       </c>
       <c r="E908" s="18">
         <v>2587.5</v>
@@ -19621,7 +19621,7 @@
         <v>14</v>
       </c>
       <c r="D909" s="6">
-        <v>1119</v>
+        <v>1241.5</v>
       </c>
       <c r="E909" s="18">
         <v>1725</v>
@@ -19641,7 +19641,7 @@
         <v>23</v>
       </c>
       <c r="D910" s="6">
-        <v>498.5</v>
+        <v>551.5</v>
       </c>
       <c r="E910" s="18">
         <v>1125</v>
@@ -19661,7 +19661,7 @@
         <v>25</v>
       </c>
       <c r="D911" s="6">
-        <v>728</v>
+        <v>794</v>
       </c>
       <c r="E911" s="18">
         <v>1132.5</v>
@@ -19701,7 +19701,7 @@
         <v>29</v>
       </c>
       <c r="D913" s="6">
-        <v>625</v>
+        <v>666</v>
       </c>
       <c r="E913" s="18">
         <v>978.75</v>
@@ -19721,7 +19721,7 @@
         <v>70</v>
       </c>
       <c r="D914" s="6">
-        <v>180.5</v>
+        <v>196.5</v>
       </c>
       <c r="E914" s="18">
         <v>600</v>
@@ -19740,6 +19740,9 @@
       <c r="C915" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="D915" s="6">
+        <v>1634.5</v>
+      </c>
       <c r="E915" s="18">
         <v>3088.125</v>
       </c>
@@ -19757,6 +19760,9 @@
       <c r="C916" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="D916" s="6">
+        <v>2179.5</v>
+      </c>
       <c r="E916" s="18">
         <v>2745</v>
       </c>
@@ -19773,6 +19779,9 @@
       </c>
       <c r="C917" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="D917" s="6">
+        <v>600</v>
       </c>
       <c r="E917" s="18">
         <v>1029.375</v>
@@ -19791,6 +19800,9 @@
       <c r="C918" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="D918" s="6">
+        <v>1682.5</v>
+      </c>
       <c r="E918" s="18">
         <v>2587.5</v>
       </c>
@@ -19808,6 +19820,9 @@
       <c r="C919" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D919" s="6">
+        <v>1387</v>
+      </c>
       <c r="E919" s="18">
         <v>1725</v>
       </c>
@@ -19825,6 +19840,9 @@
       <c r="C920" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="D920" s="6">
+        <v>608</v>
+      </c>
       <c r="E920" s="18">
         <v>1125</v>
       </c>
@@ -19842,6 +19860,9 @@
       <c r="C921" s="27" t="s">
         <v>25</v>
       </c>
+      <c r="D921" s="6">
+        <v>900.5</v>
+      </c>
       <c r="E921" s="18">
         <v>1132.5</v>
       </c>
@@ -19859,6 +19880,9 @@
       <c r="C922" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="D922" s="6">
+        <v>293</v>
+      </c>
       <c r="E922" s="18">
         <v>750</v>
       </c>
@@ -19876,6 +19900,9 @@
       <c r="C923" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="D923" s="6">
+        <v>706</v>
+      </c>
       <c r="E923" s="18">
         <v>978.75</v>
       </c>
@@ -19892,6 +19919,9 @@
       </c>
       <c r="C924" s="4" t="s">
         <v>70</v>
+      </c>
+      <c r="D924" s="6">
+        <v>244.5</v>
       </c>
       <c r="E924" s="18">
         <v>600</v>
@@ -25763,7 +25793,7 @@
         <v>5</v>
       </c>
       <c r="V36" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W36" s="6">
         <v>0</v>
@@ -25837,7 +25867,7 @@
         <v>2</v>
       </c>
       <c r="V37" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W37" s="6">
         <v>0</v>
@@ -25911,7 +25941,7 @@
         <v>3</v>
       </c>
       <c r="V38" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W38" s="6">
         <v>0</v>
@@ -25985,7 +26015,7 @@
         <v>3</v>
       </c>
       <c r="V39" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W39" s="6">
         <v>0</v>
@@ -26059,7 +26089,7 @@
         <v>2</v>
       </c>
       <c r="V40" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" s="6">
         <v>0</v>
@@ -26207,7 +26237,7 @@
         <v>3</v>
       </c>
       <c r="V42" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W42" s="6">
         <v>0</v>
@@ -26355,7 +26385,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W44" s="6">
         <v>0</v>
@@ -26429,7 +26459,7 @@
         <v>3</v>
       </c>
       <c r="V45" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W45" s="6">
         <v>0</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1682" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCA5871A-F980-4705-8AD5-6EE87CC77DF7}"/>
+  <xr:revisionPtr revIDLastSave="1712" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E14E0C14-8852-4CD2-9E5D-6F08620AC45F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -19940,6 +19940,9 @@
       <c r="C925" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="D925" s="6">
+        <v>1724</v>
+      </c>
       <c r="E925" s="18">
         <v>3088.125</v>
       </c>
@@ -19957,6 +19960,9 @@
       <c r="C926" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="D926" s="6">
+        <v>2357</v>
+      </c>
       <c r="E926" s="18">
         <v>2745</v>
       </c>
@@ -19973,6 +19979,9 @@
       </c>
       <c r="C927" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="D927" s="6">
+        <v>667.5</v>
       </c>
       <c r="E927" s="18">
         <v>1029.375</v>
@@ -19991,6 +20000,9 @@
       <c r="C928" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="D928" s="6">
+        <v>1784</v>
+      </c>
       <c r="E928" s="18">
         <v>2587.5</v>
       </c>
@@ -20008,6 +20020,9 @@
       <c r="C929" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D929" s="6">
+        <v>1593</v>
+      </c>
       <c r="E929" s="18">
         <v>1725</v>
       </c>
@@ -20025,6 +20040,9 @@
       <c r="C930" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="D930" s="6">
+        <v>698</v>
+      </c>
       <c r="E930" s="18">
         <v>1125</v>
       </c>
@@ -20042,6 +20060,9 @@
       <c r="C931" s="27" t="s">
         <v>25</v>
       </c>
+      <c r="D931" s="6">
+        <v>969</v>
+      </c>
       <c r="E931" s="18">
         <v>1132.5</v>
       </c>
@@ -20059,6 +20080,9 @@
       <c r="C932" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="D932" s="6">
+        <v>293</v>
+      </c>
       <c r="E932" s="18">
         <v>750</v>
       </c>
@@ -20076,6 +20100,9 @@
       <c r="C933" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="D933" s="6">
+        <v>744</v>
+      </c>
       <c r="E933" s="18">
         <v>978.75</v>
       </c>
@@ -20092,6 +20119,9 @@
       </c>
       <c r="C934" s="4" t="s">
         <v>70</v>
+      </c>
+      <c r="D934" s="6">
+        <v>268.5</v>
       </c>
       <c r="E934" s="18">
         <v>600</v>
@@ -25796,7 +25826,7 @@
         <v>3</v>
       </c>
       <c r="W36" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X36" s="6">
         <v>0</v>
@@ -25870,7 +25900,7 @@
         <v>1</v>
       </c>
       <c r="W37" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X37" s="6">
         <v>0</v>
@@ -26018,7 +26048,7 @@
         <v>2</v>
       </c>
       <c r="W39" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X39" s="6">
         <v>0</v>
@@ -26092,7 +26122,7 @@
         <v>1</v>
       </c>
       <c r="W40" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X40" s="6">
         <v>0</v>
@@ -26166,7 +26196,7 @@
         <v>0</v>
       </c>
       <c r="W41" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X41" s="6">
         <v>0</v>
@@ -26240,7 +26270,7 @@
         <v>2</v>
       </c>
       <c r="W42" s="6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X42" s="6">
         <v>0</v>
@@ -26388,7 +26418,7 @@
         <v>2</v>
       </c>
       <c r="W44" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X44" s="6">
         <v>0</v>
@@ -26462,7 +26492,7 @@
         <v>3</v>
       </c>
       <c r="W45" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X45" s="6">
         <v>0</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1712" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E14E0C14-8852-4CD2-9E5D-6F08620AC45F}"/>
+  <xr:revisionPtr revIDLastSave="1722" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{636FF900-8E60-491E-8229-4A74BA792107}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -20140,6 +20140,9 @@
       <c r="C935" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="D935" s="6">
+        <v>1724</v>
+      </c>
       <c r="E935" s="18">
         <v>3088.125</v>
       </c>
@@ -20157,6 +20160,9 @@
       <c r="C936" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="D936" s="6">
+        <v>2365</v>
+      </c>
       <c r="E936" s="18">
         <v>2745</v>
       </c>
@@ -20173,6 +20179,9 @@
       </c>
       <c r="C937" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="D937" s="6">
+        <v>673.5</v>
       </c>
       <c r="E937" s="18">
         <v>1029.375</v>
@@ -20191,6 +20200,9 @@
       <c r="C938" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="D938" s="6">
+        <v>1784</v>
+      </c>
       <c r="E938" s="18">
         <v>2587.5</v>
       </c>
@@ -20208,6 +20220,9 @@
       <c r="C939" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D939" s="6">
+        <v>1774.5</v>
+      </c>
       <c r="E939" s="18">
         <v>1725</v>
       </c>
@@ -20225,6 +20240,9 @@
       <c r="C940" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="D940" s="6">
+        <v>708</v>
+      </c>
       <c r="E940" s="18">
         <v>1125</v>
       </c>
@@ -20242,6 +20260,9 @@
       <c r="C941" s="27" t="s">
         <v>25</v>
       </c>
+      <c r="D941" s="6">
+        <v>1011.5</v>
+      </c>
       <c r="E941" s="18">
         <v>1132.5</v>
       </c>
@@ -20259,6 +20280,9 @@
       <c r="C942" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="D942" s="6">
+        <v>293</v>
+      </c>
       <c r="E942" s="18">
         <v>750</v>
       </c>
@@ -20276,6 +20300,9 @@
       <c r="C943" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="D943" s="6">
+        <v>783</v>
+      </c>
       <c r="E943" s="18">
         <v>978.75</v>
       </c>
@@ -20292,6 +20319,9 @@
       </c>
       <c r="C944" s="4" t="s">
         <v>70</v>
+      </c>
+      <c r="D944" s="6">
+        <v>295</v>
       </c>
       <c r="E944" s="18">
         <v>600</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1722" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{636FF900-8E60-491E-8229-4A74BA792107}"/>
+  <xr:revisionPtr revIDLastSave="1752" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B100CF9-0F4A-43A8-8CA5-67BB4420367A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20340,6 +20340,9 @@
       <c r="C945" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="D945" s="6">
+        <v>1782</v>
+      </c>
       <c r="E945" s="18">
         <v>3088.125</v>
       </c>
@@ -20357,6 +20360,9 @@
       <c r="C946" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="D946" s="6">
+        <v>2436</v>
+      </c>
       <c r="E946" s="18">
         <v>2745</v>
       </c>
@@ -20373,6 +20379,9 @@
       </c>
       <c r="C947" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="D947" s="6">
+        <v>673.5</v>
       </c>
       <c r="E947" s="18">
         <v>1029.375</v>
@@ -20391,6 +20400,9 @@
       <c r="C948" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="D948" s="6">
+        <v>1958.5</v>
+      </c>
       <c r="E948" s="18">
         <v>2587.5</v>
       </c>
@@ -20408,6 +20420,9 @@
       <c r="C949" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D949" s="6">
+        <v>1926.5</v>
+      </c>
       <c r="E949" s="18">
         <v>1725</v>
       </c>
@@ -20425,6 +20440,9 @@
       <c r="C950" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="D950" s="6">
+        <v>719.5</v>
+      </c>
       <c r="E950" s="18">
         <v>1125</v>
       </c>
@@ -20442,6 +20460,9 @@
       <c r="C951" s="27" t="s">
         <v>25</v>
       </c>
+      <c r="D951" s="6">
+        <v>1047.5</v>
+      </c>
       <c r="E951" s="18">
         <v>1132.5</v>
       </c>
@@ -20459,6 +20480,9 @@
       <c r="C952" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="D952" s="6">
+        <v>293</v>
+      </c>
       <c r="E952" s="18">
         <v>750</v>
       </c>
@@ -20476,6 +20500,9 @@
       <c r="C953" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="D953" s="6">
+        <v>847</v>
+      </c>
       <c r="E953" s="18">
         <v>978.75</v>
       </c>
@@ -20493,6 +20520,9 @@
       <c r="C954" s="4" t="s">
         <v>70</v>
       </c>
+      <c r="D954" s="6">
+        <v>295</v>
+      </c>
       <c r="E954" s="18">
         <v>600</v>
       </c>
@@ -20510,6 +20540,9 @@
       <c r="C955" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="D955" s="6">
+        <v>1782</v>
+      </c>
       <c r="E955" s="18">
         <v>4117.5</v>
       </c>
@@ -20527,6 +20560,9 @@
       <c r="C956" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="D956" s="6">
+        <v>2436</v>
+      </c>
       <c r="E956" s="18">
         <v>3660</v>
       </c>
@@ -20543,6 +20579,9 @@
       </c>
       <c r="C957" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="D957" s="6">
+        <v>673.5</v>
       </c>
       <c r="E957" s="18">
         <v>1372.5</v>
@@ -20561,6 +20600,9 @@
       <c r="C958" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="D958" s="6">
+        <v>1978.5</v>
+      </c>
       <c r="E958" s="18">
         <v>3450</v>
       </c>
@@ -20578,6 +20620,9 @@
       <c r="C959" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D959" s="6">
+        <v>1967.5</v>
+      </c>
       <c r="E959" s="18">
         <v>2300</v>
       </c>
@@ -20595,6 +20640,9 @@
       <c r="C960" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="D960" s="6">
+        <v>771.5</v>
+      </c>
       <c r="E960" s="18">
         <v>1500</v>
       </c>
@@ -20612,6 +20660,9 @@
       <c r="C961" s="27" t="s">
         <v>25</v>
       </c>
+      <c r="D961" s="6">
+        <v>1047.5</v>
+      </c>
       <c r="E961" s="18">
         <v>1510</v>
       </c>
@@ -20629,6 +20680,9 @@
       <c r="C962" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="D962" s="6">
+        <v>293</v>
+      </c>
       <c r="E962" s="18">
         <v>1000</v>
       </c>
@@ -20646,6 +20700,9 @@
       <c r="C963" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="D963" s="6">
+        <v>847</v>
+      </c>
       <c r="E963" s="18">
         <v>1305</v>
       </c>
@@ -20662,6 +20719,9 @@
       </c>
       <c r="C964" s="4" t="s">
         <v>70</v>
+      </c>
+      <c r="D964" s="6">
+        <v>295</v>
       </c>
       <c r="E964" s="18">
         <v>800</v>
@@ -25859,10 +25919,10 @@
         <v>2</v>
       </c>
       <c r="X36" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y36" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB36" s="6">
         <v>0</v>
@@ -25933,10 +25993,10 @@
         <v>1</v>
       </c>
       <c r="X37" s="6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y37" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB37" s="6">
         <v>0</v>
@@ -26007,7 +26067,7 @@
         <v>0</v>
       </c>
       <c r="X38" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y38" s="6">
         <v>0</v>
@@ -26081,10 +26141,10 @@
         <v>2</v>
       </c>
       <c r="X39" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y39" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB39" s="6">
         <v>0</v>
@@ -26155,7 +26215,7 @@
         <v>2</v>
       </c>
       <c r="X40" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y40" s="6">
         <v>0</v>
@@ -26303,7 +26363,7 @@
         <v>5</v>
       </c>
       <c r="X42" s="6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y42" s="6">
         <v>0</v>
@@ -26528,7 +26588,7 @@
         <v>0</v>
       </c>
       <c r="Y45" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB45" s="6">
         <v>0</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1752" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B100CF9-0F4A-43A8-8CA5-67BB4420367A}"/>
+  <xr:revisionPtr revIDLastSave="1911" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{891806F6-4FB8-461D-ABF9-7CA46C28209E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,10 +19,10 @@
     <sheet name="Propostas" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dados Diários'!$A$1:$F$1024</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dados Diários'!$A$1:$F$1274</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Meta de Ritmo'!$A$1:$F$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Metas 100%'!$A$1:$D$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Propostas!$A$1:$A$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Propostas!$A$1:$A$56</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3404" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4176" uniqueCount="84">
   <si>
     <t>Cidade</t>
   </si>
@@ -317,6 +317,7 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -857,15 +858,14 @@
   <sheetPr filterMode="1">
     <tabColor rgb="FF1F4E79"/>
   </sheetPr>
-  <dimension ref="A1:M1024"/>
+  <dimension ref="A1:M1294"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.7109375" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="13.42578125" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="6"/>
+    <col min="6" max="7" width="18.7109375" style="6" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="25.7109375" style="6" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" style="6" customWidth="1"/>
     <col min="10" max="10" width="21.28515625" style="6" customWidth="1"/>
@@ -11475,7 +11475,7 @@
         <v>46265</v>
       </c>
     </row>
-    <row r="505" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" s="4" t="s">
         <v>6</v>
       </c>
@@ -11495,7 +11495,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="506" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" s="4" t="s">
         <v>6</v>
       </c>
@@ -11515,7 +11515,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="507" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" s="4" t="s">
         <v>6</v>
       </c>
@@ -11535,7 +11535,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="508" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" s="4" t="s">
         <v>11</v>
       </c>
@@ -11555,7 +11555,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="509" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" s="4" t="s">
         <v>11</v>
       </c>
@@ -11575,7 +11575,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="510" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" s="4" t="s">
         <v>24</v>
       </c>
@@ -11595,7 +11595,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="511" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" s="27" t="s">
         <v>26</v>
       </c>
@@ -11615,7 +11615,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="512" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" s="4" t="s">
         <v>28</v>
       </c>
@@ -11635,7 +11635,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="513" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513" s="4" t="s">
         <v>30</v>
       </c>
@@ -11655,7 +11655,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="514" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" s="4" t="s">
         <v>68</v>
       </c>
@@ -11675,7 +11675,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="515" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" s="4" t="s">
         <v>6</v>
       </c>
@@ -11695,7 +11695,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="516" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" s="4" t="s">
         <v>6</v>
       </c>
@@ -11715,7 +11715,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="517" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517" s="4" t="s">
         <v>6</v>
       </c>
@@ -11735,7 +11735,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="518" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" s="4" t="s">
         <v>11</v>
       </c>
@@ -11755,7 +11755,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="519" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" s="4" t="s">
         <v>11</v>
       </c>
@@ -11775,7 +11775,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="520" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" s="4" t="s">
         <v>24</v>
       </c>
@@ -11795,7 +11795,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="521" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" s="27" t="s">
         <v>26</v>
       </c>
@@ -11815,7 +11815,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="522" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" s="4" t="s">
         <v>28</v>
       </c>
@@ -11835,7 +11835,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="523" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523" s="4" t="s">
         <v>30</v>
       </c>
@@ -11855,7 +11855,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="524" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" s="4" t="s">
         <v>68</v>
       </c>
@@ -11875,7 +11875,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="525" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" s="4" t="s">
         <v>6</v>
       </c>
@@ -11895,7 +11895,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="526" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" s="4" t="s">
         <v>6</v>
       </c>
@@ -11915,7 +11915,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="527" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527" s="4" t="s">
         <v>6</v>
       </c>
@@ -11935,7 +11935,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="528" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" s="4" t="s">
         <v>11</v>
       </c>
@@ -11955,7 +11955,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="529" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529" s="4" t="s">
         <v>11</v>
       </c>
@@ -11975,7 +11975,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="530" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" s="4" t="s">
         <v>24</v>
       </c>
@@ -11995,7 +11995,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="531" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" s="27" t="s">
         <v>26</v>
       </c>
@@ -12015,7 +12015,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="532" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" s="4" t="s">
         <v>28</v>
       </c>
@@ -12035,7 +12035,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="533" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" s="4" t="s">
         <v>30</v>
       </c>
@@ -12055,7 +12055,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="534" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" s="4" t="s">
         <v>68</v>
       </c>
@@ -12075,7 +12075,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="535" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" s="4" t="s">
         <v>6</v>
       </c>
@@ -12095,7 +12095,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="536" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" s="4" t="s">
         <v>6</v>
       </c>
@@ -12115,7 +12115,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="537" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" s="4" t="s">
         <v>6</v>
       </c>
@@ -12135,7 +12135,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="538" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" s="4" t="s">
         <v>11</v>
       </c>
@@ -12155,7 +12155,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="539" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" s="4" t="s">
         <v>11</v>
       </c>
@@ -12175,7 +12175,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="540" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540" s="4" t="s">
         <v>24</v>
       </c>
@@ -12195,7 +12195,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="541" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541" s="27" t="s">
         <v>26</v>
       </c>
@@ -12215,7 +12215,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="542" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" s="4" t="s">
         <v>28</v>
       </c>
@@ -12235,7 +12235,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="543" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" s="4" t="s">
         <v>30</v>
       </c>
@@ -12255,7 +12255,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="544" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" s="4" t="s">
         <v>68</v>
       </c>
@@ -12275,7 +12275,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="545" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545" s="4" t="s">
         <v>6</v>
       </c>
@@ -12295,7 +12295,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="546" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" s="4" t="s">
         <v>6</v>
       </c>
@@ -12315,7 +12315,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="547" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547" s="4" t="s">
         <v>6</v>
       </c>
@@ -12335,7 +12335,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="548" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" s="4" t="s">
         <v>11</v>
       </c>
@@ -12355,7 +12355,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="549" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" s="4" t="s">
         <v>11</v>
       </c>
@@ -12375,7 +12375,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="550" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" s="4" t="s">
         <v>24</v>
       </c>
@@ -12395,7 +12395,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="551" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" s="27" t="s">
         <v>26</v>
       </c>
@@ -12415,7 +12415,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="552" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" s="4" t="s">
         <v>28</v>
       </c>
@@ -12435,7 +12435,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="553" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553" s="4" t="s">
         <v>30</v>
       </c>
@@ -12455,7 +12455,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="554" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" s="4" t="s">
         <v>68</v>
       </c>
@@ -12475,7 +12475,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="555" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" s="4" t="s">
         <v>6</v>
       </c>
@@ -12495,7 +12495,7 @@
         <v>46273</v>
       </c>
     </row>
-    <row r="556" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" s="4" t="s">
         <v>6</v>
       </c>
@@ -12515,7 +12515,7 @@
         <v>46273</v>
       </c>
     </row>
-    <row r="557" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" s="4" t="s">
         <v>6</v>
       </c>
@@ -12535,7 +12535,7 @@
         <v>46273</v>
       </c>
     </row>
-    <row r="558" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" s="4" t="s">
         <v>11</v>
       </c>
@@ -12555,7 +12555,7 @@
         <v>46273</v>
       </c>
     </row>
-    <row r="559" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" s="4" t="s">
         <v>11</v>
       </c>
@@ -12575,7 +12575,7 @@
         <v>46273</v>
       </c>
     </row>
-    <row r="560" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" s="4" t="s">
         <v>24</v>
       </c>
@@ -12595,7 +12595,7 @@
         <v>46273</v>
       </c>
     </row>
-    <row r="561" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" s="27" t="s">
         <v>26</v>
       </c>
@@ -12615,7 +12615,7 @@
         <v>46273</v>
       </c>
     </row>
-    <row r="562" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" s="4" t="s">
         <v>28</v>
       </c>
@@ -12635,7 +12635,7 @@
         <v>46273</v>
       </c>
     </row>
-    <row r="563" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" s="4" t="s">
         <v>30</v>
       </c>
@@ -12655,7 +12655,7 @@
         <v>46273</v>
       </c>
     </row>
-    <row r="564" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" s="4" t="s">
         <v>68</v>
       </c>
@@ -12675,7 +12675,7 @@
         <v>46273</v>
       </c>
     </row>
-    <row r="565" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565" s="4" t="s">
         <v>6</v>
       </c>
@@ -12695,7 +12695,7 @@
         <v>46274</v>
       </c>
     </row>
-    <row r="566" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" s="4" t="s">
         <v>6</v>
       </c>
@@ -12715,7 +12715,7 @@
         <v>46274</v>
       </c>
     </row>
-    <row r="567" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" s="4" t="s">
         <v>6</v>
       </c>
@@ -12735,7 +12735,7 @@
         <v>46274</v>
       </c>
     </row>
-    <row r="568" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" s="4" t="s">
         <v>11</v>
       </c>
@@ -12755,7 +12755,7 @@
         <v>46274</v>
       </c>
     </row>
-    <row r="569" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" s="4" t="s">
         <v>11</v>
       </c>
@@ -12775,7 +12775,7 @@
         <v>46274</v>
       </c>
     </row>
-    <row r="570" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570" s="4" t="s">
         <v>24</v>
       </c>
@@ -12795,7 +12795,7 @@
         <v>46274</v>
       </c>
     </row>
-    <row r="571" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571" s="27" t="s">
         <v>26</v>
       </c>
@@ -12815,7 +12815,7 @@
         <v>46274</v>
       </c>
     </row>
-    <row r="572" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" s="4" t="s">
         <v>28</v>
       </c>
@@ -12835,7 +12835,7 @@
         <v>46274</v>
       </c>
     </row>
-    <row r="573" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" s="4" t="s">
         <v>30</v>
       </c>
@@ -12855,7 +12855,7 @@
         <v>46274</v>
       </c>
     </row>
-    <row r="574" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574" s="4" t="s">
         <v>68</v>
       </c>
@@ -12875,7 +12875,7 @@
         <v>46274</v>
       </c>
     </row>
-    <row r="575" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" s="4" t="s">
         <v>6</v>
       </c>
@@ -12895,7 +12895,7 @@
         <v>46275</v>
       </c>
     </row>
-    <row r="576" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576" s="4" t="s">
         <v>6</v>
       </c>
@@ -12915,7 +12915,7 @@
         <v>46275</v>
       </c>
     </row>
-    <row r="577" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577" s="4" t="s">
         <v>6</v>
       </c>
@@ -12935,7 +12935,7 @@
         <v>46275</v>
       </c>
     </row>
-    <row r="578" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578" s="4" t="s">
         <v>11</v>
       </c>
@@ -12955,7 +12955,7 @@
         <v>46275</v>
       </c>
     </row>
-    <row r="579" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579" s="4" t="s">
         <v>11</v>
       </c>
@@ -12975,7 +12975,7 @@
         <v>46275</v>
       </c>
     </row>
-    <row r="580" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580" s="4" t="s">
         <v>24</v>
       </c>
@@ -12995,7 +12995,7 @@
         <v>46275</v>
       </c>
     </row>
-    <row r="581" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581" s="27" t="s">
         <v>26</v>
       </c>
@@ -13015,7 +13015,7 @@
         <v>46275</v>
       </c>
     </row>
-    <row r="582" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582" s="4" t="s">
         <v>28</v>
       </c>
@@ -13035,7 +13035,7 @@
         <v>46275</v>
       </c>
     </row>
-    <row r="583" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583" s="4" t="s">
         <v>30</v>
       </c>
@@ -13055,7 +13055,7 @@
         <v>46275</v>
       </c>
     </row>
-    <row r="584" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584" s="4" t="s">
         <v>68</v>
       </c>
@@ -13075,7 +13075,7 @@
         <v>46275</v>
       </c>
     </row>
-    <row r="585" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" s="4" t="s">
         <v>6</v>
       </c>
@@ -13095,7 +13095,7 @@
         <v>46276</v>
       </c>
     </row>
-    <row r="586" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586" s="4" t="s">
         <v>6</v>
       </c>
@@ -13115,7 +13115,7 @@
         <v>46276</v>
       </c>
     </row>
-    <row r="587" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" s="4" t="s">
         <v>6</v>
       </c>
@@ -13135,7 +13135,7 @@
         <v>46276</v>
       </c>
     </row>
-    <row r="588" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" s="4" t="s">
         <v>11</v>
       </c>
@@ -13155,7 +13155,7 @@
         <v>46276</v>
       </c>
     </row>
-    <row r="589" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589" s="4" t="s">
         <v>11</v>
       </c>
@@ -13175,7 +13175,7 @@
         <v>46276</v>
       </c>
     </row>
-    <row r="590" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590" s="4" t="s">
         <v>24</v>
       </c>
@@ -13195,7 +13195,7 @@
         <v>46276</v>
       </c>
     </row>
-    <row r="591" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591" s="27" t="s">
         <v>26</v>
       </c>
@@ -13215,7 +13215,7 @@
         <v>46276</v>
       </c>
     </row>
-    <row r="592" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592" s="4" t="s">
         <v>28</v>
       </c>
@@ -13235,7 +13235,7 @@
         <v>46276</v>
       </c>
     </row>
-    <row r="593" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593" s="4" t="s">
         <v>30</v>
       </c>
@@ -13255,7 +13255,7 @@
         <v>46276</v>
       </c>
     </row>
-    <row r="594" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594" s="4" t="s">
         <v>68</v>
       </c>
@@ -13275,7 +13275,7 @@
         <v>46276</v>
       </c>
     </row>
-    <row r="595" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A595" s="4" t="s">
         <v>6</v>
       </c>
@@ -13295,7 +13295,7 @@
         <v>46277</v>
       </c>
     </row>
-    <row r="596" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596" s="4" t="s">
         <v>6</v>
       </c>
@@ -13315,7 +13315,7 @@
         <v>46277</v>
       </c>
     </row>
-    <row r="597" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597" s="4" t="s">
         <v>6</v>
       </c>
@@ -13335,7 +13335,7 @@
         <v>46277</v>
       </c>
     </row>
-    <row r="598" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598" s="4" t="s">
         <v>11</v>
       </c>
@@ -13355,7 +13355,7 @@
         <v>46277</v>
       </c>
     </row>
-    <row r="599" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599" s="4" t="s">
         <v>11</v>
       </c>
@@ -13375,7 +13375,7 @@
         <v>46277</v>
       </c>
     </row>
-    <row r="600" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600" s="4" t="s">
         <v>24</v>
       </c>
@@ -13395,7 +13395,7 @@
         <v>46277</v>
       </c>
     </row>
-    <row r="601" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601" s="27" t="s">
         <v>26</v>
       </c>
@@ -13415,7 +13415,7 @@
         <v>46277</v>
       </c>
     </row>
-    <row r="602" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602" s="4" t="s">
         <v>28</v>
       </c>
@@ -13435,7 +13435,7 @@
         <v>46277</v>
       </c>
     </row>
-    <row r="603" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603" s="4" t="s">
         <v>30</v>
       </c>
@@ -13455,7 +13455,7 @@
         <v>46277</v>
       </c>
     </row>
-    <row r="604" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604" s="4" t="s">
         <v>68</v>
       </c>
@@ -13475,7 +13475,7 @@
         <v>46277</v>
       </c>
     </row>
-    <row r="605" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605" s="4" t="s">
         <v>6</v>
       </c>
@@ -13495,7 +13495,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="606" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606" s="4" t="s">
         <v>6</v>
       </c>
@@ -13515,7 +13515,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="607" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A607" s="4" t="s">
         <v>6</v>
       </c>
@@ -13535,7 +13535,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="608" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A608" s="4" t="s">
         <v>11</v>
       </c>
@@ -13555,7 +13555,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="609" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609" s="4" t="s">
         <v>11</v>
       </c>
@@ -13575,7 +13575,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="610" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610" s="4" t="s">
         <v>24</v>
       </c>
@@ -13595,7 +13595,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="611" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611" s="27" t="s">
         <v>26</v>
       </c>
@@ -13615,7 +13615,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="612" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612" s="4" t="s">
         <v>28</v>
       </c>
@@ -13635,7 +13635,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="613" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A613" s="4" t="s">
         <v>30</v>
       </c>
@@ -13655,7 +13655,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="614" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614" s="4" t="s">
         <v>68</v>
       </c>
@@ -13675,7 +13675,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="615" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" s="4" t="s">
         <v>6</v>
       </c>
@@ -13695,7 +13695,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="616" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" s="4" t="s">
         <v>6</v>
       </c>
@@ -13715,7 +13715,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="617" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617" s="4" t="s">
         <v>6</v>
       </c>
@@ -13735,7 +13735,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="618" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" s="4" t="s">
         <v>11</v>
       </c>
@@ -13755,7 +13755,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="619" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619" s="4" t="s">
         <v>11</v>
       </c>
@@ -13775,7 +13775,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="620" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" s="4" t="s">
         <v>24</v>
       </c>
@@ -13795,7 +13795,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="621" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621" s="27" t="s">
         <v>26</v>
       </c>
@@ -13815,7 +13815,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="622" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A622" s="4" t="s">
         <v>28</v>
       </c>
@@ -13835,7 +13835,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="623" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" s="4" t="s">
         <v>30</v>
       </c>
@@ -13855,7 +13855,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="624" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A624" s="4" t="s">
         <v>68</v>
       </c>
@@ -13875,7 +13875,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="625" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A625" s="4" t="s">
         <v>6</v>
       </c>
@@ -13895,7 +13895,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="626" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A626" s="4" t="s">
         <v>6</v>
       </c>
@@ -13915,7 +13915,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="627" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627" s="4" t="s">
         <v>6</v>
       </c>
@@ -13935,7 +13935,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="628" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A628" s="4" t="s">
         <v>11</v>
       </c>
@@ -13955,7 +13955,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="629" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629" s="4" t="s">
         <v>11</v>
       </c>
@@ -13975,7 +13975,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="630" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A630" s="4" t="s">
         <v>24</v>
       </c>
@@ -13995,7 +13995,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="631" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A631" s="27" t="s">
         <v>26</v>
       </c>
@@ -14015,7 +14015,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="632" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632" s="4" t="s">
         <v>28</v>
       </c>
@@ -14035,7 +14035,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="633" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633" s="4" t="s">
         <v>30</v>
       </c>
@@ -14055,7 +14055,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="634" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634" s="4" t="s">
         <v>68</v>
       </c>
@@ -14075,7 +14075,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="635" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635" s="4" t="s">
         <v>6</v>
       </c>
@@ -14095,7 +14095,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="636" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A636" s="4" t="s">
         <v>6</v>
       </c>
@@ -14115,7 +14115,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="637" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A637" s="4" t="s">
         <v>6</v>
       </c>
@@ -14135,7 +14135,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="638" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A638" s="4" t="s">
         <v>11</v>
       </c>
@@ -14155,7 +14155,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="639" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A639" s="4" t="s">
         <v>11</v>
       </c>
@@ -14175,7 +14175,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="640" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A640" s="4" t="s">
         <v>24</v>
       </c>
@@ -14195,7 +14195,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="641" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641" s="27" t="s">
         <v>26</v>
       </c>
@@ -14215,7 +14215,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="642" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A642" s="4" t="s">
         <v>28</v>
       </c>
@@ -14235,7 +14235,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="643" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A643" s="4" t="s">
         <v>30</v>
       </c>
@@ -14255,7 +14255,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="644" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A644" s="4" t="s">
         <v>68</v>
       </c>
@@ -14275,7 +14275,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="645" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645" s="4" t="s">
         <v>6</v>
       </c>
@@ -14295,7 +14295,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="646" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A646" s="4" t="s">
         <v>6</v>
       </c>
@@ -14315,7 +14315,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="647" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647" s="4" t="s">
         <v>6</v>
       </c>
@@ -14335,7 +14335,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="648" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A648" s="4" t="s">
         <v>11</v>
       </c>
@@ -14355,7 +14355,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="649" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A649" s="4" t="s">
         <v>11</v>
       </c>
@@ -14375,7 +14375,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="650" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A650" s="4" t="s">
         <v>24</v>
       </c>
@@ -14395,7 +14395,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="651" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651" s="27" t="s">
         <v>26</v>
       </c>
@@ -14415,7 +14415,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="652" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A652" s="4" t="s">
         <v>28</v>
       </c>
@@ -14435,7 +14435,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="653" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653" s="4" t="s">
         <v>30</v>
       </c>
@@ -14455,7 +14455,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="654" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A654" s="4" t="s">
         <v>68</v>
       </c>
@@ -14475,7 +14475,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="655" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A655" s="4" t="s">
         <v>6</v>
       </c>
@@ -14495,7 +14495,7 @@
         <v>46284</v>
       </c>
     </row>
-    <row r="656" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656" s="4" t="s">
         <v>6</v>
       </c>
@@ -14515,7 +14515,7 @@
         <v>46284</v>
       </c>
     </row>
-    <row r="657" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657" s="4" t="s">
         <v>6</v>
       </c>
@@ -14535,7 +14535,7 @@
         <v>46284</v>
       </c>
     </row>
-    <row r="658" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A658" s="4" t="s">
         <v>11</v>
       </c>
@@ -14555,7 +14555,7 @@
         <v>46284</v>
       </c>
     </row>
-    <row r="659" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659" s="4" t="s">
         <v>11</v>
       </c>
@@ -14575,7 +14575,7 @@
         <v>46284</v>
       </c>
     </row>
-    <row r="660" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A660" s="4" t="s">
         <v>24</v>
       </c>
@@ -14595,7 +14595,7 @@
         <v>46284</v>
       </c>
     </row>
-    <row r="661" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A661" s="27" t="s">
         <v>26</v>
       </c>
@@ -14615,7 +14615,7 @@
         <v>46284</v>
       </c>
     </row>
-    <row r="662" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A662" s="4" t="s">
         <v>28</v>
       </c>
@@ -14635,7 +14635,7 @@
         <v>46284</v>
       </c>
     </row>
-    <row r="663" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A663" s="4" t="s">
         <v>30</v>
       </c>
@@ -14655,7 +14655,7 @@
         <v>46284</v>
       </c>
     </row>
-    <row r="664" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A664" s="4" t="s">
         <v>68</v>
       </c>
@@ -14675,7 +14675,7 @@
         <v>46284</v>
       </c>
     </row>
-    <row r="665" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A665" s="4" t="s">
         <v>6</v>
       </c>
@@ -14695,7 +14695,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="666" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A666" s="4" t="s">
         <v>6</v>
       </c>
@@ -14715,7 +14715,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="667" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A667" s="4" t="s">
         <v>6</v>
       </c>
@@ -14735,7 +14735,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="668" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A668" s="4" t="s">
         <v>11</v>
       </c>
@@ -14755,7 +14755,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="669" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A669" s="4" t="s">
         <v>11</v>
       </c>
@@ -14775,7 +14775,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="670" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A670" s="4" t="s">
         <v>24</v>
       </c>
@@ -14795,7 +14795,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="671" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A671" s="27" t="s">
         <v>26</v>
       </c>
@@ -14815,7 +14815,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="672" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A672" s="4" t="s">
         <v>28</v>
       </c>
@@ -14835,7 +14835,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="673" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A673" s="4" t="s">
         <v>30</v>
       </c>
@@ -14855,7 +14855,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="674" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A674" s="4" t="s">
         <v>68</v>
       </c>
@@ -14875,7 +14875,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="675" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A675" s="4" t="s">
         <v>6</v>
       </c>
@@ -14895,7 +14895,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="676" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A676" s="4" t="s">
         <v>6</v>
       </c>
@@ -14915,7 +14915,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="677" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A677" s="4" t="s">
         <v>6</v>
       </c>
@@ -14935,7 +14935,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="678" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A678" s="4" t="s">
         <v>11</v>
       </c>
@@ -14955,7 +14955,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="679" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A679" s="4" t="s">
         <v>11</v>
       </c>
@@ -14975,7 +14975,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="680" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A680" s="4" t="s">
         <v>24</v>
       </c>
@@ -14995,7 +14995,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="681" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A681" s="27" t="s">
         <v>26</v>
       </c>
@@ -15015,7 +15015,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="682" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A682" s="4" t="s">
         <v>28</v>
       </c>
@@ -15035,7 +15035,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="683" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A683" s="4" t="s">
         <v>30</v>
       </c>
@@ -15055,7 +15055,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="684" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A684" s="4" t="s">
         <v>68</v>
       </c>
@@ -15075,7 +15075,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="685" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A685" s="4" t="s">
         <v>6</v>
       </c>
@@ -15095,7 +15095,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="686" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A686" s="4" t="s">
         <v>6</v>
       </c>
@@ -15115,7 +15115,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="687" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687" s="4" t="s">
         <v>6</v>
       </c>
@@ -15135,7 +15135,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="688" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A688" s="4" t="s">
         <v>11</v>
       </c>
@@ -15155,7 +15155,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="689" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689" s="4" t="s">
         <v>11</v>
       </c>
@@ -15175,7 +15175,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="690" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A690" s="4" t="s">
         <v>24</v>
       </c>
@@ -15195,7 +15195,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="691" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A691" s="27" t="s">
         <v>26</v>
       </c>
@@ -15215,7 +15215,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="692" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A692" s="4" t="s">
         <v>28</v>
       </c>
@@ -15235,7 +15235,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="693" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693" s="4" t="s">
         <v>30</v>
       </c>
@@ -15255,7 +15255,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="694" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A694" s="4" t="s">
         <v>68</v>
       </c>
@@ -15275,7 +15275,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="695" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695" s="4" t="s">
         <v>6</v>
       </c>
@@ -15295,7 +15295,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="696" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A696" s="4" t="s">
         <v>6</v>
       </c>
@@ -15315,7 +15315,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="697" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A697" s="4" t="s">
         <v>6</v>
       </c>
@@ -15335,7 +15335,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="698" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A698" s="4" t="s">
         <v>11</v>
       </c>
@@ -15355,7 +15355,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="699" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A699" s="4" t="s">
         <v>11</v>
       </c>
@@ -15375,7 +15375,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="700" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A700" s="4" t="s">
         <v>24</v>
       </c>
@@ -15395,7 +15395,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="701" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A701" s="27" t="s">
         <v>26</v>
       </c>
@@ -15415,7 +15415,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="702" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A702" s="4" t="s">
         <v>28</v>
       </c>
@@ -15435,7 +15435,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="703" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A703" s="4" t="s">
         <v>30</v>
       </c>
@@ -15455,7 +15455,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="704" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A704" s="4" t="s">
         <v>68</v>
       </c>
@@ -15475,7 +15475,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="705" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A705" s="4" t="s">
         <v>6</v>
       </c>
@@ -15495,7 +15495,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="706" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A706" s="4" t="s">
         <v>6</v>
       </c>
@@ -15515,7 +15515,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="707" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707" s="4" t="s">
         <v>6</v>
       </c>
@@ -15535,7 +15535,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="708" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A708" s="4" t="s">
         <v>11</v>
       </c>
@@ -15555,7 +15555,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="709" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A709" s="4" t="s">
         <v>11</v>
       </c>
@@ -15575,7 +15575,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="710" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A710" s="4" t="s">
         <v>24</v>
       </c>
@@ -15595,7 +15595,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="711" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A711" s="27" t="s">
         <v>26</v>
       </c>
@@ -15615,7 +15615,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="712" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A712" s="4" t="s">
         <v>28</v>
       </c>
@@ -15635,7 +15635,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="713" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A713" s="4" t="s">
         <v>30</v>
       </c>
@@ -15655,7 +15655,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="714" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A714" s="4" t="s">
         <v>68</v>
       </c>
@@ -15675,7 +15675,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="715" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A715" s="4" t="s">
         <v>6</v>
       </c>
@@ -15695,7 +15695,7 @@
         <v>46291</v>
       </c>
     </row>
-    <row r="716" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A716" s="4" t="s">
         <v>6</v>
       </c>
@@ -15715,7 +15715,7 @@
         <v>46291</v>
       </c>
     </row>
-    <row r="717" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A717" s="4" t="s">
         <v>6</v>
       </c>
@@ -15735,7 +15735,7 @@
         <v>46291</v>
       </c>
     </row>
-    <row r="718" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A718" s="4" t="s">
         <v>11</v>
       </c>
@@ -15755,7 +15755,7 @@
         <v>46291</v>
       </c>
     </row>
-    <row r="719" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A719" s="4" t="s">
         <v>11</v>
       </c>
@@ -15775,7 +15775,7 @@
         <v>46291</v>
       </c>
     </row>
-    <row r="720" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A720" s="4" t="s">
         <v>24</v>
       </c>
@@ -15795,7 +15795,7 @@
         <v>46291</v>
       </c>
     </row>
-    <row r="721" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A721" s="27" t="s">
         <v>26</v>
       </c>
@@ -15815,7 +15815,7 @@
         <v>46291</v>
       </c>
     </row>
-    <row r="722" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A722" s="4" t="s">
         <v>28</v>
       </c>
@@ -15835,7 +15835,7 @@
         <v>46291</v>
       </c>
     </row>
-    <row r="723" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A723" s="4" t="s">
         <v>30</v>
       </c>
@@ -15855,7 +15855,7 @@
         <v>46291</v>
       </c>
     </row>
-    <row r="724" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A724" s="4" t="s">
         <v>68</v>
       </c>
@@ -15875,7 +15875,7 @@
         <v>46291</v>
       </c>
     </row>
-    <row r="725" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A725" s="4" t="s">
         <v>6</v>
       </c>
@@ -15895,7 +15895,7 @@
         <v>46293</v>
       </c>
     </row>
-    <row r="726" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A726" s="4" t="s">
         <v>6</v>
       </c>
@@ -15915,7 +15915,7 @@
         <v>46293</v>
       </c>
     </row>
-    <row r="727" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A727" s="4" t="s">
         <v>6</v>
       </c>
@@ -15935,7 +15935,7 @@
         <v>46293</v>
       </c>
     </row>
-    <row r="728" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A728" s="4" t="s">
         <v>11</v>
       </c>
@@ -15955,7 +15955,7 @@
         <v>46293</v>
       </c>
     </row>
-    <row r="729" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A729" s="4" t="s">
         <v>11</v>
       </c>
@@ -15975,7 +15975,7 @@
         <v>46293</v>
       </c>
     </row>
-    <row r="730" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A730" s="4" t="s">
         <v>24</v>
       </c>
@@ -15995,7 +15995,7 @@
         <v>46293</v>
       </c>
     </row>
-    <row r="731" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A731" s="27" t="s">
         <v>26</v>
       </c>
@@ -16015,7 +16015,7 @@
         <v>46293</v>
       </c>
     </row>
-    <row r="732" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A732" s="4" t="s">
         <v>28</v>
       </c>
@@ -16035,7 +16035,7 @@
         <v>46293</v>
       </c>
     </row>
-    <row r="733" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A733" s="4" t="s">
         <v>30</v>
       </c>
@@ -16055,7 +16055,7 @@
         <v>46293</v>
       </c>
     </row>
-    <row r="734" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A734" s="4" t="s">
         <v>68</v>
       </c>
@@ -16075,7 +16075,7 @@
         <v>46293</v>
       </c>
     </row>
-    <row r="735" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A735" s="4" t="s">
         <v>6</v>
       </c>
@@ -16095,7 +16095,7 @@
         <v>46294</v>
       </c>
     </row>
-    <row r="736" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A736" s="4" t="s">
         <v>6</v>
       </c>
@@ -16115,7 +16115,7 @@
         <v>46294</v>
       </c>
     </row>
-    <row r="737" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A737" s="4" t="s">
         <v>6</v>
       </c>
@@ -16135,7 +16135,7 @@
         <v>46294</v>
       </c>
     </row>
-    <row r="738" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A738" s="4" t="s">
         <v>11</v>
       </c>
@@ -16155,7 +16155,7 @@
         <v>46294</v>
       </c>
     </row>
-    <row r="739" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A739" s="4" t="s">
         <v>11</v>
       </c>
@@ -16175,7 +16175,7 @@
         <v>46294</v>
       </c>
     </row>
-    <row r="740" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A740" s="4" t="s">
         <v>24</v>
       </c>
@@ -16195,7 +16195,7 @@
         <v>46294</v>
       </c>
     </row>
-    <row r="741" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A741" s="27" t="s">
         <v>26</v>
       </c>
@@ -16215,7 +16215,7 @@
         <v>46294</v>
       </c>
     </row>
-    <row r="742" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A742" s="4" t="s">
         <v>28</v>
       </c>
@@ -16235,7 +16235,7 @@
         <v>46294</v>
       </c>
     </row>
-    <row r="743" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A743" s="4" t="s">
         <v>30</v>
       </c>
@@ -16255,7 +16255,7 @@
         <v>46294</v>
       </c>
     </row>
-    <row r="744" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A744" s="4" t="s">
         <v>68</v>
       </c>
@@ -16275,7 +16275,7 @@
         <v>46294</v>
       </c>
     </row>
-    <row r="745" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A745" s="4" t="s">
         <v>6</v>
       </c>
@@ -16295,7 +16295,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="746" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A746" s="4" t="s">
         <v>6</v>
       </c>
@@ -16315,7 +16315,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="747" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A747" s="4" t="s">
         <v>6</v>
       </c>
@@ -16335,7 +16335,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="748" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A748" s="4" t="s">
         <v>11</v>
       </c>
@@ -16355,7 +16355,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="749" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A749" s="4" t="s">
         <v>11</v>
       </c>
@@ -16375,7 +16375,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="750" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A750" s="4" t="s">
         <v>24</v>
       </c>
@@ -16395,7 +16395,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="751" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A751" s="27" t="s">
         <v>26</v>
       </c>
@@ -16415,7 +16415,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="752" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A752" s="4" t="s">
         <v>28</v>
       </c>
@@ -16435,7 +16435,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="753" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A753" s="4" t="s">
         <v>30</v>
       </c>
@@ -16455,7 +16455,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="754" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A754" s="4" t="s">
         <v>68</v>
       </c>
@@ -20740,6 +20740,9 @@
       <c r="C965" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="D965" s="6">
+        <v>1882.5</v>
+      </c>
       <c r="E965" s="18">
         <v>4117.5</v>
       </c>
@@ -20757,6 +20760,9 @@
       <c r="C966" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="D966" s="6">
+        <v>2779.5</v>
+      </c>
       <c r="E966" s="18">
         <v>3660</v>
       </c>
@@ -20773,6 +20779,9 @@
       </c>
       <c r="C967" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="D967" s="6">
+        <v>688.5</v>
       </c>
       <c r="E967" s="18">
         <v>1372.5</v>
@@ -20791,6 +20800,9 @@
       <c r="C968" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="D968" s="6">
+        <v>2042.5</v>
+      </c>
       <c r="E968" s="18">
         <v>3450</v>
       </c>
@@ -20808,6 +20820,9 @@
       <c r="C969" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D969" s="6">
+        <v>1973</v>
+      </c>
       <c r="E969" s="18">
         <v>2300</v>
       </c>
@@ -20825,6 +20840,9 @@
       <c r="C970" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="D970" s="6">
+        <v>816.5</v>
+      </c>
       <c r="E970" s="18">
         <v>1500</v>
       </c>
@@ -20842,6 +20860,9 @@
       <c r="C971" s="27" t="s">
         <v>25</v>
       </c>
+      <c r="D971" s="6">
+        <v>1130</v>
+      </c>
       <c r="E971" s="18">
         <v>1510</v>
       </c>
@@ -20859,6 +20880,9 @@
       <c r="C972" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="D972" s="6">
+        <v>315</v>
+      </c>
       <c r="E972" s="18">
         <v>1000</v>
       </c>
@@ -20876,6 +20900,9 @@
       <c r="C973" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="D973" s="6">
+        <v>871.5</v>
+      </c>
       <c r="E973" s="18">
         <v>1305</v>
       </c>
@@ -20893,6 +20920,9 @@
       <c r="C974" s="4" t="s">
         <v>70</v>
       </c>
+      <c r="D974" s="6">
+        <v>295</v>
+      </c>
       <c r="E974" s="18">
         <v>800</v>
       </c>
@@ -21478,7 +21508,7 @@
         <v>46325</v>
       </c>
     </row>
-    <row r="1009" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1009" s="4" t="s">
         <v>11</v>
       </c>
@@ -21495,7 +21525,7 @@
         <v>46325</v>
       </c>
     </row>
-    <row r="1010" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1010" s="4" t="s">
         <v>24</v>
       </c>
@@ -21512,7 +21542,7 @@
         <v>46325</v>
       </c>
     </row>
-    <row r="1011" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1011" s="27" t="s">
         <v>26</v>
       </c>
@@ -21529,7 +21559,7 @@
         <v>46325</v>
       </c>
     </row>
-    <row r="1012" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1012" s="4" t="s">
         <v>28</v>
       </c>
@@ -21546,7 +21576,7 @@
         <v>46325</v>
       </c>
     </row>
-    <row r="1013" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1013" s="4" t="s">
         <v>30</v>
       </c>
@@ -21563,7 +21593,7 @@
         <v>46325</v>
       </c>
     </row>
-    <row r="1014" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1014" s="4" t="s">
         <v>68</v>
       </c>
@@ -21580,7 +21610,7 @@
         <v>46325</v>
       </c>
     </row>
-    <row r="1015" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1015" s="4" t="s">
         <v>6</v>
       </c>
@@ -21597,7 +21627,7 @@
         <v>46326</v>
       </c>
     </row>
-    <row r="1016" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1016" s="4" t="s">
         <v>6</v>
       </c>
@@ -21614,7 +21644,7 @@
         <v>46326</v>
       </c>
     </row>
-    <row r="1017" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1017" s="4" t="s">
         <v>6</v>
       </c>
@@ -21631,7 +21661,7 @@
         <v>46326</v>
       </c>
     </row>
-    <row r="1018" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1018" s="4" t="s">
         <v>11</v>
       </c>
@@ -21648,7 +21678,7 @@
         <v>46326</v>
       </c>
     </row>
-    <row r="1019" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1019" s="4" t="s">
         <v>11</v>
       </c>
@@ -21665,7 +21695,7 @@
         <v>46326</v>
       </c>
     </row>
-    <row r="1020" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1020" s="4" t="s">
         <v>24</v>
       </c>
@@ -21682,7 +21712,7 @@
         <v>46326</v>
       </c>
     </row>
-    <row r="1021" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1021" s="27" t="s">
         <v>26</v>
       </c>
@@ -21699,7 +21729,7 @@
         <v>46326</v>
       </c>
     </row>
-    <row r="1022" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1022" s="4" t="s">
         <v>28</v>
       </c>
@@ -21716,7 +21746,7 @@
         <v>46326</v>
       </c>
     </row>
-    <row r="1023" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1023" s="4" t="s">
         <v>30</v>
       </c>
@@ -21732,8 +21762,9 @@
       <c r="F1023" s="5">
         <v>46326</v>
       </c>
-    </row>
-    <row r="1024" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H1023" s="5"/>
+    </row>
+    <row r="1024" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1024" s="4" t="s">
         <v>68</v>
       </c>
@@ -21749,13 +21780,3863 @@
       <c r="F1024" s="5">
         <v>46326</v>
       </c>
+      <c r="H1024" s="5"/>
+    </row>
+    <row r="1025" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1025" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1025" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1025" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1025" s="5">
+        <v>46328</v>
+      </c>
+      <c r="H1025" s="5"/>
+    </row>
+    <row r="1026" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1026" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1026" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1026" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1026" s="5">
+        <v>46328</v>
+      </c>
+      <c r="H1026" s="5"/>
+    </row>
+    <row r="1027" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1027" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1027" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1027" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1027" s="5">
+        <v>46328</v>
+      </c>
+      <c r="H1027" s="5"/>
+    </row>
+    <row r="1028" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1028" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1028" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1028" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1028" s="5">
+        <v>46328</v>
+      </c>
+      <c r="H1028" s="5"/>
+    </row>
+    <row r="1029" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1029" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1029" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1029" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1029" s="5">
+        <v>46328</v>
+      </c>
+      <c r="H1029" s="5"/>
+    </row>
+    <row r="1030" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1030" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1030" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1030" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1030" s="5">
+        <v>46328</v>
+      </c>
+      <c r="H1030" s="5"/>
+    </row>
+    <row r="1031" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1031" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1031" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1031" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1031" s="5">
+        <v>46328</v>
+      </c>
+      <c r="H1031" s="5"/>
+    </row>
+    <row r="1032" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1032" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1032" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1032" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1032" s="5">
+        <v>46328</v>
+      </c>
+      <c r="H1032" s="5"/>
+    </row>
+    <row r="1033" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1033" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1033" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1033" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1033" s="5">
+        <v>46328</v>
+      </c>
+      <c r="H1033" s="5"/>
+    </row>
+    <row r="1034" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1034" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1034" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1034" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1034" s="5">
+        <v>46328</v>
+      </c>
+      <c r="H1034" s="5"/>
+    </row>
+    <row r="1035" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1035" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1035" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1035" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1035" s="5">
+        <v>46329</v>
+      </c>
+      <c r="H1035" s="5"/>
+    </row>
+    <row r="1036" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1036" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1036" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1036" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1036" s="5">
+        <v>46329</v>
+      </c>
+      <c r="H1036" s="5"/>
+    </row>
+    <row r="1037" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1037" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1037" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1037" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1037" s="5">
+        <v>46329</v>
+      </c>
+      <c r="H1037" s="5"/>
+    </row>
+    <row r="1038" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1038" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1038" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1038" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1038" s="5">
+        <v>46329</v>
+      </c>
+      <c r="H1038" s="5"/>
+    </row>
+    <row r="1039" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1039" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1039" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1039" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1039" s="5">
+        <v>46329</v>
+      </c>
+      <c r="H1039" s="5"/>
+    </row>
+    <row r="1040" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1040" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1040" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1040" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1040" s="5">
+        <v>46329</v>
+      </c>
+      <c r="H1040" s="5"/>
+    </row>
+    <row r="1041" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1041" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1041" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1041" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1041" s="5">
+        <v>46329</v>
+      </c>
+      <c r="H1041" s="5"/>
+    </row>
+    <row r="1042" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1042" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1042" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1042" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1042" s="5">
+        <v>46329</v>
+      </c>
+      <c r="H1042" s="5"/>
+    </row>
+    <row r="1043" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1043" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1043" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1043" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1043" s="5">
+        <v>46329</v>
+      </c>
+      <c r="H1043" s="5"/>
+    </row>
+    <row r="1044" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1044" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1044" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1044" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1044" s="5">
+        <v>46329</v>
+      </c>
+      <c r="H1044" s="5"/>
+    </row>
+    <row r="1045" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1045" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1045" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1045" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1045" s="5">
+        <v>46330</v>
+      </c>
+      <c r="H1045" s="5"/>
+    </row>
+    <row r="1046" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1046" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1046" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1046" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1046" s="5">
+        <v>46330</v>
+      </c>
+      <c r="H1046" s="5"/>
+    </row>
+    <row r="1047" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1047" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1047" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1047" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1047" s="5">
+        <v>46330</v>
+      </c>
+      <c r="H1047" s="5"/>
+    </row>
+    <row r="1048" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1048" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1048" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1048" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1048" s="5">
+        <v>46330</v>
+      </c>
+      <c r="H1048" s="5"/>
+    </row>
+    <row r="1049" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1049" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1049" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1049" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1049" s="5">
+        <v>46330</v>
+      </c>
+      <c r="H1049" s="5"/>
+    </row>
+    <row r="1050" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1050" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1050" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1050" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1050" s="5">
+        <v>46330</v>
+      </c>
+      <c r="H1050" s="5"/>
+    </row>
+    <row r="1051" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1051" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1051" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1051" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1051" s="5">
+        <v>46330</v>
+      </c>
+      <c r="H1051" s="5"/>
+    </row>
+    <row r="1052" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1052" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1052" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1052" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1052" s="5">
+        <v>46330</v>
+      </c>
+      <c r="H1052" s="5"/>
+    </row>
+    <row r="1053" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1053" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1053" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1053" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1053" s="5">
+        <v>46330</v>
+      </c>
+      <c r="H1053" s="5"/>
+    </row>
+    <row r="1054" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1054" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1054" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1054" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1054" s="5">
+        <v>46330</v>
+      </c>
+      <c r="H1054" s="5"/>
+    </row>
+    <row r="1055" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1055" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1055" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1055" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1055" s="5">
+        <v>46331</v>
+      </c>
+      <c r="H1055" s="5"/>
+    </row>
+    <row r="1056" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1056" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1056" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1056" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1056" s="5">
+        <v>46331</v>
+      </c>
+      <c r="H1056" s="5"/>
+    </row>
+    <row r="1057" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1057" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1057" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1057" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1057" s="5">
+        <v>46331</v>
+      </c>
+      <c r="H1057" s="5"/>
+    </row>
+    <row r="1058" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1058" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1058" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1058" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1058" s="5">
+        <v>46331</v>
+      </c>
+      <c r="H1058" s="5"/>
+    </row>
+    <row r="1059" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1059" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1059" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1059" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1059" s="5">
+        <v>46331</v>
+      </c>
+      <c r="H1059" s="5"/>
+    </row>
+    <row r="1060" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1060" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1060" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1060" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1060" s="5">
+        <v>46331</v>
+      </c>
+      <c r="H1060" s="5"/>
+    </row>
+    <row r="1061" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1061" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1061" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1061" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1061" s="5">
+        <v>46331</v>
+      </c>
+      <c r="H1061" s="5"/>
+    </row>
+    <row r="1062" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1062" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1062" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1062" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1062" s="5">
+        <v>46331</v>
+      </c>
+      <c r="H1062" s="5"/>
+    </row>
+    <row r="1063" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1063" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1063" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1063" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1063" s="5">
+        <v>46331</v>
+      </c>
+      <c r="H1063" s="5"/>
+    </row>
+    <row r="1064" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1064" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1064" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1064" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1064" s="5">
+        <v>46331</v>
+      </c>
+      <c r="H1064" s="5"/>
+    </row>
+    <row r="1065" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1065" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1065" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1065" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1065" s="5">
+        <v>46332</v>
+      </c>
+      <c r="H1065" s="5"/>
+    </row>
+    <row r="1066" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1066" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1066" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1066" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1066" s="5">
+        <v>46332</v>
+      </c>
+      <c r="H1066" s="5"/>
+    </row>
+    <row r="1067" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1067" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1067" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1067" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1067" s="5">
+        <v>46332</v>
+      </c>
+      <c r="H1067" s="5"/>
+    </row>
+    <row r="1068" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1068" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1068" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1068" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1068" s="5">
+        <v>46332</v>
+      </c>
+      <c r="H1068" s="5"/>
+    </row>
+    <row r="1069" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1069" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1069" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1069" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1069" s="5">
+        <v>46332</v>
+      </c>
+      <c r="H1069" s="5"/>
+    </row>
+    <row r="1070" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1070" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1070" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1070" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1070" s="5">
+        <v>46332</v>
+      </c>
+      <c r="H1070" s="5"/>
+    </row>
+    <row r="1071" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1071" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1071" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1071" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1071" s="5">
+        <v>46332</v>
+      </c>
+      <c r="H1071" s="5"/>
+    </row>
+    <row r="1072" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1072" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1072" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1072" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1072" s="5">
+        <v>46332</v>
+      </c>
+      <c r="H1072" s="5"/>
+    </row>
+    <row r="1073" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1073" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1073" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1073" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1073" s="5">
+        <v>46332</v>
+      </c>
+      <c r="H1073" s="5"/>
+    </row>
+    <row r="1074" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1074" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1074" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1074" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1074" s="5">
+        <v>46332</v>
+      </c>
+      <c r="H1074" s="5"/>
+    </row>
+    <row r="1075" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1075" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1075" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1075" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1075" s="5">
+        <v>46333</v>
+      </c>
+      <c r="H1075" s="5"/>
+    </row>
+    <row r="1076" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1076" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1076" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1076" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1076" s="5">
+        <v>46333</v>
+      </c>
+      <c r="H1076" s="5"/>
+    </row>
+    <row r="1077" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1077" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1077" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1077" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1077" s="5">
+        <v>46333</v>
+      </c>
+      <c r="H1077" s="5"/>
+    </row>
+    <row r="1078" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1078" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1078" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1078" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1078" s="5">
+        <v>46333</v>
+      </c>
+      <c r="H1078" s="5"/>
+    </row>
+    <row r="1079" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1079" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1079" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1079" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1079" s="5">
+        <v>46333</v>
+      </c>
+      <c r="H1079" s="5"/>
+    </row>
+    <row r="1080" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1080" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1080" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1080" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1080" s="5">
+        <v>46333</v>
+      </c>
+      <c r="H1080" s="5"/>
+    </row>
+    <row r="1081" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1081" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1081" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1081" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1081" s="5">
+        <v>46333</v>
+      </c>
+      <c r="H1081" s="5"/>
+    </row>
+    <row r="1082" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1082" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1082" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1082" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1082" s="5">
+        <v>46333</v>
+      </c>
+      <c r="H1082" s="5"/>
+    </row>
+    <row r="1083" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1083" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1083" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1083" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1083" s="5">
+        <v>46333</v>
+      </c>
+      <c r="H1083" s="5"/>
+    </row>
+    <row r="1084" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1084" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1084" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1084" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1084" s="5">
+        <v>46333</v>
+      </c>
+      <c r="H1084" s="5"/>
+    </row>
+    <row r="1085" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1085" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1085" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1085" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1085" s="5">
+        <v>46335</v>
+      </c>
+      <c r="H1085" s="5"/>
+    </row>
+    <row r="1086" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1086" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1086" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1086" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1086" s="5">
+        <v>46335</v>
+      </c>
+      <c r="H1086" s="5"/>
+    </row>
+    <row r="1087" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1087" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1087" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1087" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1087" s="5">
+        <v>46335</v>
+      </c>
+      <c r="H1087" s="5"/>
+    </row>
+    <row r="1088" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1088" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1088" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1088" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1088" s="5">
+        <v>46335</v>
+      </c>
+      <c r="H1088" s="5"/>
+    </row>
+    <row r="1089" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1089" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1089" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1089" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1089" s="5">
+        <v>46335</v>
+      </c>
+      <c r="H1089" s="5"/>
+    </row>
+    <row r="1090" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1090" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1090" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1090" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1090" s="5">
+        <v>46335</v>
+      </c>
+      <c r="H1090" s="5"/>
+    </row>
+    <row r="1091" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1091" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1091" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1091" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1091" s="5">
+        <v>46335</v>
+      </c>
+      <c r="H1091" s="5"/>
+    </row>
+    <row r="1092" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1092" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1092" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1092" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1092" s="5">
+        <v>46335</v>
+      </c>
+      <c r="H1092" s="5"/>
+    </row>
+    <row r="1093" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1093" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1093" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1093" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1093" s="5">
+        <v>46335</v>
+      </c>
+      <c r="H1093" s="5"/>
+    </row>
+    <row r="1094" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1094" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1094" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1094" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1094" s="5">
+        <v>46335</v>
+      </c>
+      <c r="H1094" s="5"/>
+    </row>
+    <row r="1095" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1095" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1095" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1095" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1095" s="5">
+        <v>46336</v>
+      </c>
+      <c r="H1095" s="5"/>
+    </row>
+    <row r="1096" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1096" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1096" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1096" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1096" s="5">
+        <v>46336</v>
+      </c>
+      <c r="H1096" s="5"/>
+    </row>
+    <row r="1097" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1097" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1097" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1097" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1097" s="5">
+        <v>46336</v>
+      </c>
+      <c r="H1097" s="5"/>
+    </row>
+    <row r="1098" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1098" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1098" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1098" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1098" s="5">
+        <v>46336</v>
+      </c>
+      <c r="H1098" s="5"/>
+    </row>
+    <row r="1099" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1099" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1099" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1099" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1099" s="5">
+        <v>46336</v>
+      </c>
+      <c r="H1099" s="5"/>
+    </row>
+    <row r="1100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1100" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1100" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1100" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1100" s="5">
+        <v>46336</v>
+      </c>
+      <c r="H1100" s="5"/>
+    </row>
+    <row r="1101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1101" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1101" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1101" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1101" s="5">
+        <v>46336</v>
+      </c>
+      <c r="H1101" s="5"/>
+    </row>
+    <row r="1102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1102" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1102" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1102" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1102" s="5">
+        <v>46336</v>
+      </c>
+      <c r="H1102" s="5"/>
+    </row>
+    <row r="1103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1103" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1103" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1103" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1103" s="5">
+        <v>46336</v>
+      </c>
+      <c r="H1103" s="5"/>
+    </row>
+    <row r="1104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1104" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1104" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1104" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1104" s="5">
+        <v>46336</v>
+      </c>
+      <c r="H1104" s="5"/>
+    </row>
+    <row r="1105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1105" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1105" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1105" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1105" s="5">
+        <v>46337</v>
+      </c>
+      <c r="H1105" s="5"/>
+    </row>
+    <row r="1106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1106" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1106" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1106" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1106" s="5">
+        <v>46337</v>
+      </c>
+      <c r="H1106" s="5"/>
+    </row>
+    <row r="1107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1107" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1107" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1107" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1107" s="5">
+        <v>46337</v>
+      </c>
+      <c r="H1107" s="5"/>
+    </row>
+    <row r="1108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1108" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1108" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1108" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1108" s="5">
+        <v>46337</v>
+      </c>
+      <c r="H1108" s="5"/>
+    </row>
+    <row r="1109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1109" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1109" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1109" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1109" s="5">
+        <v>46337</v>
+      </c>
+      <c r="H1109" s="5"/>
+    </row>
+    <row r="1110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1110" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1110" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1110" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1110" s="5">
+        <v>46337</v>
+      </c>
+      <c r="H1110" s="5"/>
+    </row>
+    <row r="1111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1111" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1111" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1111" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1111" s="5">
+        <v>46337</v>
+      </c>
+      <c r="H1111" s="5"/>
+    </row>
+    <row r="1112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1112" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1112" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1112" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1112" s="5">
+        <v>46337</v>
+      </c>
+      <c r="H1112" s="5"/>
+    </row>
+    <row r="1113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1113" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1113" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1113" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1113" s="5">
+        <v>46337</v>
+      </c>
+      <c r="H1113" s="5"/>
+    </row>
+    <row r="1114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1114" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1114" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1114" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1114" s="5">
+        <v>46337</v>
+      </c>
+      <c r="H1114" s="5"/>
+    </row>
+    <row r="1115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1115" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1115" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1115" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1115" s="5">
+        <v>46338</v>
+      </c>
+      <c r="H1115" s="5"/>
+    </row>
+    <row r="1116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1116" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1116" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1116" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1116" s="5">
+        <v>46338</v>
+      </c>
+      <c r="H1116" s="5"/>
+    </row>
+    <row r="1117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1117" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1117" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1117" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1117" s="5">
+        <v>46338</v>
+      </c>
+      <c r="H1117" s="5"/>
+    </row>
+    <row r="1118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1118" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1118" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1118" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1118" s="5">
+        <v>46338</v>
+      </c>
+      <c r="H1118" s="5"/>
+    </row>
+    <row r="1119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1119" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1119" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1119" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1119" s="5">
+        <v>46338</v>
+      </c>
+      <c r="H1119" s="5"/>
+    </row>
+    <row r="1120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1120" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1120" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1120" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1120" s="5">
+        <v>46338</v>
+      </c>
+      <c r="H1120" s="5"/>
+    </row>
+    <row r="1121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1121" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1121" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1121" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1121" s="5">
+        <v>46338</v>
+      </c>
+      <c r="H1121" s="5"/>
+    </row>
+    <row r="1122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1122" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1122" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1122" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1122" s="5">
+        <v>46338</v>
+      </c>
+      <c r="H1122" s="5"/>
+    </row>
+    <row r="1123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1123" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1123" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1123" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1123" s="5">
+        <v>46338</v>
+      </c>
+      <c r="H1123" s="5"/>
+    </row>
+    <row r="1124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1124" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1124" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1124" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1124" s="5">
+        <v>46338</v>
+      </c>
+      <c r="H1124" s="5"/>
+    </row>
+    <row r="1125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1125" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1125" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1125" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1125" s="5">
+        <v>46339</v>
+      </c>
+      <c r="H1125" s="5"/>
+    </row>
+    <row r="1126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1126" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1126" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1126" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1126" s="5">
+        <v>46339</v>
+      </c>
+      <c r="H1126" s="5"/>
+    </row>
+    <row r="1127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1127" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1127" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1127" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1127" s="5">
+        <v>46339</v>
+      </c>
+      <c r="H1127" s="5"/>
+    </row>
+    <row r="1128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1128" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1128" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1128" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1128" s="5">
+        <v>46339</v>
+      </c>
+      <c r="H1128" s="5"/>
+    </row>
+    <row r="1129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1129" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1129" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1129" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1129" s="5">
+        <v>46339</v>
+      </c>
+      <c r="H1129" s="5"/>
+    </row>
+    <row r="1130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1130" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1130" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1130" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1130" s="5">
+        <v>46339</v>
+      </c>
+      <c r="H1130" s="5"/>
+    </row>
+    <row r="1131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1131" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1131" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1131" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1131" s="5">
+        <v>46339</v>
+      </c>
+      <c r="H1131" s="5"/>
+    </row>
+    <row r="1132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1132" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1132" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1132" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1132" s="5">
+        <v>46339</v>
+      </c>
+      <c r="H1132" s="5"/>
+    </row>
+    <row r="1133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1133" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1133" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1133" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1133" s="5">
+        <v>46339</v>
+      </c>
+      <c r="H1133" s="5"/>
+    </row>
+    <row r="1134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1134" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1134" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1134" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1134" s="5">
+        <v>46339</v>
+      </c>
+      <c r="H1134" s="5"/>
+    </row>
+    <row r="1135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1135" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1135" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1135" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1135" s="5">
+        <v>46340</v>
+      </c>
+      <c r="H1135" s="5"/>
+    </row>
+    <row r="1136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1136" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1136" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1136" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1136" s="5">
+        <v>46340</v>
+      </c>
+      <c r="H1136" s="5"/>
+    </row>
+    <row r="1137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1137" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1137" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1137" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1137" s="5">
+        <v>46340</v>
+      </c>
+      <c r="H1137" s="5"/>
+    </row>
+    <row r="1138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1138" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1138" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1138" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1138" s="5">
+        <v>46340</v>
+      </c>
+      <c r="H1138" s="5"/>
+    </row>
+    <row r="1139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1139" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1139" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1139" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1139" s="5">
+        <v>46340</v>
+      </c>
+      <c r="H1139" s="5"/>
+    </row>
+    <row r="1140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1140" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1140" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1140" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1140" s="5">
+        <v>46340</v>
+      </c>
+      <c r="H1140" s="5"/>
+    </row>
+    <row r="1141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1141" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1141" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1141" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1141" s="5">
+        <v>46340</v>
+      </c>
+      <c r="H1141" s="5"/>
+    </row>
+    <row r="1142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1142" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1142" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1142" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1142" s="5">
+        <v>46340</v>
+      </c>
+      <c r="H1142" s="5"/>
+    </row>
+    <row r="1143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1143" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1143" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1143" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1143" s="5">
+        <v>46340</v>
+      </c>
+      <c r="H1143" s="5"/>
+    </row>
+    <row r="1144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1144" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1144" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1144" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1144" s="5">
+        <v>46340</v>
+      </c>
+      <c r="H1144" s="5"/>
+    </row>
+    <row r="1145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1145" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1145" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1145" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1145" s="5">
+        <v>46342</v>
+      </c>
+      <c r="H1145" s="5"/>
+    </row>
+    <row r="1146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1146" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1146" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1146" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1146" s="5">
+        <v>46342</v>
+      </c>
+      <c r="H1146" s="5"/>
+    </row>
+    <row r="1147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1147" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1147" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1147" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1147" s="5">
+        <v>46342</v>
+      </c>
+      <c r="H1147" s="5"/>
+    </row>
+    <row r="1148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1148" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1148" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1148" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1148" s="5">
+        <v>46342</v>
+      </c>
+      <c r="H1148" s="5"/>
+    </row>
+    <row r="1149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1149" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1149" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1149" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1149" s="5">
+        <v>46342</v>
+      </c>
+      <c r="H1149" s="5"/>
+    </row>
+    <row r="1150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1150" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1150" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1150" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1150" s="5">
+        <v>46342</v>
+      </c>
+      <c r="H1150" s="5"/>
+    </row>
+    <row r="1151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1151" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1151" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1151" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1151" s="5">
+        <v>46342</v>
+      </c>
+      <c r="H1151" s="5"/>
+    </row>
+    <row r="1152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1152" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1152" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1152" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1152" s="5">
+        <v>46342</v>
+      </c>
+      <c r="H1152" s="5"/>
+    </row>
+    <row r="1153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1153" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1153" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1153" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1153" s="5">
+        <v>46342</v>
+      </c>
+      <c r="H1153" s="5"/>
+    </row>
+    <row r="1154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1154" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1154" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1154" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1154" s="5">
+        <v>46342</v>
+      </c>
+      <c r="H1154" s="5"/>
+    </row>
+    <row r="1155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1155" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1155" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1155" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1155" s="5">
+        <v>46343</v>
+      </c>
+      <c r="H1155" s="5"/>
+    </row>
+    <row r="1156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1156" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1156" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1156" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1156" s="5">
+        <v>46343</v>
+      </c>
+      <c r="H1156" s="5"/>
+    </row>
+    <row r="1157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1157" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1157" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1157" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1157" s="5">
+        <v>46343</v>
+      </c>
+      <c r="H1157" s="5"/>
+    </row>
+    <row r="1158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1158" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1158" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1158" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1158" s="5">
+        <v>46343</v>
+      </c>
+      <c r="H1158" s="5"/>
+    </row>
+    <row r="1159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1159" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1159" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1159" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1159" s="5">
+        <v>46343</v>
+      </c>
+      <c r="H1159" s="5"/>
+    </row>
+    <row r="1160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1160" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1160" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1160" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1160" s="5">
+        <v>46343</v>
+      </c>
+      <c r="H1160" s="5"/>
+    </row>
+    <row r="1161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1161" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1161" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1161" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1161" s="5">
+        <v>46343</v>
+      </c>
+      <c r="H1161" s="5"/>
+    </row>
+    <row r="1162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1162" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1162" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1162" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1162" s="5">
+        <v>46343</v>
+      </c>
+      <c r="H1162" s="5"/>
+    </row>
+    <row r="1163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1163" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1163" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1163" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1163" s="5">
+        <v>46343</v>
+      </c>
+      <c r="H1163" s="5"/>
+    </row>
+    <row r="1164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1164" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1164" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1164" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1164" s="5">
+        <v>46343</v>
+      </c>
+      <c r="H1164" s="5"/>
+    </row>
+    <row r="1165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1165" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1165" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1165" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1165" s="5">
+        <v>46344</v>
+      </c>
+      <c r="H1165" s="5"/>
+    </row>
+    <row r="1166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1166" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1166" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1166" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1166" s="5">
+        <v>46344</v>
+      </c>
+      <c r="H1166" s="5"/>
+    </row>
+    <row r="1167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1167" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1167" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1167" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1167" s="5">
+        <v>46344</v>
+      </c>
+      <c r="H1167" s="5"/>
+    </row>
+    <row r="1168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1168" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1168" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1168" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1168" s="5">
+        <v>46344</v>
+      </c>
+      <c r="H1168" s="5"/>
+    </row>
+    <row r="1169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1169" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1169" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1169" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1169" s="5">
+        <v>46344</v>
+      </c>
+      <c r="H1169" s="5"/>
+    </row>
+    <row r="1170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1170" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1170" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1170" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1170" s="5">
+        <v>46344</v>
+      </c>
+      <c r="H1170" s="5"/>
+    </row>
+    <row r="1171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1171" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1171" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1171" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1171" s="5">
+        <v>46344</v>
+      </c>
+      <c r="H1171" s="5"/>
+    </row>
+    <row r="1172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1172" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1172" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1172" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1172" s="5">
+        <v>46344</v>
+      </c>
+      <c r="H1172" s="5"/>
+    </row>
+    <row r="1173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1173" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1173" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1173" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1173" s="5">
+        <v>46344</v>
+      </c>
+      <c r="H1173" s="5"/>
+    </row>
+    <row r="1174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1174" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1174" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1174" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1174" s="5">
+        <v>46344</v>
+      </c>
+      <c r="H1174" s="5"/>
+    </row>
+    <row r="1175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1175" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1175" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1175" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1175" s="5">
+        <v>46345</v>
+      </c>
+      <c r="H1175" s="5"/>
+    </row>
+    <row r="1176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1176" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1176" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1176" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1176" s="5">
+        <v>46345</v>
+      </c>
+      <c r="H1176" s="5"/>
+    </row>
+    <row r="1177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1177" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1177" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1177" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1177" s="5">
+        <v>46345</v>
+      </c>
+      <c r="H1177" s="5"/>
+    </row>
+    <row r="1178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1178" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1178" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1178" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1178" s="5">
+        <v>46345</v>
+      </c>
+      <c r="H1178" s="5"/>
+    </row>
+    <row r="1179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1179" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1179" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1179" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1179" s="5">
+        <v>46345</v>
+      </c>
+      <c r="H1179" s="5"/>
+    </row>
+    <row r="1180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1180" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1180" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1180" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1180" s="5">
+        <v>46345</v>
+      </c>
+      <c r="H1180" s="5"/>
+    </row>
+    <row r="1181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1181" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1181" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1181" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1181" s="5">
+        <v>46345</v>
+      </c>
+      <c r="H1181" s="5"/>
+    </row>
+    <row r="1182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1182" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1182" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1182" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1182" s="5">
+        <v>46345</v>
+      </c>
+      <c r="H1182" s="5"/>
+    </row>
+    <row r="1183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1183" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1183" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1183" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1183" s="5">
+        <v>46345</v>
+      </c>
+      <c r="H1183" s="5"/>
+    </row>
+    <row r="1184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1184" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1184" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1184" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1184" s="5">
+        <v>46345</v>
+      </c>
+      <c r="H1184" s="5"/>
+    </row>
+    <row r="1185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1185" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1185" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1185" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1185" s="5">
+        <v>46346</v>
+      </c>
+      <c r="H1185" s="5"/>
+    </row>
+    <row r="1186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1186" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1186" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1186" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1186" s="5">
+        <v>46346</v>
+      </c>
+      <c r="H1186" s="5"/>
+    </row>
+    <row r="1187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1187" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1187" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1187" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1187" s="5">
+        <v>46346</v>
+      </c>
+      <c r="H1187" s="5"/>
+    </row>
+    <row r="1188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1188" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1188" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1188" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1188" s="5">
+        <v>46346</v>
+      </c>
+      <c r="H1188" s="5"/>
+    </row>
+    <row r="1189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1189" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1189" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1189" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1189" s="5">
+        <v>46346</v>
+      </c>
+      <c r="H1189" s="5"/>
+    </row>
+    <row r="1190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1190" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1190" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1190" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1190" s="5">
+        <v>46346</v>
+      </c>
+      <c r="H1190" s="5"/>
+    </row>
+    <row r="1191" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1191" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1191" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1191" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1191" s="5">
+        <v>46346</v>
+      </c>
+      <c r="H1191" s="5"/>
+    </row>
+    <row r="1192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1192" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1192" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1192" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1192" s="5">
+        <v>46346</v>
+      </c>
+      <c r="H1192" s="5"/>
+    </row>
+    <row r="1193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1193" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1193" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1193" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1193" s="5">
+        <v>46346</v>
+      </c>
+      <c r="H1193" s="5"/>
+    </row>
+    <row r="1194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1194" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1194" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1194" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1194" s="5">
+        <v>46346</v>
+      </c>
+      <c r="H1194" s="5"/>
+    </row>
+    <row r="1195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1195" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1195" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1195" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1195" s="5">
+        <v>46347</v>
+      </c>
+      <c r="H1195" s="5"/>
+    </row>
+    <row r="1196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1196" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1196" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1196" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1196" s="5">
+        <v>46347</v>
+      </c>
+      <c r="H1196" s="5"/>
+    </row>
+    <row r="1197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1197" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1197" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1197" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1197" s="5">
+        <v>46347</v>
+      </c>
+      <c r="H1197" s="5"/>
+    </row>
+    <row r="1198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1198" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1198" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1198" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1198" s="5">
+        <v>46347</v>
+      </c>
+      <c r="H1198" s="5"/>
+    </row>
+    <row r="1199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1199" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1199" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1199" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1199" s="5">
+        <v>46347</v>
+      </c>
+      <c r="H1199" s="5"/>
+    </row>
+    <row r="1200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1200" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1200" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1200" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1200" s="5">
+        <v>46347</v>
+      </c>
+      <c r="H1200" s="5"/>
+    </row>
+    <row r="1201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1201" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1201" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1201" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1201" s="5">
+        <v>46347</v>
+      </c>
+      <c r="H1201" s="5"/>
+    </row>
+    <row r="1202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1202" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1202" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1202" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1202" s="5">
+        <v>46347</v>
+      </c>
+      <c r="H1202" s="5"/>
+    </row>
+    <row r="1203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1203" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1203" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1203" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1203" s="5">
+        <v>46347</v>
+      </c>
+      <c r="H1203" s="5"/>
+    </row>
+    <row r="1204" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1204" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1204" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1204" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1204" s="5">
+        <v>46347</v>
+      </c>
+      <c r="H1204" s="5"/>
+    </row>
+    <row r="1205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1205" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1205" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1205" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1205" s="5">
+        <v>46349</v>
+      </c>
+      <c r="H1205" s="5"/>
+    </row>
+    <row r="1206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1206" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1206" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1206" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1206" s="5">
+        <v>46349</v>
+      </c>
+      <c r="H1206" s="5"/>
+    </row>
+    <row r="1207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1207" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1207" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1207" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1207" s="5">
+        <v>46349</v>
+      </c>
+      <c r="H1207" s="5"/>
+    </row>
+    <row r="1208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1208" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1208" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1208" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1208" s="5">
+        <v>46349</v>
+      </c>
+      <c r="H1208" s="5"/>
+    </row>
+    <row r="1209" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1209" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1209" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1209" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1209" s="5">
+        <v>46349</v>
+      </c>
+      <c r="H1209" s="5"/>
+    </row>
+    <row r="1210" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1210" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1210" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1210" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1210" s="5">
+        <v>46349</v>
+      </c>
+      <c r="H1210" s="5"/>
+    </row>
+    <row r="1211" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1211" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1211" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1211" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1211" s="5">
+        <v>46349</v>
+      </c>
+      <c r="H1211" s="5"/>
+    </row>
+    <row r="1212" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1212" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1212" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1212" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1212" s="5">
+        <v>46349</v>
+      </c>
+      <c r="H1212" s="5"/>
+    </row>
+    <row r="1213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1213" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1213" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1213" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1213" s="5">
+        <v>46349</v>
+      </c>
+      <c r="H1213" s="5"/>
+    </row>
+    <row r="1214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1214" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1214" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1214" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1214" s="5">
+        <v>46349</v>
+      </c>
+      <c r="H1214" s="5"/>
+    </row>
+    <row r="1215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1215" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1215" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1215" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1215" s="5">
+        <v>46350</v>
+      </c>
+      <c r="H1215" s="5"/>
+    </row>
+    <row r="1216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1216" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1216" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1216" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1216" s="5">
+        <v>46350</v>
+      </c>
+      <c r="H1216" s="5"/>
+    </row>
+    <row r="1217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1217" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1217" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1217" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1217" s="5">
+        <v>46350</v>
+      </c>
+      <c r="H1217" s="5"/>
+    </row>
+    <row r="1218" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1218" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1218" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1218" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1218" s="5">
+        <v>46350</v>
+      </c>
+      <c r="H1218" s="5"/>
+    </row>
+    <row r="1219" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1219" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1219" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1219" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1219" s="5">
+        <v>46350</v>
+      </c>
+      <c r="H1219" s="5"/>
+    </row>
+    <row r="1220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1220" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1220" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1220" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1220" s="5">
+        <v>46350</v>
+      </c>
+      <c r="H1220" s="5"/>
+    </row>
+    <row r="1221" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1221" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1221" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1221" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1221" s="5">
+        <v>46350</v>
+      </c>
+      <c r="H1221" s="5"/>
+    </row>
+    <row r="1222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1222" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1222" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1222" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1222" s="5">
+        <v>46350</v>
+      </c>
+      <c r="H1222" s="5"/>
+    </row>
+    <row r="1223" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1223" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1223" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1223" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1223" s="5">
+        <v>46350</v>
+      </c>
+      <c r="H1223" s="5"/>
+    </row>
+    <row r="1224" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1224" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1224" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1224" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1224" s="5">
+        <v>46350</v>
+      </c>
+      <c r="H1224" s="5"/>
+    </row>
+    <row r="1225" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1225" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1225" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1225" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1225" s="5">
+        <v>46351</v>
+      </c>
+      <c r="H1225" s="5"/>
+    </row>
+    <row r="1226" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1226" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1226" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1226" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1226" s="5">
+        <v>46351</v>
+      </c>
+      <c r="H1226" s="5"/>
+    </row>
+    <row r="1227" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1227" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1227" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1227" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1227" s="5">
+        <v>46351</v>
+      </c>
+      <c r="H1227" s="5"/>
+    </row>
+    <row r="1228" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1228" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1228" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1228" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1228" s="5">
+        <v>46351</v>
+      </c>
+      <c r="H1228" s="5"/>
+    </row>
+    <row r="1229" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1229" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1229" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1229" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1229" s="5">
+        <v>46351</v>
+      </c>
+      <c r="H1229" s="5"/>
+    </row>
+    <row r="1230" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1230" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1230" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1230" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1230" s="5">
+        <v>46351</v>
+      </c>
+      <c r="H1230" s="5"/>
+    </row>
+    <row r="1231" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1231" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1231" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1231" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1231" s="5">
+        <v>46351</v>
+      </c>
+      <c r="H1231" s="5"/>
+    </row>
+    <row r="1232" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1232" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1232" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1232" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1232" s="5">
+        <v>46351</v>
+      </c>
+      <c r="H1232" s="5"/>
+    </row>
+    <row r="1233" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1233" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1233" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1233" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1233" s="5">
+        <v>46351</v>
+      </c>
+      <c r="H1233" s="5"/>
+    </row>
+    <row r="1234" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1234" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1234" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1234" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1234" s="5">
+        <v>46351</v>
+      </c>
+      <c r="H1234" s="5"/>
+    </row>
+    <row r="1235" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1235" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1235" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1235" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1235" s="5">
+        <v>46352</v>
+      </c>
+      <c r="H1235" s="5"/>
+    </row>
+    <row r="1236" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1236" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1236" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1236" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1236" s="5">
+        <v>46352</v>
+      </c>
+      <c r="H1236" s="5"/>
+    </row>
+    <row r="1237" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1237" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1237" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1237" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1237" s="5">
+        <v>46352</v>
+      </c>
+      <c r="H1237" s="5"/>
+    </row>
+    <row r="1238" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1238" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1238" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1238" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1238" s="5">
+        <v>46352</v>
+      </c>
+      <c r="H1238" s="5"/>
+    </row>
+    <row r="1239" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1239" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1239" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1239" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1239" s="5">
+        <v>46352</v>
+      </c>
+      <c r="H1239" s="5"/>
+    </row>
+    <row r="1240" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1240" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1240" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1240" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1240" s="5">
+        <v>46352</v>
+      </c>
+      <c r="H1240" s="5"/>
+    </row>
+    <row r="1241" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1241" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1241" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1241" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1241" s="5">
+        <v>46352</v>
+      </c>
+      <c r="H1241" s="5"/>
+    </row>
+    <row r="1242" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1242" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1242" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1242" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1242" s="5">
+        <v>46352</v>
+      </c>
+      <c r="H1242" s="5"/>
+    </row>
+    <row r="1243" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1243" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1243" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1243" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1243" s="5">
+        <v>46352</v>
+      </c>
+      <c r="H1243" s="5"/>
+    </row>
+    <row r="1244" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1244" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1244" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1244" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1244" s="5">
+        <v>46352</v>
+      </c>
+      <c r="H1244" s="5"/>
+    </row>
+    <row r="1245" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1245" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1245" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1245" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1245" s="5">
+        <v>46353</v>
+      </c>
+      <c r="H1245" s="5"/>
+    </row>
+    <row r="1246" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1246" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1246" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1246" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1246" s="5">
+        <v>46353</v>
+      </c>
+      <c r="H1246" s="5"/>
+    </row>
+    <row r="1247" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1247" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1247" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1247" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1247" s="5">
+        <v>46353</v>
+      </c>
+      <c r="H1247" s="5"/>
+    </row>
+    <row r="1248" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1248" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1248" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1248" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1248" s="5">
+        <v>46353</v>
+      </c>
+      <c r="H1248" s="5"/>
+    </row>
+    <row r="1249" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1249" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1249" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1249" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1249" s="5">
+        <v>46353</v>
+      </c>
+      <c r="H1249" s="5"/>
+    </row>
+    <row r="1250" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1250" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1250" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1250" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1250" s="5">
+        <v>46353</v>
+      </c>
+      <c r="H1250" s="5"/>
+    </row>
+    <row r="1251" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1251" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1251" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1251" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1251" s="5">
+        <v>46353</v>
+      </c>
+      <c r="H1251" s="5"/>
+    </row>
+    <row r="1252" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1252" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1252" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1252" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1252" s="5">
+        <v>46353</v>
+      </c>
+      <c r="H1252" s="5"/>
+    </row>
+    <row r="1253" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1253" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1253" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1253" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1253" s="5">
+        <v>46353</v>
+      </c>
+      <c r="H1253" s="5"/>
+    </row>
+    <row r="1254" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1254" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1254" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1254" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1254" s="5">
+        <v>46353</v>
+      </c>
+      <c r="H1254" s="5"/>
+    </row>
+    <row r="1255" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1255" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1255" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1255" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1255" s="5">
+        <v>46354</v>
+      </c>
+      <c r="H1255" s="5"/>
+    </row>
+    <row r="1256" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1256" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1256" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1256" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1256" s="5">
+        <v>46354</v>
+      </c>
+      <c r="H1256" s="5"/>
+    </row>
+    <row r="1257" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1257" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1257" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1257" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1257" s="5">
+        <v>46354</v>
+      </c>
+      <c r="H1257" s="5"/>
+    </row>
+    <row r="1258" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1258" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1258" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1258" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1258" s="5">
+        <v>46354</v>
+      </c>
+      <c r="H1258" s="5"/>
+    </row>
+    <row r="1259" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1259" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1259" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1259" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1259" s="5">
+        <v>46354</v>
+      </c>
+      <c r="H1259" s="5"/>
+    </row>
+    <row r="1260" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1260" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1260" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1260" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1260" s="5">
+        <v>46354</v>
+      </c>
+      <c r="H1260" s="5"/>
+    </row>
+    <row r="1261" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1261" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1261" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1261" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1261" s="5">
+        <v>46354</v>
+      </c>
+      <c r="H1261" s="5"/>
+    </row>
+    <row r="1262" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1262" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1262" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1262" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1262" s="5">
+        <v>46354</v>
+      </c>
+      <c r="H1262" s="5"/>
+    </row>
+    <row r="1263" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1263" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1263" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1263" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1263" s="5">
+        <v>46354</v>
+      </c>
+      <c r="H1263" s="5"/>
+    </row>
+    <row r="1264" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1264" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1264" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1264" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1264" s="5">
+        <v>46354</v>
+      </c>
+      <c r="H1264" s="5"/>
+    </row>
+    <row r="1265" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1265" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1265" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1265" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1265" s="5">
+        <v>46356</v>
+      </c>
+      <c r="H1265" s="5"/>
+    </row>
+    <row r="1266" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1266" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1266" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1266" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1266" s="5">
+        <v>46356</v>
+      </c>
+      <c r="H1266" s="5"/>
+    </row>
+    <row r="1267" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1267" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1267" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1267" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1267" s="5">
+        <v>46356</v>
+      </c>
+      <c r="H1267" s="5"/>
+    </row>
+    <row r="1268" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1268" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1268" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1268" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1268" s="5">
+        <v>46356</v>
+      </c>
+      <c r="H1268" s="5"/>
+    </row>
+    <row r="1269" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1269" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1269" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1269" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1269" s="5">
+        <v>46356</v>
+      </c>
+      <c r="H1269" s="5"/>
+    </row>
+    <row r="1270" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1270" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1270" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1270" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1270" s="5">
+        <v>46356</v>
+      </c>
+      <c r="H1270" s="5"/>
+    </row>
+    <row r="1271" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1271" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1271" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1271" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1271" s="5">
+        <v>46356</v>
+      </c>
+      <c r="H1271" s="5"/>
+    </row>
+    <row r="1272" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1272" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1272" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1272" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1272" s="5">
+        <v>46356</v>
+      </c>
+      <c r="H1272" s="5"/>
+    </row>
+    <row r="1273" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1273" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1273" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1273" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1273" s="5">
+        <v>46356</v>
+      </c>
+      <c r="H1273" s="5"/>
+    </row>
+    <row r="1274" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1274" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1274" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1274" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1274" s="5">
+        <v>46356</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1275" s="4"/>
+      <c r="B1275" s="4"/>
+      <c r="C1275" s="4"/>
+    </row>
+    <row r="1276" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1276" s="4"/>
+      <c r="B1276" s="4"/>
+      <c r="C1276" s="4"/>
+    </row>
+    <row r="1277" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1277" s="4"/>
+      <c r="B1277" s="4"/>
+      <c r="C1277" s="4"/>
+    </row>
+    <row r="1278" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1278" s="4"/>
+      <c r="B1278" s="4"/>
+      <c r="C1278" s="4"/>
+    </row>
+    <row r="1279" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1279" s="4"/>
+      <c r="B1279" s="4"/>
+      <c r="C1279" s="4"/>
+    </row>
+    <row r="1280" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1280" s="4"/>
+      <c r="B1280" s="4"/>
+      <c r="C1280" s="4"/>
+    </row>
+    <row r="1281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1281" s="27"/>
+      <c r="B1281" s="27"/>
+      <c r="C1281" s="27"/>
+    </row>
+    <row r="1282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1282" s="4"/>
+      <c r="B1282" s="4"/>
+      <c r="C1282" s="4"/>
+    </row>
+    <row r="1283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1283" s="4"/>
+      <c r="B1283" s="4"/>
+      <c r="C1283" s="4"/>
+    </row>
+    <row r="1284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1284" s="4"/>
+      <c r="B1284" s="4"/>
+      <c r="C1284" s="4"/>
+    </row>
+    <row r="1285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1285" s="4"/>
+      <c r="B1285" s="4"/>
+      <c r="C1285" s="4"/>
+    </row>
+    <row r="1286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1286" s="4"/>
+      <c r="B1286" s="4"/>
+      <c r="C1286" s="4"/>
+    </row>
+    <row r="1287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1287" s="4"/>
+      <c r="B1287" s="4"/>
+      <c r="C1287" s="4"/>
+    </row>
+    <row r="1288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1288" s="4"/>
+      <c r="B1288" s="4"/>
+      <c r="C1288" s="4"/>
+    </row>
+    <row r="1289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1289" s="4"/>
+      <c r="B1289" s="4"/>
+      <c r="C1289" s="4"/>
+    </row>
+    <row r="1290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1290" s="4"/>
+      <c r="B1290" s="4"/>
+      <c r="C1290" s="4"/>
+    </row>
+    <row r="1291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1291" s="27"/>
+      <c r="B1291" s="27"/>
+      <c r="C1291" s="27"/>
+    </row>
+    <row r="1292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1292" s="4"/>
+      <c r="B1292" s="4"/>
+      <c r="C1292" s="4"/>
+    </row>
+    <row r="1293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1293" s="4"/>
+      <c r="B1293" s="4"/>
+      <c r="C1293" s="4"/>
+    </row>
+    <row r="1294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1294" s="4"/>
+      <c r="B1294" s="4"/>
+      <c r="C1294" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1024" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:F1274" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="5">
       <filters>
-        <dateGroupItem year="2026" month="9" dateTimeGrouping="month"/>
         <dateGroupItem year="2026" month="10" dateTimeGrouping="month"/>
+        <dateGroupItem year="2026" month="11" dateTimeGrouping="month"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -22894,7 +26775,7 @@
   <sheetPr filterMode="1">
     <tabColor rgb="FF2E75B6"/>
   </sheetPr>
-  <dimension ref="A1:AG45"/>
+  <dimension ref="A1:AG56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="6" bestFit="1" customWidth="1"/>
@@ -25925,7 +29806,7 @@
         <v>1</v>
       </c>
       <c r="AB36" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC36" s="6">
         <v>0</v>
@@ -25999,7 +29880,7 @@
         <v>2</v>
       </c>
       <c r="AB37" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC37" s="6">
         <v>0</v>
@@ -26073,7 +29954,7 @@
         <v>0</v>
       </c>
       <c r="AB38" s="6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AC38" s="6">
         <v>0</v>
@@ -26147,7 +30028,7 @@
         <v>2</v>
       </c>
       <c r="AB39" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC39" s="6">
         <v>0</v>
@@ -26221,7 +30102,7 @@
         <v>0</v>
       </c>
       <c r="AB40" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC40" s="6">
         <v>0</v>
@@ -26295,7 +30176,7 @@
         <v>0</v>
       </c>
       <c r="AB41" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC41" s="6">
         <v>0</v>
@@ -26369,7 +30250,7 @@
         <v>0</v>
       </c>
       <c r="AB42" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC42" s="6">
         <v>0</v>
@@ -26606,8 +30487,817 @@
         <v>0</v>
       </c>
     </row>
+    <row r="46" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" s="14">
+        <v>46327</v>
+      </c>
+      <c r="D46" s="13">
+        <v>46328</v>
+      </c>
+      <c r="E46" s="13">
+        <v>46329</v>
+      </c>
+      <c r="F46" s="13">
+        <v>46330</v>
+      </c>
+      <c r="G46" s="13">
+        <v>46331</v>
+      </c>
+      <c r="H46" s="13">
+        <v>46332</v>
+      </c>
+      <c r="I46" s="14">
+        <v>46333</v>
+      </c>
+      <c r="J46" s="14">
+        <v>46334</v>
+      </c>
+      <c r="K46" s="13">
+        <v>46335</v>
+      </c>
+      <c r="L46" s="13">
+        <v>46336</v>
+      </c>
+      <c r="M46" s="13">
+        <v>46337</v>
+      </c>
+      <c r="N46" s="13">
+        <v>46338</v>
+      </c>
+      <c r="O46" s="13">
+        <v>46339</v>
+      </c>
+      <c r="P46" s="14">
+        <v>46340</v>
+      </c>
+      <c r="Q46" s="14">
+        <v>46341</v>
+      </c>
+      <c r="R46" s="13">
+        <v>46342</v>
+      </c>
+      <c r="S46" s="13">
+        <v>46343</v>
+      </c>
+      <c r="T46" s="13">
+        <v>46344</v>
+      </c>
+      <c r="U46" s="13">
+        <v>46345</v>
+      </c>
+      <c r="V46" s="13">
+        <v>46346</v>
+      </c>
+      <c r="W46" s="14">
+        <v>46347</v>
+      </c>
+      <c r="X46" s="14">
+        <v>46348</v>
+      </c>
+      <c r="Y46" s="13">
+        <v>46349</v>
+      </c>
+      <c r="Z46" s="13">
+        <v>46350</v>
+      </c>
+      <c r="AA46" s="13">
+        <v>46351</v>
+      </c>
+      <c r="AB46" s="13">
+        <v>46352</v>
+      </c>
+      <c r="AC46" s="13">
+        <v>46353</v>
+      </c>
+      <c r="AD46" s="14">
+        <v>46354</v>
+      </c>
+      <c r="AE46" s="14">
+        <v>46355</v>
+      </c>
+      <c r="AF46" s="13">
+        <v>46356</v>
+      </c>
+      <c r="AG46" s="13"/>
+    </row>
+    <row r="47" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="6">
+        <v>0</v>
+      </c>
+      <c r="E47" s="6">
+        <v>0</v>
+      </c>
+      <c r="F47" s="6">
+        <v>0</v>
+      </c>
+      <c r="G47" s="6">
+        <v>0</v>
+      </c>
+      <c r="H47" s="6">
+        <v>0</v>
+      </c>
+      <c r="K47" s="6">
+        <v>0</v>
+      </c>
+      <c r="L47" s="6">
+        <v>0</v>
+      </c>
+      <c r="M47" s="6">
+        <v>0</v>
+      </c>
+      <c r="N47" s="6">
+        <v>0</v>
+      </c>
+      <c r="O47" s="6">
+        <v>0</v>
+      </c>
+      <c r="R47" s="6">
+        <v>0</v>
+      </c>
+      <c r="S47" s="6">
+        <v>0</v>
+      </c>
+      <c r="T47" s="6">
+        <v>0</v>
+      </c>
+      <c r="U47" s="6">
+        <v>0</v>
+      </c>
+      <c r="V47" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="6">
+        <v>0</v>
+      </c>
+      <c r="E48" s="6">
+        <v>0</v>
+      </c>
+      <c r="F48" s="6">
+        <v>0</v>
+      </c>
+      <c r="G48" s="6">
+        <v>0</v>
+      </c>
+      <c r="H48" s="6">
+        <v>0</v>
+      </c>
+      <c r="K48" s="6">
+        <v>0</v>
+      </c>
+      <c r="L48" s="6">
+        <v>0</v>
+      </c>
+      <c r="M48" s="6">
+        <v>0</v>
+      </c>
+      <c r="N48" s="6">
+        <v>0</v>
+      </c>
+      <c r="O48" s="6">
+        <v>0</v>
+      </c>
+      <c r="R48" s="6">
+        <v>0</v>
+      </c>
+      <c r="S48" s="6">
+        <v>0</v>
+      </c>
+      <c r="T48" s="6">
+        <v>0</v>
+      </c>
+      <c r="U48" s="6">
+        <v>0</v>
+      </c>
+      <c r="V48" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z48" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB48" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF48" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D49" s="6">
+        <v>0</v>
+      </c>
+      <c r="E49" s="6">
+        <v>0</v>
+      </c>
+      <c r="F49" s="6">
+        <v>0</v>
+      </c>
+      <c r="G49" s="6">
+        <v>0</v>
+      </c>
+      <c r="H49" s="6">
+        <v>0</v>
+      </c>
+      <c r="K49" s="6">
+        <v>0</v>
+      </c>
+      <c r="L49" s="6">
+        <v>0</v>
+      </c>
+      <c r="M49" s="6">
+        <v>0</v>
+      </c>
+      <c r="N49" s="6">
+        <v>0</v>
+      </c>
+      <c r="O49" s="6">
+        <v>0</v>
+      </c>
+      <c r="R49" s="6">
+        <v>0</v>
+      </c>
+      <c r="S49" s="6">
+        <v>0</v>
+      </c>
+      <c r="T49" s="6">
+        <v>0</v>
+      </c>
+      <c r="U49" s="6">
+        <v>0</v>
+      </c>
+      <c r="V49" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB49" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF49" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D50" s="6">
+        <v>0</v>
+      </c>
+      <c r="E50" s="6">
+        <v>0</v>
+      </c>
+      <c r="F50" s="6">
+        <v>0</v>
+      </c>
+      <c r="G50" s="6">
+        <v>0</v>
+      </c>
+      <c r="H50" s="6">
+        <v>0</v>
+      </c>
+      <c r="K50" s="6">
+        <v>0</v>
+      </c>
+      <c r="L50" s="6">
+        <v>0</v>
+      </c>
+      <c r="M50" s="6">
+        <v>0</v>
+      </c>
+      <c r="N50" s="6">
+        <v>0</v>
+      </c>
+      <c r="O50" s="6">
+        <v>0</v>
+      </c>
+      <c r="R50" s="6">
+        <v>0</v>
+      </c>
+      <c r="S50" s="6">
+        <v>0</v>
+      </c>
+      <c r="T50" s="6">
+        <v>0</v>
+      </c>
+      <c r="U50" s="6">
+        <v>0</v>
+      </c>
+      <c r="V50" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF50" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="6">
+        <v>0</v>
+      </c>
+      <c r="E51" s="6">
+        <v>0</v>
+      </c>
+      <c r="F51" s="6">
+        <v>0</v>
+      </c>
+      <c r="G51" s="6">
+        <v>0</v>
+      </c>
+      <c r="H51" s="6">
+        <v>0</v>
+      </c>
+      <c r="K51" s="6">
+        <v>0</v>
+      </c>
+      <c r="L51" s="6">
+        <v>0</v>
+      </c>
+      <c r="M51" s="6">
+        <v>0</v>
+      </c>
+      <c r="N51" s="6">
+        <v>0</v>
+      </c>
+      <c r="O51" s="6">
+        <v>0</v>
+      </c>
+      <c r="R51" s="6">
+        <v>0</v>
+      </c>
+      <c r="S51" s="6">
+        <v>0</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>0</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D52" s="6">
+        <v>0</v>
+      </c>
+      <c r="E52" s="6">
+        <v>0</v>
+      </c>
+      <c r="F52" s="6">
+        <v>0</v>
+      </c>
+      <c r="G52" s="6">
+        <v>0</v>
+      </c>
+      <c r="H52" s="6">
+        <v>0</v>
+      </c>
+      <c r="K52" s="6">
+        <v>0</v>
+      </c>
+      <c r="L52" s="6">
+        <v>0</v>
+      </c>
+      <c r="M52" s="6">
+        <v>0</v>
+      </c>
+      <c r="N52" s="6">
+        <v>0</v>
+      </c>
+      <c r="O52" s="6">
+        <v>0</v>
+      </c>
+      <c r="R52" s="6">
+        <v>0</v>
+      </c>
+      <c r="S52" s="6">
+        <v>0</v>
+      </c>
+      <c r="T52" s="6">
+        <v>0</v>
+      </c>
+      <c r="U52" s="6">
+        <v>0</v>
+      </c>
+      <c r="V52" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D53" s="6">
+        <v>0</v>
+      </c>
+      <c r="E53" s="6">
+        <v>0</v>
+      </c>
+      <c r="F53" s="6">
+        <v>0</v>
+      </c>
+      <c r="G53" s="6">
+        <v>0</v>
+      </c>
+      <c r="H53" s="6">
+        <v>0</v>
+      </c>
+      <c r="K53" s="6">
+        <v>0</v>
+      </c>
+      <c r="L53" s="6">
+        <v>0</v>
+      </c>
+      <c r="M53" s="6">
+        <v>0</v>
+      </c>
+      <c r="N53" s="6">
+        <v>0</v>
+      </c>
+      <c r="O53" s="6">
+        <v>0</v>
+      </c>
+      <c r="R53" s="6">
+        <v>0</v>
+      </c>
+      <c r="S53" s="6">
+        <v>0</v>
+      </c>
+      <c r="T53" s="6">
+        <v>0</v>
+      </c>
+      <c r="U53" s="6">
+        <v>0</v>
+      </c>
+      <c r="V53" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D54" s="6">
+        <v>0</v>
+      </c>
+      <c r="E54" s="6">
+        <v>0</v>
+      </c>
+      <c r="F54" s="6">
+        <v>0</v>
+      </c>
+      <c r="G54" s="6">
+        <v>0</v>
+      </c>
+      <c r="H54" s="6">
+        <v>0</v>
+      </c>
+      <c r="K54" s="6">
+        <v>0</v>
+      </c>
+      <c r="L54" s="6">
+        <v>0</v>
+      </c>
+      <c r="M54" s="6">
+        <v>0</v>
+      </c>
+      <c r="N54" s="6">
+        <v>0</v>
+      </c>
+      <c r="O54" s="6">
+        <v>0</v>
+      </c>
+      <c r="R54" s="6">
+        <v>0</v>
+      </c>
+      <c r="S54" s="6">
+        <v>0</v>
+      </c>
+      <c r="T54" s="6">
+        <v>0</v>
+      </c>
+      <c r="U54" s="6">
+        <v>0</v>
+      </c>
+      <c r="V54" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB54" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC54" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF54" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" s="6">
+        <v>0</v>
+      </c>
+      <c r="E55" s="6">
+        <v>0</v>
+      </c>
+      <c r="F55" s="6">
+        <v>0</v>
+      </c>
+      <c r="G55" s="6">
+        <v>0</v>
+      </c>
+      <c r="H55" s="6">
+        <v>0</v>
+      </c>
+      <c r="K55" s="6">
+        <v>0</v>
+      </c>
+      <c r="L55" s="6">
+        <v>0</v>
+      </c>
+      <c r="M55" s="6">
+        <v>0</v>
+      </c>
+      <c r="N55" s="6">
+        <v>0</v>
+      </c>
+      <c r="O55" s="6">
+        <v>0</v>
+      </c>
+      <c r="R55" s="6">
+        <v>0</v>
+      </c>
+      <c r="S55" s="6">
+        <v>0</v>
+      </c>
+      <c r="T55" s="6">
+        <v>0</v>
+      </c>
+      <c r="U55" s="6">
+        <v>0</v>
+      </c>
+      <c r="V55" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y55" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF55" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D56" s="6">
+        <v>0</v>
+      </c>
+      <c r="E56" s="6">
+        <v>0</v>
+      </c>
+      <c r="F56" s="6">
+        <v>0</v>
+      </c>
+      <c r="G56" s="6">
+        <v>0</v>
+      </c>
+      <c r="H56" s="6">
+        <v>0</v>
+      </c>
+      <c r="K56" s="6">
+        <v>0</v>
+      </c>
+      <c r="L56" s="6">
+        <v>0</v>
+      </c>
+      <c r="M56" s="6">
+        <v>0</v>
+      </c>
+      <c r="N56" s="6">
+        <v>0</v>
+      </c>
+      <c r="O56" s="6">
+        <v>0</v>
+      </c>
+      <c r="R56" s="6">
+        <v>0</v>
+      </c>
+      <c r="S56" s="6">
+        <v>0</v>
+      </c>
+      <c r="T56" s="6">
+        <v>0</v>
+      </c>
+      <c r="U56" s="6">
+        <v>0</v>
+      </c>
+      <c r="V56" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y56" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA56" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB56" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC56" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF56" s="6">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:A45" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <autoFilter ref="A1:A56" xr:uid="{00000000-0001-0000-0200-000000000000}">
     <filterColumn colId="0">
       <filters>
         <filter val="Outubro"/>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1911" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{891806F6-4FB8-461D-ABF9-7CA46C28209E}"/>
+  <xr:revisionPtr revIDLastSave="1930" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE1AFCA4-9ED2-412A-B675-68198CD010E6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -20940,6 +20940,9 @@
       <c r="C975" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="D975" s="6">
+        <v>2004</v>
+      </c>
       <c r="E975" s="18">
         <v>4117.5</v>
       </c>
@@ -20957,6 +20960,9 @@
       <c r="C976" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="D976" s="6">
+        <v>3008.5</v>
+      </c>
       <c r="E976" s="18">
         <v>3660</v>
       </c>
@@ -20973,6 +20979,9 @@
       </c>
       <c r="C977" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="D977" s="6">
+        <v>707.5</v>
       </c>
       <c r="E977" s="18">
         <v>1372.5</v>
@@ -20991,6 +21000,9 @@
       <c r="C978" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="D978" s="6">
+        <v>2109.5</v>
+      </c>
       <c r="E978" s="18">
         <v>3450</v>
       </c>
@@ -21008,6 +21020,9 @@
       <c r="C979" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D979" s="6">
+        <v>2118</v>
+      </c>
       <c r="E979" s="18">
         <v>2300</v>
       </c>
@@ -21025,6 +21040,9 @@
       <c r="C980" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="D980" s="6">
+        <v>895</v>
+      </c>
       <c r="E980" s="18">
         <v>1500</v>
       </c>
@@ -21042,6 +21060,9 @@
       <c r="C981" s="27" t="s">
         <v>25</v>
       </c>
+      <c r="D981" s="6">
+        <v>1168</v>
+      </c>
       <c r="E981" s="18">
         <v>1510</v>
       </c>
@@ -21059,6 +21080,9 @@
       <c r="C982" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="D982" s="6">
+        <v>327</v>
+      </c>
       <c r="E982" s="18">
         <v>1000</v>
       </c>
@@ -21076,6 +21100,9 @@
       <c r="C983" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="D983" s="6">
+        <v>884.5</v>
+      </c>
       <c r="E983" s="18">
         <v>1305</v>
       </c>
@@ -21092,6 +21119,9 @@
       </c>
       <c r="C984" s="4" t="s">
         <v>70</v>
+      </c>
+      <c r="D984" s="6">
+        <v>319</v>
       </c>
       <c r="E984" s="18">
         <v>800</v>
@@ -29809,7 +29839,7 @@
         <v>1</v>
       </c>
       <c r="AC36" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD36" s="6">
         <v>0</v>
@@ -29883,7 +29913,7 @@
         <v>1</v>
       </c>
       <c r="AC37" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD37" s="6">
         <v>0</v>
@@ -29957,7 +29987,7 @@
         <v>5</v>
       </c>
       <c r="AC38" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD38" s="6">
         <v>0</v>
@@ -30031,7 +30061,7 @@
         <v>3</v>
       </c>
       <c r="AC39" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD39" s="6">
         <v>0</v>
@@ -30105,7 +30135,7 @@
         <v>3</v>
       </c>
       <c r="AC40" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD40" s="6">
         <v>0</v>
@@ -30179,7 +30209,7 @@
         <v>2</v>
       </c>
       <c r="AC41" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD41" s="6">
         <v>0</v>
@@ -30253,7 +30283,7 @@
         <v>1</v>
       </c>
       <c r="AC42" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD42" s="6">
         <v>0</v>
@@ -30401,7 +30431,7 @@
         <v>0</v>
       </c>
       <c r="AC44" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD44" s="6">
         <v>0</v>
@@ -30475,7 +30505,7 @@
         <v>0</v>
       </c>
       <c r="AC45" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD45" s="6">
         <v>0</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1930" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE1AFCA4-9ED2-412A-B675-68198CD010E6}"/>
+  <xr:revisionPtr revIDLastSave="1947" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E01C572A-2275-43EC-9738-72C05233874C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -21140,6 +21140,9 @@
       <c r="C985" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="D985" s="6">
+        <v>2117.5</v>
+      </c>
       <c r="E985" s="18">
         <v>4117.5</v>
       </c>
@@ -21157,6 +21160,9 @@
       <c r="C986" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="D986" s="6">
+        <v>3280</v>
+      </c>
       <c r="E986" s="18">
         <v>3660</v>
       </c>
@@ -21173,6 +21179,9 @@
       </c>
       <c r="C987" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="D987" s="6">
+        <v>807.5</v>
       </c>
       <c r="E987" s="18">
         <v>1372.5</v>
@@ -21191,6 +21200,9 @@
       <c r="C988" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="D988" s="6">
+        <v>2335.5</v>
+      </c>
       <c r="E988" s="18">
         <v>3450</v>
       </c>
@@ -21208,6 +21220,9 @@
       <c r="C989" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D989" s="6">
+        <v>2187</v>
+      </c>
       <c r="E989" s="18">
         <v>2300</v>
       </c>
@@ -21225,6 +21240,9 @@
       <c r="C990" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="D990" s="6">
+        <v>983</v>
+      </c>
       <c r="E990" s="18">
         <v>1500</v>
       </c>
@@ -21242,6 +21260,9 @@
       <c r="C991" s="27" t="s">
         <v>25</v>
       </c>
+      <c r="D991" s="6">
+        <v>1264</v>
+      </c>
       <c r="E991" s="18">
         <v>1510</v>
       </c>
@@ -21259,6 +21280,9 @@
       <c r="C992" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="D992" s="6">
+        <v>403</v>
+      </c>
       <c r="E992" s="18">
         <v>1000</v>
       </c>
@@ -21276,6 +21300,9 @@
       <c r="C993" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="D993" s="6">
+        <v>908.5</v>
+      </c>
       <c r="E993" s="18">
         <v>1305</v>
       </c>
@@ -21292,6 +21319,9 @@
       </c>
       <c r="C994" s="4" t="s">
         <v>70</v>
+      </c>
+      <c r="D994" s="6">
+        <v>335</v>
       </c>
       <c r="E994" s="18">
         <v>800</v>
@@ -29842,7 +29872,7 @@
         <v>2</v>
       </c>
       <c r="AD36" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE36" s="6">
         <v>0</v>
@@ -29916,7 +29946,7 @@
         <v>1</v>
       </c>
       <c r="AD37" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE37" s="6">
         <v>0</v>
@@ -29990,7 +30020,7 @@
         <v>1</v>
       </c>
       <c r="AD38" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE38" s="6">
         <v>0</v>
@@ -30064,7 +30094,7 @@
         <v>1</v>
       </c>
       <c r="AD39" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE39" s="6">
         <v>0</v>
@@ -30138,7 +30168,7 @@
         <v>2</v>
       </c>
       <c r="AD40" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE40" s="6">
         <v>0</v>
@@ -30212,7 +30242,7 @@
         <v>1</v>
       </c>
       <c r="AD41" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE41" s="6">
         <v>0</v>
@@ -30286,7 +30316,7 @@
         <v>1</v>
       </c>
       <c r="AD42" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE42" s="6">
         <v>0</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1947" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E01C572A-2275-43EC-9738-72C05233874C}"/>
+  <xr:revisionPtr revIDLastSave="1984" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33C3F950-28FC-445E-AF86-3922C3F39663}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25819,10 +25819,18 @@
       <c r="B6" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
+      <c r="C6" s="24">
+        <v>9</v>
+      </c>
+      <c r="D6" s="24">
+        <v>16</v>
+      </c>
+      <c r="E6" s="24">
+        <v>23</v>
+      </c>
+      <c r="F6" s="24">
+        <v>30</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="22">
@@ -26073,7 +26081,7 @@
         <v>4117.5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>21</v>
       </c>
@@ -26083,9 +26091,11 @@
       <c r="C6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="18"/>
-    </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D6" s="18">
+        <v>3892.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>22</v>
       </c>
@@ -26095,7 +26105,9 @@
       <c r="C7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="17"/>
+      <c r="D7" s="17">
+        <v>3802.5</v>
+      </c>
     </row>
     <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
@@ -26153,7 +26165,7 @@
         <v>3660</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>21</v>
       </c>
@@ -26163,9 +26175,11 @@
       <c r="C12" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="18"/>
-    </row>
-    <row r="13" spans="1:8" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D12" s="18">
+        <v>3460</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>22</v>
       </c>
@@ -26175,7 +26189,9 @@
       <c r="C13" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="17"/>
+      <c r="D13" s="17">
+        <v>3380</v>
+      </c>
     </row>
     <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
@@ -26233,7 +26249,7 @@
         <v>1372.5</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>21</v>
       </c>
@@ -26243,9 +26259,11 @@
       <c r="C18" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="18"/>
-    </row>
-    <row r="19" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D18" s="18">
+        <v>1297.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>22</v>
       </c>
@@ -26255,7 +26273,9 @@
       <c r="C19" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="17"/>
+      <c r="D19" s="17">
+        <v>1267.5</v>
+      </c>
     </row>
     <row r="20" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
@@ -26313,7 +26333,7 @@
         <v>3450</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>21</v>
       </c>
@@ -26323,9 +26343,11 @@
       <c r="C24" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D24" s="18"/>
-    </row>
-    <row r="25" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D24" s="18">
+        <v>3210</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>22</v>
       </c>
@@ -26335,7 +26357,9 @@
       <c r="C25" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D25" s="17"/>
+      <c r="D25" s="17">
+        <v>2940</v>
+      </c>
     </row>
     <row r="26" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
@@ -26393,7 +26417,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>21</v>
       </c>
@@ -26403,9 +26427,11 @@
       <c r="C30" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D30" s="18"/>
-    </row>
-    <row r="31" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D30" s="18">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
         <v>22</v>
       </c>
@@ -26415,7 +26441,9 @@
       <c r="C31" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="17"/>
+      <c r="D31" s="17">
+        <v>1960</v>
+      </c>
     </row>
     <row r="32" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
@@ -26473,7 +26501,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>21</v>
       </c>
@@ -26483,9 +26511,11 @@
       <c r="C36" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D36" s="18"/>
-    </row>
-    <row r="37" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D36" s="18">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
         <v>22</v>
       </c>
@@ -26495,7 +26525,9 @@
       <c r="C37" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D37" s="17"/>
+      <c r="D37" s="17">
+        <v>1258</v>
+      </c>
     </row>
     <row r="38" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
@@ -26553,7 +26585,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
         <v>21</v>
       </c>
@@ -26563,9 +26595,11 @@
       <c r="C42" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D42" s="18"/>
-    </row>
-    <row r="43" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D42" s="18">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
         <v>22</v>
       </c>
@@ -26575,7 +26609,9 @@
       <c r="C43" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D43" s="17"/>
+      <c r="D43" s="17">
+        <v>1250</v>
+      </c>
     </row>
     <row r="44" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
@@ -26633,7 +26669,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
         <v>21</v>
       </c>
@@ -26643,9 +26679,11 @@
       <c r="C48" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D48" s="18"/>
-    </row>
-    <row r="49" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D48" s="18">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
         <v>22</v>
       </c>
@@ -26655,7 +26693,9 @@
       <c r="C49" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D49" s="17"/>
+      <c r="D49" s="17">
+        <v>820</v>
+      </c>
     </row>
     <row r="50" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
@@ -26713,7 +26753,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
         <v>21</v>
       </c>
@@ -26723,9 +26763,11 @@
       <c r="C54" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D54" s="18"/>
-    </row>
-    <row r="55" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D54" s="18">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
         <v>22</v>
       </c>
@@ -26735,7 +26777,9 @@
       <c r="C55" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D55" s="17"/>
+      <c r="D55" s="17">
+        <v>1055</v>
+      </c>
     </row>
     <row r="56" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
@@ -26793,7 +26837,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
         <v>21</v>
       </c>
@@ -26803,9 +26847,11 @@
       <c r="C60" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D60" s="18"/>
-    </row>
-    <row r="61" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D60" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="s">
         <v>22</v>
       </c>
@@ -26815,12 +26861,16 @@
       <c r="C61" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D61" s="17"/>
+      <c r="D61" s="17">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D61" xr:uid="{00000000-0001-0000-0100-000000000000}">
     <filterColumn colId="0">
       <filters>
+        <filter val="Dezembro"/>
+        <filter val="Novembro"/>
         <filter val="Outubro"/>
       </filters>
     </filterColumn>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/Alessandro/Dashbord/METAS PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1984" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33C3F950-28FC-445E-AF86-3922C3F39663}"/>
+  <xr:revisionPtr revIDLastSave="1998" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6112E545-4DE1-403D-9405-DEBC6101F914}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -21340,6 +21340,9 @@
       <c r="C995" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="D995" s="6">
+        <v>2210.5</v>
+      </c>
       <c r="E995" s="18">
         <v>4117.5</v>
       </c>
@@ -21357,6 +21360,9 @@
       <c r="C996" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="D996" s="6">
+        <v>3458</v>
+      </c>
       <c r="E996" s="18">
         <v>3660</v>
       </c>
@@ -21373,6 +21379,9 @@
       </c>
       <c r="C997" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="D997" s="6">
+        <v>861</v>
       </c>
       <c r="E997" s="18">
         <v>1372.5</v>
@@ -21391,6 +21400,9 @@
       <c r="C998" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="D998" s="6">
+        <v>2576</v>
+      </c>
       <c r="E998" s="18">
         <v>3450</v>
       </c>
@@ -21408,6 +21420,9 @@
       <c r="C999" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D999" s="6">
+        <v>2255</v>
+      </c>
       <c r="E999" s="18">
         <v>2300</v>
       </c>
@@ -21425,6 +21440,9 @@
       <c r="C1000" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="D1000" s="6">
+        <v>1024.5</v>
+      </c>
       <c r="E1000" s="18">
         <v>1500</v>
       </c>
@@ -21442,6 +21460,9 @@
       <c r="C1001" s="27" t="s">
         <v>25</v>
       </c>
+      <c r="D1001" s="6">
+        <v>1430.5</v>
+      </c>
       <c r="E1001" s="18">
         <v>1510</v>
       </c>
@@ -21459,6 +21480,9 @@
       <c r="C1002" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="D1002" s="6">
+        <v>423.5</v>
+      </c>
       <c r="E1002" s="18">
         <v>1000</v>
       </c>
@@ -21476,6 +21500,9 @@
       <c r="C1003" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="D1003" s="6">
+        <v>944</v>
+      </c>
       <c r="E1003" s="18">
         <v>1305</v>
       </c>
@@ -21492,6 +21519,9 @@
       </c>
       <c r="C1004" s="4" t="s">
         <v>70</v>
+      </c>
+      <c r="D1004" s="6">
+        <v>378</v>
       </c>
       <c r="E1004" s="18">
         <v>800</v>
@@ -29999,7 +30029,7 @@
         <v>3</v>
       </c>
       <c r="AE37" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF37" s="6">
         <v>0</v>
@@ -30073,7 +30103,7 @@
         <v>3</v>
       </c>
       <c r="AE38" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF38" s="6">
         <v>0</v>
@@ -30147,7 +30177,7 @@
         <v>2</v>
       </c>
       <c r="AE39" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF39" s="6">
         <v>0</v>
@@ -30221,7 +30251,7 @@
         <v>1</v>
       </c>
       <c r="AE40" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF40" s="6">
         <v>0</v>
